--- a/tables/Flexible CUE/Local_estpar_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_True_vo_True_CUE_True.xlsx
@@ -588,46 +588,46 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301524983055982</v>
+        <v>0.001838908966245269</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2101434442509864</v>
+        <v>0.004801288814977661</v>
       </c>
       <c r="M2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.428549100137174</v>
       </c>
       <c r="N2" t="n">
-        <v>4.388065537784857</v>
+        <v>4.430319695540526</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002616589558701607</v>
+        <v>0.00181243363692048</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002638249850423418</v>
+        <v>1.000000000020666e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001238831000339568</v>
+        <v>0.001265151641667229</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009919188896053855</v>
+        <v>0.0006572126239619282</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006355976787112878</v>
+        <v>0.0003013662695292899</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00837852615154956</v>
+        <v>0.007220662104250231</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00583321089564182</v>
+        <v>0.01335677176717739</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004203906145009709</v>
+        <v>0.004609781837847328</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001894995549107314</v>
+        <v>0.004339154019135831</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001570584031072673</v>
+        <v>0.00544199787126697</v>
       </c>
     </row>
     <row r="3">
@@ -668,46 +668,46 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001488718167071711</v>
+        <v>0.001488722301635293</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003526760984496855</v>
+        <v>0.003526771802274085</v>
       </c>
       <c r="M3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.340363192882071</v>
       </c>
       <c r="N3" t="n">
-        <v>4.31334778997532</v>
+        <v>4.312630789934726</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002072724865327512</v>
+        <v>0.002072717941895862</v>
       </c>
       <c r="P3" t="n">
-        <v>1.000000000000194e-05</v>
+        <v>1.000000000000539e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009345557298921726</v>
+        <v>0.0009345535120094947</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003666811996349373</v>
+        <v>0.0003666806132081498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001870069537692181</v>
+        <v>0.0001870037091887262</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009515640008486469</v>
+        <v>0.009515705338381256</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02160094727709794</v>
+        <v>0.02160099393560846</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003002846549581499</v>
+        <v>0.003002790181098498</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004586376134727599</v>
+        <v>0.004586380540618682</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003639370598224325</v>
+        <v>0.003639364459247231</v>
       </c>
     </row>
     <row r="4">
@@ -748,46 +748,46 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4340590818808676</v>
+        <v>0.4182132258886959</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2117991851850853</v>
+        <v>0.2202130590196362</v>
       </c>
       <c r="M4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.293493812215727</v>
       </c>
       <c r="N4" t="n">
-        <v>4.431950470530878</v>
+        <v>4.558566168431991</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002965111603674069</v>
+        <v>0.002791111708370265</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00237275730284839</v>
+        <v>0.002317129919691388</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005108488663115309</v>
+        <v>0.0005257623692854295</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001107958688434967</v>
+        <v>0.001144606864305468</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002582806557295051</v>
+        <v>0.0002604835020386588</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009051400660800003</v>
+        <v>0.008282507116400826</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006483331898713885</v>
+        <v>0.006153530817096397</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002521191026231846</v>
+        <v>0.002620901503959097</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001920440754346314</v>
+        <v>0.002079355207349396</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001548014133780756</v>
+        <v>0.001591051297729244</v>
       </c>
     </row>
     <row r="5">
@@ -828,46 +828,46 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851828485504524</v>
+        <v>0.1838378561531941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2270412700758009</v>
+        <v>0.2239793250601291</v>
       </c>
       <c r="M5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.308694607789535</v>
       </c>
       <c r="N5" t="n">
-        <v>4.405659794622688</v>
+        <v>4.348658188890339</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002366628443364324</v>
+        <v>0.002359367928976639</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002184698987051882</v>
+        <v>0.00216167928923792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001408058666062747</v>
+        <v>0.001407036633308179</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000838750953258824</v>
+        <v>0.0008342967139811359</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001167234321758539</v>
+        <v>0.001161370413790567</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007547873389149824</v>
+        <v>0.007528554891609053</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004379037214246165</v>
+        <v>0.004340090029285593</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004889909623474245</v>
+        <v>0.004898429666654569</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001622449103374284</v>
+        <v>0.001660147201223164</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002516579398797982</v>
+        <v>0.002486558493163133</v>
       </c>
     </row>
     <row r="6">
@@ -908,46 +908,46 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1709875190959763</v>
+        <v>0.1683825408883233</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2157404983534841</v>
+        <v>0.2128810735540558</v>
       </c>
       <c r="M6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.376451817448588</v>
       </c>
       <c r="N6" t="n">
-        <v>4.470737369374437</v>
+        <v>4.382914066084051</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001784765036338482</v>
+        <v>0.001759699108784047</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001400818682329281</v>
+        <v>0.001371696633390666</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008773091420074899</v>
+        <v>0.0008848921533980229</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004022359768442972</v>
+        <v>0.0003979444488495593</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003587797180150623</v>
+        <v>0.0003554642255074089</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005408457359194511</v>
+        <v>0.005320201585769097</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002462997846837224</v>
+        <v>0.002524265543290404</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002788619075206999</v>
+        <v>0.002824905179679858</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009537581822528465</v>
+        <v>0.0009754383319290675</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001072661522743269</v>
+        <v>0.001054559052407779</v>
       </c>
     </row>
     <row r="7">
@@ -988,46 +988,46 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001787394683151308</v>
+        <v>0.001787398233962809</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004065258744681145</v>
+        <v>0.004065270357696367</v>
       </c>
       <c r="M7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.252970041033242</v>
       </c>
       <c r="N7" t="n">
-        <v>4.318694485384197</v>
+        <v>4.358146218724919</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00258899757797919</v>
+        <v>0.00258899009536736</v>
       </c>
       <c r="P7" t="n">
-        <v>1.000000000000118e-05</v>
+        <v>1.000000000004398e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007417311201976686</v>
+        <v>0.0007417309071018624</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006067859208564781</v>
+        <v>0.0006067861512552388</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002746880780731669</v>
+        <v>0.0002746896904264295</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01161112254771015</v>
+        <v>0.01161070953494402</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02701826992642997</v>
+        <v>0.02701805903610212</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003105183195528964</v>
+        <v>0.003105164155020395</v>
       </c>
       <c r="W7" t="n">
-        <v>0.007929217107218058</v>
+        <v>0.007929144812544822</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008160920292865527</v>
+        <v>0.008160861657476121</v>
       </c>
     </row>
     <row r="8">
@@ -1068,46 +1068,46 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1585030469725749</v>
+        <v>0.1601303832383536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1474081655145545</v>
+        <v>0.1522977922019766</v>
       </c>
       <c r="M8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.44514495646937</v>
       </c>
       <c r="N8" t="n">
-        <v>4.281552095051933</v>
+        <v>4.408810185001522</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00506611137510772</v>
+        <v>0.005078307386426126</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00275120073326398</v>
+        <v>0.002790201184433834</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001425607369946249</v>
+        <v>0.00142924531364939</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001437791893319581</v>
+        <v>0.001446189069921446</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006784148982709919</v>
+        <v>0.0006845102427713426</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02107117514718748</v>
+        <v>0.02107203520869344</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009203938540081376</v>
+        <v>0.009185300390162975</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004843202666290762</v>
+        <v>0.004877947084765272</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003018989241052143</v>
+        <v>0.003091512397015516</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00142873392370399</v>
+        <v>0.00144215010920352</v>
       </c>
     </row>
     <row r="9">
@@ -1148,46 +1148,46 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00132723150364138</v>
+        <v>0.00132724233869487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004151845156587003</v>
+        <v>0.00415186641684472</v>
       </c>
       <c r="M9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.224225056384286</v>
       </c>
       <c r="N9" t="n">
-        <v>4.364795001937667</v>
+        <v>4.344234670659814</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003611062822837588</v>
+        <v>0.003611015906108416</v>
       </c>
       <c r="P9" t="n">
-        <v>1.000000002321202e-05</v>
+        <v>1.000000000072385e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001061412021623172</v>
+        <v>0.001061413336212196</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006557843782613906</v>
+        <v>0.0006557840610649507</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0006296328945097099</v>
+        <v>0.0006296329335881741</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01536882682943342</v>
+        <v>0.01536833022798306</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01926140438959622</v>
+        <v>0.01926139535871686</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003756025360054701</v>
+        <v>0.003756038970481013</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004897507250450503</v>
+        <v>0.004897516613533341</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003717896549791484</v>
+        <v>0.003717905149215594</v>
       </c>
     </row>
     <row r="10">
@@ -1228,46 +1228,46 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2213013737149055</v>
+        <v>0.2184121480973804</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1157855817224158</v>
+        <v>0.1173373640138827</v>
       </c>
       <c r="M10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.114152557453664</v>
       </c>
       <c r="N10" t="n">
-        <v>4.178003108204181</v>
+        <v>4.236237869017937</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004513772446699434</v>
+        <v>0.004504611049889398</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003048488084371499</v>
+        <v>0.003053536285341186</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007332206758455338</v>
+        <v>0.0007341552063229759</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00101424043687271</v>
+        <v>0.001016859689721932</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005841905544395916</v>
+        <v>0.0005845228032727086</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0182476363798524</v>
+        <v>0.01819965483089298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01026254676605237</v>
+        <v>0.01017847888491195</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002168591349996531</v>
+        <v>0.002178538063623833</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001868670940513711</v>
+        <v>0.001923673799178807</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001311334006423872</v>
+        <v>0.001307551328464436</v>
       </c>
     </row>
     <row r="11">
@@ -1308,46 +1308,46 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1753512382165856</v>
+        <v>0.1757473902023626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3448783154534303</v>
+        <v>0.346737297774575</v>
       </c>
       <c r="M11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.070128680268422</v>
       </c>
       <c r="N11" t="n">
-        <v>4.244686102385959</v>
+        <v>4.260751537960866</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002906096081903612</v>
+        <v>0.002910557884972551</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001703469216567865</v>
+        <v>0.001710580451432206</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004595009044597567</v>
+        <v>0.004600689920554843</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00181741968759942</v>
+        <v>0.001827338124300223</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001643858650361816</v>
+        <v>0.001644515380493603</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009945524731490745</v>
+        <v>0.009917333818493876</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003460771885063549</v>
+        <v>0.003546882173476502</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02349771079751779</v>
+        <v>0.02365734662705007</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00407237131916157</v>
+        <v>0.00433165744879935</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00367313071522006</v>
+        <v>0.003683025112671779</v>
       </c>
     </row>
     <row r="12">
@@ -1388,46 +1388,46 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1045250285804663</v>
+        <v>0.1058258334398891</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1656456054144585</v>
+        <v>0.1650178171755515</v>
       </c>
       <c r="M12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.069166306475234</v>
       </c>
       <c r="N12" t="n">
-        <v>4.069970356007272</v>
+        <v>4.116738332305455</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001233441459721532</v>
+        <v>0.001236844122141616</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001923862103784724</v>
+        <v>0.001893568259837541</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0006987373609616335</v>
+        <v>0.0006708561132844725</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001603475176922114</v>
+        <v>0.001577945078393295</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005194912048528896</v>
+        <v>0.0005159289436911813</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005120557339498319</v>
+        <v>0.005180714883698488</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004840586088087928</v>
+        <v>0.005500303970544891</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002158851975763098</v>
+        <v>0.002102540176373066</v>
       </c>
       <c r="W12" t="n">
-        <v>0.006742960275488781</v>
+        <v>0.007123502943990877</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001088332124438015</v>
+        <v>0.001098906384636875</v>
       </c>
     </row>
     <row r="13">
@@ -1468,46 +1468,46 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1372751297687382</v>
+        <v>0.148515007205576</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2040438602813413</v>
+        <v>0.2205669081358906</v>
       </c>
       <c r="M13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.284045086843435</v>
       </c>
       <c r="N13" t="n">
-        <v>4.288853823356991</v>
+        <v>4.51367414491185</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002070333635343385</v>
+        <v>0.002134332250830006</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001548257924604003</v>
+        <v>0.001761806068326073</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001788415593556834</v>
+        <v>0.001834052754278803</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008564989820917994</v>
+        <v>0.00867864905336191</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01468393403953337</v>
+        <v>0.01479978519774553</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01688580440152492</v>
+        <v>0.01662959998050208</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04377804440347326</v>
+        <v>0.04277330469049109</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01480013199956822</v>
+        <v>0.01475224373249821</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02369535262986185</v>
+        <v>0.02333877682440299</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03951863670846618</v>
+        <v>0.03966562280682006</v>
       </c>
     </row>
     <row r="14">
@@ -1548,46 +1548,46 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.171587651340829</v>
+        <v>0.1727584722120463</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2983055854264955</v>
+        <v>0.2990582685016128</v>
       </c>
       <c r="M14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.415219190537966</v>
       </c>
       <c r="N14" t="n">
-        <v>4.324467288337289</v>
+        <v>4.362336425507728</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01118045747215313</v>
+        <v>0.01125534832037346</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003576037155758639</v>
+        <v>0.003607630656927784</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01805958154930947</v>
+        <v>0.01788996516652828</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007206068225221823</v>
+        <v>0.007182597802538842</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01118408283261425</v>
+        <v>0.01121561652147218</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02919818386706022</v>
+        <v>0.02923068112280584</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02162193028564661</v>
+        <v>0.02182599392278025</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0638628616596976</v>
+        <v>0.06322226242153146</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01443722271508459</v>
+        <v>0.01494646419532208</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03023289054123882</v>
+        <v>0.03039923048985699</v>
       </c>
     </row>
     <row r="15">
@@ -1628,46 +1628,46 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1960420645582539</v>
+        <v>0.1895470751595914</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2990856874988774</v>
+        <v>0.29369105404012</v>
       </c>
       <c r="M15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.12729937470144</v>
       </c>
       <c r="N15" t="n">
-        <v>4.326262142333204</v>
+        <v>4.251286225585371</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01157950717120407</v>
+        <v>0.01153787057806632</v>
       </c>
       <c r="P15" t="n">
-        <v>0.005056192323717964</v>
+        <v>0.00491396510312218</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01719251018215374</v>
+        <v>0.01714618352170721</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005920894139844743</v>
+        <v>0.005813051837501348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02628539795579034</v>
+        <v>0.02602301365812578</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03027207836833962</v>
+        <v>0.03008980968168116</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01434813060341132</v>
+        <v>0.01420621379998798</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06161037557882532</v>
+        <v>0.06147698604334072</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01258728668543796</v>
+        <v>0.01289384432520191</v>
       </c>
       <c r="X15" t="n">
-        <v>0.09370311976534683</v>
+        <v>0.0922494979583097</v>
       </c>
     </row>
     <row r="16">
@@ -1708,46 +1708,46 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5421174973423735</v>
+        <v>0.5109637156163565</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5410870433101997</v>
+        <v>0.5248228053291905</v>
       </c>
       <c r="M16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.305324632016705</v>
       </c>
       <c r="N16" t="n">
-        <v>4.712048845873904</v>
+        <v>4.499578138446319</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02866328612717311</v>
+        <v>0.02795977037058923</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0206601656487206</v>
+        <v>0.01973319386874771</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2656266252036891</v>
+        <v>0.2494908810873907</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01352176138581163</v>
+        <v>0.01289464404103659</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0251381516298808</v>
+        <v>0.03895640810840645</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08556330799087607</v>
+        <v>0.08300044579389146</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04389252388459687</v>
+        <v>0.03064668158106581</v>
       </c>
       <c r="V16" t="n">
-        <v>2.208044904685567</v>
+        <v>14.77209280393934</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02277970894122609</v>
+        <v>0.05918381767874265</v>
       </c>
       <c r="X16" t="n">
-        <v>3.835534457457514</v>
+        <v>62.19966838387636</v>
       </c>
     </row>
     <row r="17">
@@ -1788,46 +1788,46 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1403488321675085</v>
+        <v>0.1374919669067439</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2395779401355477</v>
+        <v>0.2308473659312212</v>
       </c>
       <c r="M17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.873370159099386</v>
       </c>
       <c r="N17" t="n">
-        <v>4.197727316697493</v>
+        <v>4.005862584706665</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01275131387502834</v>
+        <v>0.01274779713484942</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001267279528570365</v>
+        <v>0.001087304268477051</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01371282455240211</v>
+        <v>0.0135142453541742</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003978140285908051</v>
+        <v>0.003854742165844369</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01044284115639254</v>
+        <v>0.01038510830637266</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03368303973063491</v>
+        <v>0.03437143974099936</v>
       </c>
       <c r="U17" t="n">
-        <v>0.04185229911678633</v>
+        <v>0.04661198334546052</v>
       </c>
       <c r="V17" t="n">
-        <v>0.04551487203059584</v>
+        <v>0.04457607386191233</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0218127605569962</v>
+        <v>0.02445355547810242</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02225143678805712</v>
+        <v>0.02261828801005894</v>
       </c>
     </row>
     <row r="18">
@@ -1868,46 +1868,46 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2393672981629223</v>
+        <v>0.24258952682581</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2628081312818585</v>
+        <v>0.2660266826871621</v>
       </c>
       <c r="M18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.300562681691318</v>
       </c>
       <c r="N18" t="n">
-        <v>4.25088271316103</v>
+        <v>4.300495078191944</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01319992004729003</v>
+        <v>0.0132376709096335</v>
       </c>
       <c r="P18" t="n">
-        <v>0.006728754323315997</v>
+        <v>0.00681129232931395</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01170224384500646</v>
+        <v>0.01171949635204929</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008428035761379779</v>
+        <v>0.00849322490141575</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008798279283511594</v>
+        <v>0.008848764120452022</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03407483992074226</v>
+        <v>0.03396721605044127</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01548000663660184</v>
+        <v>0.01541847042973249</v>
       </c>
       <c r="V18" t="n">
-        <v>0.03666003053022078</v>
+        <v>0.03681490085125969</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01432588512901706</v>
+        <v>0.01494770064066304</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01557934607447598</v>
+        <v>0.01553792814555296</v>
       </c>
     </row>
     <row r="19">
@@ -1948,46 +1948,46 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1872651872905624</v>
+        <v>0.1618647634163979</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2401937752238114</v>
+        <v>0.2267943694544231</v>
       </c>
       <c r="M19" t="n">
-        <v>4.597747250805167</v>
+        <v>4.01013022703957</v>
       </c>
       <c r="N19" t="n">
-        <v>4.655565571231425</v>
+        <v>4.381077920595329</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004960445033678655</v>
+        <v>0.004872206345465319</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01009503217597352</v>
+        <v>0.009584503966047387</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.005692714731710508</v>
+        <v>0.00567637946513994</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001557559596239036</v>
+        <v>0.001511907495789723</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03219939774238828</v>
+        <v>0.03178593550258741</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01930544268811069</v>
+        <v>0.01913960821570984</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02422871794239524</v>
+        <v>0.02404432928852039</v>
       </c>
       <c r="V19" t="n">
-        <v>0.01847620733257224</v>
+        <v>0.01841223697550069</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006752582281590081</v>
+        <v>0.006863433741323773</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1611588900177265</v>
+        <v>0.1605060758022008</v>
       </c>
     </row>
     <row r="20">
@@ -2028,46 +2028,46 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2655681489740055</v>
+        <v>0.270337140109575</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3008990122974649</v>
+        <v>0.3065526125294156</v>
       </c>
       <c r="M20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.622332151259288</v>
       </c>
       <c r="N20" t="n">
-        <v>4.510584265198912</v>
+        <v>4.58922304767674</v>
       </c>
       <c r="O20" t="n">
-        <v>0.007777518769539154</v>
+        <v>0.00785931586429609</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0008440332892536504</v>
+        <v>0.001025000800824494</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.009811782301937936</v>
+        <v>0.009860404575518641</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00544843227081606</v>
+        <v>0.005480568839047294</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01546097434560976</v>
+        <v>0.01578174284774004</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0204744598549283</v>
+        <v>0.02039597948269816</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01588734943804225</v>
+        <v>0.01580429778794902</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03089100697323576</v>
+        <v>0.03100472001297187</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0110821423433777</v>
+        <v>0.01141743107428418</v>
       </c>
       <c r="X20" t="n">
-        <v>0.03076829762206538</v>
+        <v>0.03092722591672567</v>
       </c>
     </row>
     <row r="21">
@@ -2108,46 +2108,46 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1248690725745343</v>
+        <v>0.1205682193591666</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1430950761200596</v>
+        <v>0.1423733601157885</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.116445283604787</v>
       </c>
       <c r="N21" t="n">
-        <v>4.339705353093607</v>
+        <v>4.12095334053991</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01570255775811887</v>
+        <v>0.01478801104066373</v>
       </c>
       <c r="P21" t="n">
-        <v>0.05259007364202014</v>
+        <v>0.04991584459655532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.006436928753078647</v>
+        <v>0.006895745083284601</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000001674e-05</v>
+        <v>1.000000000000209e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000002724e-05</v>
+        <v>1.00000000000495e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05602463563376646</v>
+        <v>0.05290185517907468</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1679447969534848</v>
+        <v>0.1596640232419171</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02304428324316529</v>
+        <v>0.02511739227185156</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01081746027102802</v>
+        <v>0.0112216396004246</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03738595409513938</v>
+        <v>0.03925832733083881</v>
       </c>
     </row>
     <row r="22">
@@ -2188,46 +2188,46 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2789552405431617</v>
+        <v>0.2807614585076638</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3267936778505216</v>
+        <v>0.3240124900058231</v>
       </c>
       <c r="M22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.13956210274015</v>
       </c>
       <c r="N22" t="n">
-        <v>4.394735300209087</v>
+        <v>4.310404336206148</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005758840952179562</v>
+        <v>0.00571654877721342</v>
       </c>
       <c r="P22" t="n">
-        <v>1.000000000000004e-05</v>
+        <v>1.00000228731639e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.006916655671479154</v>
+        <v>0.006856071904564442</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003441929677658579</v>
+        <v>0.003427287695314076</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01269747146421901</v>
+        <v>0.0126438157668045</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01626978088595468</v>
+        <v>0.01594674238280221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01851903092582424</v>
+        <v>0.01521096615998836</v>
       </c>
       <c r="V22" t="n">
-        <v>0.02713481235997965</v>
+        <v>0.02671265268570759</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01009181597633801</v>
+        <v>0.009394481557100728</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02924490353599254</v>
+        <v>0.02780094666908808</v>
       </c>
     </row>
     <row r="23">
@@ -2268,46 +2268,46 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2148383705391921</v>
+        <v>0.2125758680225998</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2765021139724618</v>
+        <v>0.2730812615444278</v>
       </c>
       <c r="M23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.85839694517567</v>
       </c>
       <c r="N23" t="n">
-        <v>4.197990968516907</v>
+        <v>4.109303918133452</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01073857269976681</v>
+        <v>0.01072659083934483</v>
       </c>
       <c r="P23" t="n">
-        <v>0.00437629329803946</v>
+        <v>0.004300359945717686</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.008987555053419262</v>
+        <v>0.008953973906172932</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006294949567480787</v>
+        <v>0.006185063060610859</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02459551784806006</v>
+        <v>0.02443520304292202</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0276646870654188</v>
+        <v>0.02759364091948696</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01884771027252581</v>
+        <v>0.01924557130798039</v>
       </c>
       <c r="V23" t="n">
-        <v>0.02985878395591712</v>
+        <v>0.02987848763398218</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01494583871121341</v>
+        <v>0.01567491900785745</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07762413058504257</v>
+        <v>0.07694288199533526</v>
       </c>
     </row>
     <row r="24">
@@ -2348,46 +2348,46 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3751494643248936</v>
+        <v>0.3899491530645845</v>
       </c>
       <c r="L24" t="n">
-        <v>0.443079613465554</v>
+        <v>0.4738363484336767</v>
       </c>
       <c r="M24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.330915049849626</v>
       </c>
       <c r="N24" t="n">
-        <v>4.128611849288868</v>
+        <v>4.386143874223134</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01238854176564995</v>
+        <v>0.01270831934923817</v>
       </c>
       <c r="P24" t="n">
-        <v>0.008841541137283542</v>
+        <v>0.009365876712975773</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.08777259161739923</v>
+        <v>0.09201728505651084</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01255698868128798</v>
+        <v>0.01374423130417479</v>
       </c>
       <c r="S24" t="n">
-        <v>1.000000000245826e-05</v>
+        <v>1.000000000093162e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03592754243097236</v>
+        <v>0.03005267218255816</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03410402988375306</v>
+        <v>0.0174588122687918</v>
       </c>
       <c r="V24" t="n">
-        <v>0.512866892267799</v>
+        <v>0.957382973086685</v>
       </c>
       <c r="W24" t="n">
-        <v>0.05905344274766579</v>
+        <v>0.022327840589088</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4944390402589408</v>
+        <v>1.070619086120369</v>
       </c>
     </row>
     <row r="25">
@@ -2428,46 +2428,46 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2172140991091026</v>
+        <v>0.2158934749426978</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2292169313163831</v>
+        <v>0.2288212176259103</v>
       </c>
       <c r="M25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.311008836928643</v>
       </c>
       <c r="N25" t="n">
-        <v>4.343876813371136</v>
+        <v>4.340698822330908</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002219793808708978</v>
+        <v>0.002227050793343374</v>
       </c>
       <c r="P25" t="n">
-        <v>1.000000000000617e-05</v>
+        <v>1.000000000000249e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0009293363736647648</v>
+        <v>0.0009272596949026803</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003330972160887703</v>
+        <v>0.0003337747272566673</v>
       </c>
       <c r="S25" t="n">
-        <v>9.962044722758846e-05</v>
+        <v>9.830293358068274e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005451917333700039</v>
+        <v>0.005445970633114964</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002865337270466939</v>
+        <v>0.002891211546329953</v>
       </c>
       <c r="V25" t="n">
-        <v>0.003147064446687676</v>
+        <v>0.003144059723205296</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001298935182329354</v>
+        <v>0.001343883601891845</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001332910237608775</v>
+        <v>0.001314232368928139</v>
       </c>
     </row>
     <row r="26">
@@ -2508,46 +2508,46 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3294247814180385</v>
+        <v>0.319605401855295</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3143376648895922</v>
+        <v>0.3067566003139182</v>
       </c>
       <c r="M26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.221808346553291</v>
       </c>
       <c r="N26" t="n">
-        <v>4.389042027517038</v>
+        <v>4.299252264058017</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002887495765738182</v>
+        <v>0.002895729894423425</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001589666725173933</v>
+        <v>0.001540869741159283</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001553539000285109</v>
+        <v>0.001530688559659498</v>
       </c>
       <c r="R26" t="n">
-        <v>0.000572973530735055</v>
+        <v>0.0005610067201126984</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003294165476834455</v>
+        <v>0.000320505036665777</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005810585408081373</v>
+        <v>0.005815480477789379</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002425521696126876</v>
+        <v>0.002436834387079412</v>
       </c>
       <c r="V26" t="n">
-        <v>0.005179008627373535</v>
+        <v>0.005128512473180752</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001440257242922153</v>
+        <v>0.001509443271880516</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001287815870506555</v>
+        <v>0.001258773084795716</v>
       </c>
     </row>
     <row r="27">
@@ -2588,46 +2588,46 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2426473726089903</v>
+        <v>0.2452896402637705</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3115247044527188</v>
+        <v>0.3103151281310915</v>
       </c>
       <c r="M27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.171003209011483</v>
       </c>
       <c r="N27" t="n">
-        <v>4.155593983175509</v>
+        <v>4.14908671879705</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001434517542254398</v>
+        <v>0.001437276480514978</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005801979261219694</v>
+        <v>0.0005765645320171647</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00285155607046689</v>
+        <v>0.002832226853502619</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006473910416905309</v>
+        <v>0.0006441285626390565</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007215997917366378</v>
+        <v>0.000723606562769694</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003452441654540115</v>
+        <v>0.003444973016160398</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002355620452512151</v>
+        <v>0.002439560836847509</v>
       </c>
       <c r="V27" t="n">
-        <v>0.009081022649112577</v>
+        <v>0.009038235150673847</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001622379621253287</v>
+        <v>0.00172238019203396</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001823198898110183</v>
+        <v>0.001795122101848619</v>
       </c>
     </row>
     <row r="28">
@@ -2668,46 +2668,46 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4028027310904022</v>
+        <v>0.3983434145777525</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3914469935810257</v>
+        <v>0.4053307112609433</v>
       </c>
       <c r="M28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.109024811393252</v>
       </c>
       <c r="N28" t="n">
-        <v>4.170257650412323</v>
+        <v>4.291467493787325</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002116552966053097</v>
+        <v>0.002072957554302384</v>
       </c>
       <c r="P28" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.005724042804272113</v>
+        <v>0.005863184085985075</v>
       </c>
       <c r="R28" t="n">
-        <v>0.004772242121867223</v>
+        <v>0.004994582163527573</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01039405915627132</v>
+        <v>0.0103342467062638</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004859157402850147</v>
+        <v>0.004751802764048289</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01105264547599418</v>
+        <v>0.01082368026150989</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0183522318256768</v>
+        <v>0.01889566661618548</v>
       </c>
       <c r="W28" t="n">
-        <v>0.008649377507351213</v>
+        <v>0.009508319048192264</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02395980099542723</v>
+        <v>0.02337550559569725</v>
       </c>
     </row>
     <row r="29">
@@ -2748,46 +2748,46 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.512131704883432</v>
+        <v>0.5340055862294603</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3414605716300541</v>
+        <v>0.3537511708827761</v>
       </c>
       <c r="M29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.257333241600258</v>
       </c>
       <c r="N29" t="n">
-        <v>4.104778950333008</v>
+        <v>4.213034118342315</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004749727595907296</v>
+        <v>0.004706119344066876</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01827108221212901</v>
+        <v>0.01781406183477655</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0008088553130563692</v>
+        <v>0.001112501966933918</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01575150272490811</v>
+        <v>0.01718721293510463</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009460333641577598</v>
+        <v>0.009435734175553634</v>
       </c>
       <c r="T29" t="n">
-        <v>0.009241235140625652</v>
+        <v>0.008991775749481973</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06653550199698265</v>
+        <v>0.06048863068591687</v>
       </c>
       <c r="V29" t="n">
-        <v>0.008944524714289991</v>
+        <v>0.009328677827489671</v>
       </c>
       <c r="W29" t="n">
-        <v>0.02759469022616411</v>
+        <v>0.03271838197794723</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01677532477169065</v>
+        <v>0.01595010890889274</v>
       </c>
     </row>
     <row r="30">
@@ -2828,46 +2828,46 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4711354159409922</v>
+        <v>0.4943630247919256</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3865708863048746</v>
+        <v>0.4068925873055509</v>
       </c>
       <c r="M30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.508966688135797</v>
       </c>
       <c r="N30" t="n">
-        <v>4.107585956081562</v>
+        <v>4.315230370276968</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002561591806002798</v>
+        <v>0.002582538463188679</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004784422287435638</v>
+        <v>0.005210999333369798</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.001492035711290681</v>
+        <v>0.00178291325763776</v>
       </c>
       <c r="R30" t="n">
-        <v>0.008852537621161005</v>
+        <v>0.009395269430449356</v>
       </c>
       <c r="S30" t="n">
-        <v>0.003981862152706922</v>
+        <v>0.00423607094647921</v>
       </c>
       <c r="T30" t="n">
-        <v>0.00497692675356526</v>
+        <v>0.004948356639668149</v>
       </c>
       <c r="U30" t="n">
-        <v>0.008768190809158822</v>
+        <v>0.009468897455161546</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01373739081390746</v>
+        <v>0.01415929849040101</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01406555619279511</v>
+        <v>0.01535040043333628</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005531148619148522</v>
+        <v>0.005622001961398414</v>
       </c>
     </row>
     <row r="31">
@@ -2908,46 +2908,46 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5036033975236921</v>
+        <v>0.4901448304506785</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4306682808414808</v>
+        <v>0.4307997022511386</v>
       </c>
       <c r="M31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.249026147841872</v>
       </c>
       <c r="N31" t="n">
-        <v>4.404981860948973</v>
+        <v>4.408930889587362</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002798849442774158</v>
+        <v>0.002771812191914096</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00741180139247395</v>
+        <v>0.007349276814842575</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.001605395959368419</v>
+        <v>0.001566470648079969</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001819078228691201</v>
+        <v>0.001811076871221427</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005988105918276117</v>
+        <v>0.0005777036260591665</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0050981964794766</v>
+        <v>0.005009747952420827</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01740292567692638</v>
+        <v>0.01717453529252223</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01289208522845007</v>
+        <v>0.01294604338786009</v>
       </c>
       <c r="W31" t="n">
-        <v>0.00280990044964147</v>
+        <v>0.002981214292240811</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002878936051915373</v>
+        <v>0.002777060325854031</v>
       </c>
     </row>
     <row r="32">
@@ -2988,46 +2988,46 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4586807473470598</v>
+        <v>0.5003028185540506</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3967614517414144</v>
+        <v>0.4274257323699956</v>
       </c>
       <c r="M32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.530139452862152</v>
       </c>
       <c r="N32" t="n">
-        <v>4.108327589059241</v>
+        <v>4.426366733301174</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008145747668686942</v>
+        <v>0.0008333218414156414</v>
       </c>
       <c r="P32" t="n">
-        <v>0.004975909875013858</v>
+        <v>0.005242317589998033</v>
       </c>
       <c r="Q32" t="n">
         <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004152374550974437</v>
+        <v>0.00440900614646704</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001306713274232407</v>
+        <v>0.00139890869216171</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00280228753309128</v>
+        <v>0.002812879990652049</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01097134569689242</v>
+        <v>0.01135121579130941</v>
       </c>
       <c r="V32" t="n">
-        <v>0.01152117656041309</v>
+        <v>0.0112527633064123</v>
       </c>
       <c r="W32" t="n">
-        <v>0.007412352558769223</v>
+        <v>0.008038982106448744</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003588661914460989</v>
+        <v>0.003574017750836421</v>
       </c>
     </row>
     <row r="33">
@@ -3066,46 +3066,46 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2751054178962024</v>
+        <v>0.2845720576653915</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2953870234060791</v>
+        <v>0.3094853665471586</v>
       </c>
       <c r="M33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.300519149462805</v>
       </c>
       <c r="N33" t="n">
-        <v>4.148002708443999</v>
+        <v>4.268789356988536</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006567028913609717</v>
+        <v>0.006459786430733619</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00360597802992074</v>
+        <v>0.00399209826014126</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.008351724604685055</v>
+        <v>0.008740491515353622</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007034452409027506</v>
+        <v>0.00740634246084285</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003955940643477558</v>
+        <v>0.004069966116854634</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0180882711833539</v>
+        <v>0.01754609504531611</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02431814029811672</v>
+        <v>0.02441502329541632</v>
       </c>
       <c r="V33" t="n">
-        <v>0.03139563926596872</v>
+        <v>0.03359882083314529</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01284279270198474</v>
+        <v>0.01425906458768727</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007697065051923854</v>
+        <v>0.007911558518548282</v>
       </c>
     </row>
     <row r="34">
@@ -3146,46 +3146,46 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5165578838213738</v>
+        <v>0.5337173211659239</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4379218360464911</v>
+        <v>0.4594789794307157</v>
       </c>
       <c r="M34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.254011730907492</v>
       </c>
       <c r="N34" t="n">
-        <v>4.126735953238143</v>
+        <v>4.290063054664384</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005311926735983131</v>
+        <v>0.005293537958390806</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01384651328288907</v>
+        <v>0.01449325049678961</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.01930244324766697</v>
+        <v>0.02173365729682402</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0134165945420735</v>
+        <v>0.01405915792835894</v>
       </c>
       <c r="S34" t="n">
-        <v>0.007687172077502751</v>
+        <v>0.008223738851225243</v>
       </c>
       <c r="T34" t="n">
-        <v>0.007940095410271481</v>
+        <v>0.007883139557382282</v>
       </c>
       <c r="U34" t="n">
-        <v>0.05099722408447282</v>
+        <v>0.05427348058791771</v>
       </c>
       <c r="V34" t="n">
-        <v>0.074305016010406</v>
+        <v>0.08259749265859682</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01609682777477259</v>
+        <v>0.01769669622720369</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00694867368390586</v>
+        <v>0.00716031978545314</v>
       </c>
     </row>
     <row r="35">
@@ -3226,46 +3226,46 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3001566209783726</v>
+        <v>0.3017567405934108</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2366836831230797</v>
+        <v>0.2446039175795452</v>
       </c>
       <c r="M35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.047146068348874</v>
       </c>
       <c r="N35" t="n">
-        <v>4.028731431290875</v>
+        <v>4.156055410298507</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002580632758255691</v>
+        <v>0.002591332400424746</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0582950288538906</v>
+        <v>0.05839057765869057</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.001151903512550638</v>
+        <v>0.001164952168749607</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004608721419558584</v>
+        <v>0.004759437049525006</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009339211527331631</v>
+        <v>0.0009506602365975521</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01219000840003935</v>
+        <v>0.01243090473175927</v>
       </c>
       <c r="U35" t="n">
-        <v>25.53062052147693</v>
+        <v>26.22187932220613</v>
       </c>
       <c r="V35" t="n">
-        <v>0.006662591495784272</v>
+        <v>0.006920718809434856</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02034792175537868</v>
+        <v>0.0224981326684356</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002593931459411908</v>
+        <v>0.002626807572345213</v>
       </c>
     </row>
     <row r="36">
@@ -3306,46 +3306,46 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4200622561347667</v>
+        <v>0.4303510992459229</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3831339757680553</v>
+        <v>0.3939800805864314</v>
       </c>
       <c r="M36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.305403694774172</v>
       </c>
       <c r="N36" t="n">
-        <v>4.208616430795051</v>
+        <v>4.32080620179621</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001344955357074</v>
+        <v>0.001354609422965776</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002691112226113858</v>
+        <v>0.002766124108187839</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.001557227765884963</v>
+        <v>0.001606529954626481</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001874592729878768</v>
+        <v>0.00193283348767519</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001275715523840283</v>
+        <v>0.001309712328047509</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003584292444817782</v>
+        <v>0.00357449806879154</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006131571523605946</v>
+        <v>0.006171265407889702</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01068435951215018</v>
+        <v>0.01083814594914742</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003402089363094501</v>
+        <v>0.00360372821623126</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004577248161048739</v>
+        <v>0.004516753479447161</v>
       </c>
     </row>
     <row r="37">
@@ -3386,46 +3386,46 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1057540787127461</v>
+        <v>0.1033156315000568</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1089880675011074</v>
+        <v>0.1059828642371518</v>
       </c>
       <c r="M37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.2322895226395</v>
       </c>
       <c r="N37" t="n">
-        <v>4.362925574838995</v>
+        <v>4.263470541648745</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007574842705621827</v>
+        <v>0.007601944601201592</v>
       </c>
       <c r="P37" t="n">
-        <v>0.00340545300474077</v>
+        <v>0.003361003954592212</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001420068709220617</v>
+        <v>0.001413775568260181</v>
       </c>
       <c r="R37" t="n">
-        <v>0.000852371989892978</v>
+        <v>0.000843397419013481</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002298580066037795</v>
+        <v>0.002269007126178266</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02824265799343905</v>
+        <v>0.02835794664986396</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009420730655618055</v>
+        <v>0.009377544212304727</v>
       </c>
       <c r="V37" t="n">
-        <v>0.004417315584377717</v>
+        <v>0.004401015687790313</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002533251101958504</v>
+        <v>0.002560594535593874</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005823911038394572</v>
+        <v>0.005732714442660184</v>
       </c>
     </row>
     <row r="38">
@@ -3466,46 +3466,46 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1483762115382365</v>
+        <v>0.1414949912042679</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1137185800671764</v>
+        <v>0.1087290221050649</v>
       </c>
       <c r="M38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.109497407226164</v>
       </c>
       <c r="N38" t="n">
-        <v>4.35445625892701</v>
+        <v>4.195576882556786</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009407666335364762</v>
+        <v>0.009466158791810689</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002622085536061277</v>
+        <v>0.002600888321473296</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0008620406003334903</v>
+        <v>0.0008554167754102429</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004790756672375326</v>
+        <v>0.0004639389345015955</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0004439509816230622</v>
+        <v>0.0003912853955704609</v>
       </c>
       <c r="T38" t="n">
-        <v>0.03156730409103652</v>
+        <v>0.03180668575211528</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009224052250673333</v>
+        <v>0.009225924844419304</v>
       </c>
       <c r="V38" t="n">
-        <v>0.003396997548965482</v>
+        <v>0.003383070468159375</v>
       </c>
       <c r="W38" t="n">
-        <v>0.0020992891228714</v>
+        <v>0.002123099521003483</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003206482737564038</v>
+        <v>0.003150037007840459</v>
       </c>
     </row>
     <row r="39">
@@ -3546,46 +3546,46 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1491847814540822</v>
+        <v>0.1514588065490762</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1316597533177679</v>
+        <v>0.1342305756371794</v>
       </c>
       <c r="M39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.258033543989585</v>
       </c>
       <c r="N39" t="n">
-        <v>4.188971928840091</v>
+        <v>4.266426390932311</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006459211668263568</v>
+        <v>0.006470581946873035</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002000854841993216</v>
+        <v>0.002042234687859863</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001426041890109345</v>
+        <v>0.001427725333833631</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002312068017019901</v>
+        <v>0.002326252982001576</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001416128843862737</v>
+        <v>0.001422625470839602</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01697621561715183</v>
+        <v>0.01696030028570612</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009743220078990313</v>
+        <v>0.009743853811556683</v>
       </c>
       <c r="V39" t="n">
-        <v>0.004191952944577803</v>
+        <v>0.004199213581852069</v>
       </c>
       <c r="W39" t="n">
-        <v>0.003954059222525886</v>
+        <v>0.004036201977016299</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003037101273468859</v>
+        <v>0.003023760583938646</v>
       </c>
     </row>
     <row r="40">
@@ -3626,46 +3626,46 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2411411590284251</v>
+        <v>0.2387698264019981</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4036821281927297</v>
+        <v>0.3956825352388806</v>
       </c>
       <c r="M40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.328495843657492</v>
       </c>
       <c r="N40" t="n">
-        <v>4.621231606751769</v>
+        <v>4.521598307569784</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004169130819236093</v>
+        <v>0.004141366185699709</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002715917127084151</v>
+        <v>0.002630245184229858</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.008544858737746651</v>
+        <v>0.008507641359775022</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002482626858512609</v>
+        <v>0.002450527941873048</v>
       </c>
       <c r="S40" t="n">
-        <v>0.05546003792158938</v>
+        <v>0.05435511079335989</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008261946401277427</v>
+        <v>0.008166940448019633</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004393947183935877</v>
+        <v>0.004233563662852916</v>
       </c>
       <c r="V40" t="n">
-        <v>0.02793677391455169</v>
+        <v>0.0277448184869841</v>
       </c>
       <c r="W40" t="n">
-        <v>0.003605539211909978</v>
+        <v>0.003730238184086705</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2674294843029978</v>
+        <v>0.2590994290714659</v>
       </c>
     </row>
     <row r="41">
@@ -3706,46 +3706,46 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2672649319402196</v>
+        <v>0.2578829215911677</v>
       </c>
       <c r="L41" t="n">
-        <v>0.293671168335245</v>
+        <v>0.2872888548942679</v>
       </c>
       <c r="M41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.435301806859223</v>
       </c>
       <c r="N41" t="n">
-        <v>4.614030833203471</v>
+        <v>4.505865362691527</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001901213821742523</v>
+        <v>0.001885877375446798</v>
       </c>
       <c r="P41" t="n">
-        <v>0.00318396852955482</v>
+        <v>0.003090226968247373</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.002023274199691214</v>
+        <v>0.002032213311689036</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009699489710165681</v>
+        <v>0.0009525834802123272</v>
       </c>
       <c r="S41" t="n">
-        <v>0.004001682603587061</v>
+        <v>0.00394716397471301</v>
       </c>
       <c r="T41" t="n">
-        <v>0.004776617305307966</v>
+        <v>0.004721541871466996</v>
       </c>
       <c r="U41" t="n">
-        <v>0.005275071944466012</v>
+        <v>0.00524317454898725</v>
       </c>
       <c r="V41" t="n">
-        <v>0.005934651068417836</v>
+        <v>0.00595275449814794</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002097069930144371</v>
+        <v>0.00214361476577934</v>
       </c>
       <c r="X41" t="n">
-        <v>0.007103575528681633</v>
+        <v>0.006966234404942577</v>
       </c>
     </row>
     <row r="42">
@@ -3786,46 +3786,46 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1903469762152839</v>
+        <v>0.277385678721059</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4351362377117415</v>
+        <v>0.4383678837373725</v>
       </c>
       <c r="M42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.541320208590085</v>
       </c>
       <c r="N42" t="n">
-        <v>4.609880042753449</v>
+        <v>4.559186423294103</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004826576978193675</v>
+        <v>0.004705710918496453</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0041125205166345</v>
+        <v>0.003876279332582651</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01806584629286574</v>
+        <v>0.01857064230759505</v>
       </c>
       <c r="R42" t="n">
-        <v>0.00308079496543708</v>
+        <v>0.003052553016029436</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1772500932400848</v>
+        <v>1e-05</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01267041034724376</v>
+        <v>0.01259720908775944</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03046212008459008</v>
+        <v>0.009059050116525634</v>
       </c>
       <c r="V42" t="n">
-        <v>0.08118148357040231</v>
+        <v>0.08843077978423618</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01076785433571017</v>
+        <v>0.006262541837585448</v>
       </c>
       <c r="X42" t="n">
-        <v>246.2032079498098</v>
+        <v>0.5431002981913414</v>
       </c>
     </row>
     <row r="43">
@@ -3866,46 +3866,46 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1504728716669206</v>
+        <v>0.1503222139950792</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3659740790743728</v>
+        <v>0.3686132989106535</v>
       </c>
       <c r="M43" t="n">
-        <v>4.103051778684014</v>
+        <v>4.014610252289849</v>
       </c>
       <c r="N43" t="n">
-        <v>4.243188846182056</v>
+        <v>4.251204890422223</v>
       </c>
       <c r="O43" t="n">
-        <v>0.02410559859659311</v>
+        <v>0.02407732618856541</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0135463821910682</v>
+        <v>0.01359415067763194</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.05854643426733767</v>
+        <v>0.05916084326513653</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02174688863692746</v>
+        <v>0.02190333776307291</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06092494125012646</v>
+        <v>0.06097075169211408</v>
       </c>
       <c r="T43" t="n">
-        <v>0.05914107651324824</v>
+        <v>0.05850073955802389</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02049153793753907</v>
+        <v>0.02077956282061677</v>
       </c>
       <c r="V43" t="n">
-        <v>0.2280578623989022</v>
+        <v>0.2311450064487306</v>
       </c>
       <c r="W43" t="n">
-        <v>0.03540566759573611</v>
+        <v>0.03758231622513954</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1653387722830078</v>
+        <v>0.1655365740693592</v>
       </c>
     </row>
     <row r="44">
@@ -3946,46 +3946,46 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1778728783246155</v>
+        <v>0.1750004298657557</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3417554746072173</v>
+        <v>0.3277841145113169</v>
       </c>
       <c r="M44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.26677501303533</v>
       </c>
       <c r="N44" t="n">
-        <v>4.578600905246178</v>
+        <v>4.388906099140782</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05443596516439162</v>
+        <v>0.05523841796833086</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02297314781289453</v>
+        <v>0.02242912332517252</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04194219028726407</v>
+        <v>0.04130001213799385</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01162191152425748</v>
+        <v>0.01124542818330652</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02317842407887171</v>
+        <v>0.02245171420635166</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1620267699442295</v>
+        <v>0.1662677252229182</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0410422461771248</v>
+        <v>0.04069814013028705</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1524490191178978</v>
+        <v>0.1496235450402074</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0216345026323616</v>
+        <v>0.02142311010372736</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04804823095673413</v>
+        <v>0.04611776250969853</v>
       </c>
     </row>
     <row r="45">
@@ -4026,46 +4026,46 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.399617491041528</v>
+        <v>0.3970700662958236</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3251834590783698</v>
+        <v>0.3269920361240056</v>
       </c>
       <c r="M45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.224020019874794</v>
       </c>
       <c r="N45" t="n">
-        <v>4.340743054981425</v>
+        <v>4.376588707455891</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1181144792302148</v>
+        <v>0.1183172323013069</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1286763265756729</v>
+        <v>0.1290516876741385</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1520905991227159</v>
+        <v>0.151567191082598</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09418008263790811</v>
+        <v>0.09413662262835801</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1134692834865529</v>
+        <v>0.1138836702494154</v>
       </c>
       <c r="T45" t="n">
-        <v>0.5471197296089135</v>
+        <v>0.5422051448390474</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4155882440051387</v>
+        <v>0.4101037140660773</v>
       </c>
       <c r="V45" t="n">
-        <v>1.106116322134769</v>
+        <v>1.106649450776112</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2573781712494533</v>
+        <v>0.2716016590243724</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4452393673761411</v>
+        <v>0.4490887177443214</v>
       </c>
     </row>
     <row r="46">
@@ -4106,46 +4106,46 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4729359869420497</v>
+        <v>0.4191548341898909</v>
       </c>
       <c r="L46" t="n">
-        <v>0.430517839718132</v>
+        <v>0.4168528808457668</v>
       </c>
       <c r="M46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.769550246054656</v>
       </c>
       <c r="N46" t="n">
-        <v>4.57589401428416</v>
+        <v>4.479216138634888</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06817862861588646</v>
+        <v>0.06815244606365466</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04522173852542566</v>
+        <v>0.04363101644153401</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1205687517904313</v>
+        <v>0.1115269200480784</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03737947207785126</v>
+        <v>0.03506941055577647</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1700229080552603</v>
+        <v>0.1766596998023533</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1824957641877887</v>
+        <v>0.1839301078095844</v>
       </c>
       <c r="U46" t="n">
-        <v>0.09093043520071539</v>
+        <v>0.08708392857054373</v>
       </c>
       <c r="V46" t="n">
-        <v>0.4524539810942154</v>
+        <v>0.4252814507212731</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0524505398038006</v>
+        <v>0.05383642207826184</v>
       </c>
       <c r="X46" t="n">
-        <v>1.552597388985682</v>
+        <v>1.852554806219026</v>
       </c>
     </row>
     <row r="47">
@@ -4186,46 +4186,46 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.251984504906933</v>
+        <v>0.2534470292225203</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3855702825603511</v>
+        <v>0.3811388062430823</v>
       </c>
       <c r="M47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.285238971656212</v>
       </c>
       <c r="N47" t="n">
-        <v>4.397607024679764</v>
+        <v>4.355084664189493</v>
       </c>
       <c r="O47" t="n">
-        <v>0.03710742273150507</v>
+        <v>0.03719789115727632</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01939219001244907</v>
+        <v>0.0192020824216369</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.06163246662530462</v>
+        <v>0.06126978512097164</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01814642557392724</v>
+        <v>0.01798217060741234</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02727441943986038</v>
+        <v>0.02701672834624705</v>
       </c>
       <c r="T47" t="n">
-        <v>0.09212600494953893</v>
+        <v>0.0922260101293388</v>
       </c>
       <c r="U47" t="n">
-        <v>0.0325702302720056</v>
+        <v>0.03184278833795193</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2529207691208217</v>
+        <v>0.2514649973089039</v>
       </c>
       <c r="W47" t="n">
-        <v>0.02979978874863761</v>
+        <v>0.03095129787733047</v>
       </c>
       <c r="X47" t="n">
-        <v>0.05012954965675885</v>
+        <v>0.04978584852880755</v>
       </c>
     </row>
     <row r="48">
@@ -4266,46 +4266,46 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1259930651411941</v>
+        <v>0.1132798991704734</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3934668303615036</v>
+        <v>0.3961852980358451</v>
       </c>
       <c r="M48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.703826593445649</v>
       </c>
       <c r="N48" t="n">
-        <v>4.346547468226732</v>
+        <v>4.328103045292792</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03676638341473935</v>
+        <v>0.03608141213484152</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05279473507530624</v>
+        <v>0.05217034402924473</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1155907352840377</v>
+        <v>0.1190733979486861</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03901259904355779</v>
+        <v>0.03932959554243818</v>
       </c>
       <c r="S48" t="n">
-        <v>0.3951771649220845</v>
+        <v>0.2373343859913021</v>
       </c>
       <c r="T48" t="n">
-        <v>0.1097831269549982</v>
+        <v>0.105073370176132</v>
       </c>
       <c r="U48" t="n">
-        <v>0.1204283946514029</v>
+        <v>0.115918779459669</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5743713597273182</v>
+        <v>0.5973731506809006</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08366768127789725</v>
+        <v>0.08880654171337501</v>
       </c>
       <c r="X48" t="n">
-        <v>18.68588175214583</v>
+        <v>5.873755705300761</v>
       </c>
     </row>
     <row r="49">
@@ -4346,46 +4346,46 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.310323155304724</v>
+        <v>0.3104389713261221</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4673469295047175</v>
+        <v>0.4661903841014798</v>
       </c>
       <c r="M49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.067105644874856</v>
       </c>
       <c r="N49" t="n">
-        <v>4.418201683363578</v>
+        <v>4.397535410259387</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01970632659472147</v>
+        <v>0.0195800640648723</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01191367744571463</v>
+        <v>0.01184954805723922</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1122703265392914</v>
+        <v>0.1116541917950874</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01819591017663679</v>
+        <v>0.0181838818403872</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09538080594600609</v>
+        <v>0.09474574817526989</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03874495212552505</v>
+        <v>0.03797539827685248</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01718075174901631</v>
+        <v>0.01669329196316697</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4496273210555584</v>
+        <v>0.4475239439399956</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02501049422284504</v>
+        <v>0.02679993955553984</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3340085763958589</v>
+        <v>0.3310683530183063</v>
       </c>
     </row>
     <row r="50">
@@ -4426,46 +4426,46 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5222632463286973</v>
+        <v>0.5041804397675377</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5295868492589658</v>
+        <v>0.5283724817625948</v>
       </c>
       <c r="M50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.245466267633814</v>
       </c>
       <c r="N50" t="n">
-        <v>4.633136721279348</v>
+        <v>4.524558493791908</v>
       </c>
       <c r="O50" t="n">
-        <v>0.08623673250270637</v>
+        <v>0.0870643850815126</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06995465604366134</v>
+        <v>0.06649343178727672</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4926317048348459</v>
+        <v>0.4950957030827258</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0355670102954517</v>
+        <v>0.03299544411367916</v>
       </c>
       <c r="S50" t="n">
-        <v>0.03213319719135749</v>
+        <v>0.004429056687361941</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2918243217070373</v>
+        <v>0.0002369187574658769</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1424290975962103</v>
+        <v>0.1340819236589611</v>
       </c>
       <c r="V50" t="n">
-        <v>2.318611215739077</v>
+        <v>2.297132503872639</v>
       </c>
       <c r="W50" t="n">
-        <v>0.06142855179121803</v>
+        <v>0.06795212325910853</v>
       </c>
       <c r="X50" t="n">
-        <v>0.0002810707893535721</v>
+        <v>0.2650505668175427</v>
       </c>
     </row>
     <row r="51">
@@ -4506,46 +4506,46 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3792927310630153</v>
+        <v>0.403137792451537</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4526220601744602</v>
+        <v>0.4653196877428078</v>
       </c>
       <c r="M51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.865900326542421</v>
       </c>
       <c r="N51" t="n">
-        <v>4.331893180387352</v>
+        <v>4.48384234197186</v>
       </c>
       <c r="O51" t="n">
-        <v>0.4987455810079018</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="P51" t="n">
-        <v>0.07862558577498598</v>
+        <v>0.08714068819845351</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.499999999999985</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="R51" t="n">
-        <v>0.131818942188253</v>
+        <v>0.11180265482878</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2342116646565396</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T51" t="n">
-        <v>17.86596741394894</v>
+        <v>35.70558667471899</v>
       </c>
       <c r="U51" t="n">
-        <v>0.2796427455938775</v>
+        <v>0.3389177667722044</v>
       </c>
       <c r="V51" t="n">
-        <v>5.08753902773576</v>
+        <v>6.343129710584399</v>
       </c>
       <c r="W51" t="n">
-        <v>0.6177346991579808</v>
+        <v>0.6244297718457708</v>
       </c>
       <c r="X51" t="n">
-        <v>4.238420426455792</v>
+        <v>28.98723405653553</v>
       </c>
     </row>
     <row r="52">
@@ -4586,46 +4586,46 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1593376026831239</v>
+        <v>0.1606943136811414</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3361072216961569</v>
+        <v>0.3258488121138525</v>
       </c>
       <c r="M52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.367592709598685</v>
       </c>
       <c r="N52" t="n">
-        <v>4.405228274292543</v>
+        <v>4.304345849735195</v>
       </c>
       <c r="O52" t="n">
-        <v>0.01573619811950618</v>
+        <v>0.01559011913636744</v>
       </c>
       <c r="P52" t="n">
-        <v>0.008760321494378998</v>
+        <v>0.008592507796055511</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.02702934197181239</v>
+        <v>0.02659308178128166</v>
       </c>
       <c r="R52" t="n">
-        <v>0.00616227274127964</v>
+        <v>0.005967432658001913</v>
       </c>
       <c r="S52" t="n">
-        <v>0.02075957916394475</v>
+        <v>0.01993959391141046</v>
       </c>
       <c r="T52" t="n">
-        <v>0.03711307135785095</v>
+        <v>0.03672823729495082</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01685197103721101</v>
+        <v>0.0166197342823487</v>
       </c>
       <c r="V52" t="n">
-        <v>0.08749237690084749</v>
+        <v>0.0858232788430276</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01408054423538957</v>
+        <v>0.01435306706455114</v>
       </c>
       <c r="X52" t="n">
-        <v>0.04839325330522284</v>
+        <v>0.04672440451977132</v>
       </c>
     </row>
     <row r="53">
@@ -4666,46 +4666,46 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.331297244801841</v>
+        <v>0.3301843999480364</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2205555332501337</v>
+        <v>0.2240901512487175</v>
       </c>
       <c r="M53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.38210137775019</v>
       </c>
       <c r="N53" t="n">
-        <v>4.342627665237804</v>
+        <v>4.426651157655445</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03824571372077026</v>
+        <v>0.03852063928316336</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02182707820403546</v>
+        <v>0.02203292985472621</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01664377087780608</v>
+        <v>0.01662066593722407</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02147090669262507</v>
+        <v>0.02157825212368393</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06442127984809906</v>
+        <v>0.06492062944712745</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08253961473691346</v>
+        <v>0.08361079889747045</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03760646180946092</v>
+        <v>0.03750899195664795</v>
       </c>
       <c r="V53" t="n">
-        <v>0.04211636112204025</v>
+        <v>0.04232456896730836</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03557745675335886</v>
+        <v>0.03674217385693565</v>
       </c>
       <c r="X53" t="n">
-        <v>0.0816897950879143</v>
+        <v>0.0833636015477511</v>
       </c>
     </row>
     <row r="54">
@@ -4746,46 +4746,46 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1412187048639822</v>
+        <v>0.1364187938617844</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4289553085455123</v>
+        <v>0.4114960935501225</v>
       </c>
       <c r="M54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.231856710657762</v>
       </c>
       <c r="N54" t="n">
-        <v>4.473339780082302</v>
+        <v>4.304873160013968</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02957201485327174</v>
+        <v>0.02910654022717292</v>
       </c>
       <c r="P54" t="n">
-        <v>0.009714964413895825</v>
+        <v>0.009243086630634095</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.07312325960929374</v>
+        <v>0.07255981861292519</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009498009301797776</v>
+        <v>0.009067833061688037</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02392835809120407</v>
+        <v>0.02310987300211455</v>
       </c>
       <c r="T54" t="n">
-        <v>0.07236311208038844</v>
+        <v>0.07128378914059678</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0175716006200648</v>
+        <v>0.01705502859555651</v>
       </c>
       <c r="V54" t="n">
-        <v>0.2975821459384932</v>
+        <v>0.2943742743972195</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01607589710380515</v>
+        <v>0.01638544768323177</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04382748915190741</v>
+        <v>0.04201567078519512</v>
       </c>
     </row>
     <row r="55">
@@ -4826,46 +4826,46 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.09429883103599272</v>
+        <v>0.0949000769531866</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4226422141017169</v>
+        <v>0.4231232279039885</v>
       </c>
       <c r="M55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.425812673917372</v>
       </c>
       <c r="N55" t="n">
-        <v>4.379791881537836</v>
+        <v>4.387990122460482</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02061279926343093</v>
+        <v>0.02018013346376439</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009927893749559635</v>
+        <v>0.009946550188878916</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.08237740878664727</v>
+        <v>0.08210655172856671</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01284118487219932</v>
+        <v>0.01297656494219324</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01211098176335709</v>
+        <v>0.01212401297244044</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04693522731761192</v>
+        <v>0.04517608153037267</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0154412421320995</v>
+        <v>0.01531409660371437</v>
       </c>
       <c r="V55" t="n">
-        <v>0.3416254889716088</v>
+        <v>0.3407612491355209</v>
       </c>
       <c r="W55" t="n">
-        <v>0.01733889424481865</v>
+        <v>0.01846199273579462</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02316536921314722</v>
+        <v>0.02293597909263046</v>
       </c>
     </row>
     <row r="56">
@@ -4906,46 +4906,46 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2182594007781727</v>
+        <v>0.2084054602031741</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3632041525073144</v>
+        <v>0.3600930313309837</v>
       </c>
       <c r="M56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.062930613106723</v>
       </c>
       <c r="N56" t="n">
-        <v>4.366532482874562</v>
+        <v>4.325495710244655</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02225400803211986</v>
+        <v>0.02210648824806744</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01197093652481622</v>
+        <v>0.01176598458901091</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.04092289907416974</v>
+        <v>0.04075638105339113</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01424153954652057</v>
+        <v>0.01410140152206501</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0438841256441355</v>
+        <v>0.04455726009686568</v>
       </c>
       <c r="T56" t="n">
-        <v>0.05123022807234651</v>
+        <v>0.05061686586084162</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02114476350325476</v>
+        <v>0.02061985347214569</v>
       </c>
       <c r="V56" t="n">
-        <v>0.1525327221890158</v>
+        <v>0.1520098973950142</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02357754336827928</v>
+        <v>0.02442111072520134</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1101127042870771</v>
+        <v>0.1119627520468515</v>
       </c>
     </row>
     <row r="57">
@@ -4986,46 +4986,46 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3849234920957109</v>
+        <v>0.3825163888057561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4589257250886275</v>
+        <v>0.4558533320374499</v>
       </c>
       <c r="M57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.276433697976676</v>
       </c>
       <c r="N57" t="n">
-        <v>4.399626542032839</v>
+        <v>4.373380090074489</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02525194925333811</v>
+        <v>0.02538363146635662</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01010886488170158</v>
+        <v>0.00997545735538052</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.08652608198650005</v>
+        <v>0.08595078289326201</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01393674822243521</v>
+        <v>0.01385699480007947</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02181837753645295</v>
+        <v>0.02163546040652497</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05254577903710254</v>
+        <v>0.05255138351840975</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01676245829707809</v>
+        <v>0.01630445804602742</v>
       </c>
       <c r="V57" t="n">
-        <v>0.3280266098639196</v>
+        <v>0.3264916220278885</v>
       </c>
       <c r="W57" t="n">
-        <v>0.01882221182874181</v>
+        <v>0.02010057229666719</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03426812216578749</v>
+        <v>0.03345048501093955</v>
       </c>
     </row>
     <row r="58">
@@ -5066,46 +5066,46 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.08261752618468854</v>
+        <v>0.07740090498216672</v>
       </c>
       <c r="L58" t="n">
-        <v>0.48743776283418</v>
+        <v>0.4686578136586437</v>
       </c>
       <c r="M58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.225917546295505</v>
       </c>
       <c r="N58" t="n">
-        <v>4.735138371290561</v>
+        <v>4.399910791868061</v>
       </c>
       <c r="O58" t="n">
-        <v>0.05168765095694937</v>
+        <v>0.05115586872456744</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01141431645896345</v>
+        <v>0.01056689686493179</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.1704580182212461</v>
+        <v>0.1695130321053566</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008297837225579663</v>
+        <v>0.007709478013053325</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0451501866667048</v>
+        <v>0.04347199380854039</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1455004864511501</v>
+        <v>0.1456320596511286</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02176597973406314</v>
+        <v>0.02010374954440855</v>
       </c>
       <c r="V58" t="n">
-        <v>1.09253310847922</v>
+        <v>1.091195420794422</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01819762094195803</v>
+        <v>0.01796724233466184</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09971566492702515</v>
+        <v>0.09615967060313067</v>
       </c>
     </row>
     <row r="59">
@@ -5146,46 +5146,46 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4698313368793378</v>
+        <v>0.4677808511850242</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5167502134279384</v>
+        <v>0.515649168052881</v>
       </c>
       <c r="M59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.211580767596805</v>
       </c>
       <c r="N59" t="n">
-        <v>4.389919451764065</v>
+        <v>4.385713492739145</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01064279948295068</v>
+        <v>0.01105778307330017</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004413509263889431</v>
+        <v>0.004345440540321473</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.117554152245852</v>
+        <v>0.1144390838443708</v>
       </c>
       <c r="R59" t="n">
-        <v>0.006065223801866916</v>
+        <v>0.006022792112750541</v>
       </c>
       <c r="S59" t="n">
-        <v>0.007081269292755724</v>
+        <v>0.007022642699285349</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01796699834413976</v>
+        <v>0.01886039609919973</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005649199991748862</v>
+        <v>0.005461442732465875</v>
       </c>
       <c r="V59" t="n">
-        <v>0.4303333891414136</v>
+        <v>0.4198095712585483</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005400096343505143</v>
+        <v>0.005860135464004924</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006882034393591435</v>
+        <v>0.006622152778646</v>
       </c>
     </row>
     <row r="60">
@@ -5226,46 +5226,46 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3312705578089989</v>
+        <v>0.3189569329734549</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2474873129924716</v>
+        <v>0.2352244177000707</v>
       </c>
       <c r="M60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.034948938354199</v>
       </c>
       <c r="N60" t="n">
-        <v>4.306473805398287</v>
+        <v>4.20670577107314</v>
       </c>
       <c r="O60" t="n">
-        <v>0.00495253874719614</v>
+        <v>0.005140916073778912</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003655375825875404</v>
+        <v>0.003592402431774052</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001935602657099448</v>
+        <v>0.001837122072453943</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001736051491214729</v>
+        <v>0.001655957385243227</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004776350684123118</v>
+        <v>0.004692208695951013</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008569375132733681</v>
+        <v>0.008957972913942772</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005540284498413784</v>
+        <v>0.005505035720714246</v>
       </c>
       <c r="V60" t="n">
-        <v>0.004968461511640454</v>
+        <v>0.004777767969539658</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002263217605396731</v>
+        <v>0.002288017436048617</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005500805565327364</v>
+        <v>0.005390282671363266</v>
       </c>
     </row>
     <row r="61">
@@ -5306,46 +5306,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3143533444338791</v>
+        <v>0.3156444100186744</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2959827124680777</v>
+        <v>0.2998222032130222</v>
       </c>
       <c r="M61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.852023036776635</v>
       </c>
       <c r="N61" t="n">
-        <v>4.185935594603875</v>
+        <v>4.246883897328603</v>
       </c>
       <c r="O61" t="n">
-        <v>0.007938081137459413</v>
+        <v>0.008000835002615484</v>
       </c>
       <c r="P61" t="n">
-        <v>0.00689200436830891</v>
+        <v>0.006969793551223095</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.006606598568396101</v>
+        <v>0.006581062093736738</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01013052719966298</v>
+        <v>0.01015760648561536</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0371225572840316</v>
+        <v>0.03655672033482341</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01350804921171758</v>
+        <v>0.01355272840557953</v>
       </c>
       <c r="U61" t="n">
-        <v>0.008944225356434413</v>
+        <v>0.0088587644751767</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01748423029122681</v>
+        <v>0.01752125348787074</v>
       </c>
       <c r="W61" t="n">
-        <v>0.009548442745591216</v>
+        <v>0.01002039379629985</v>
       </c>
       <c r="X61" t="n">
-        <v>0.2145085902402799</v>
+        <v>0.2063285917700857</v>
       </c>
     </row>
     <row r="62">
@@ -5386,46 +5386,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1480862046118177</v>
+        <v>0.1479508876328733</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2287565666655229</v>
+        <v>0.2335736377982629</v>
       </c>
       <c r="M62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.143875794202612</v>
       </c>
       <c r="N62" t="n">
-        <v>4.116517245805645</v>
+        <v>4.196078696735074</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01011478770515744</v>
+        <v>0.01013572231471528</v>
       </c>
       <c r="P62" t="n">
-        <v>0.004708410768109818</v>
+        <v>0.004716179654627466</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.005962769539222874</v>
+        <v>0.006015638688699266</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01323334418843647</v>
+        <v>0.01328294584221445</v>
       </c>
       <c r="S62" t="n">
-        <v>0.00947143695865924</v>
+        <v>0.009508792157189323</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02107380520745036</v>
+        <v>0.02101183914386468</v>
       </c>
       <c r="U62" t="n">
-        <v>0.008964797537690307</v>
+        <v>0.00916925041257584</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01624592531893912</v>
+        <v>0.01643212575949786</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02159366987629204</v>
+        <v>0.02201037740592593</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01985396495599737</v>
+        <v>0.01995416574495661</v>
       </c>
     </row>
     <row r="63">
@@ -5466,46 +5466,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2731492526497677</v>
+        <v>0.2740450099273068</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2926965032457601</v>
+        <v>0.2963371421677554</v>
       </c>
       <c r="M63" t="n">
-        <v>4.076109010387499</v>
+        <v>3.971058122228126</v>
       </c>
       <c r="N63" t="n">
-        <v>4.196302435184911</v>
+        <v>4.237971206123075</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007353178023350164</v>
+        <v>0.007370477188540842</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006018275989540945</v>
+        <v>0.006053861537779436</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.00576663111914415</v>
+        <v>0.005778785575188449</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007725617864644303</v>
+        <v>0.007746446798016527</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01657217820854397</v>
+        <v>0.01655511826470095</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01298096043243058</v>
+        <v>0.01291409643532909</v>
       </c>
       <c r="U63" t="n">
-        <v>0.008007718227869994</v>
+        <v>0.007907969858541563</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01558824422283204</v>
+        <v>0.01566925641199429</v>
       </c>
       <c r="W63" t="n">
-        <v>0.009982302575600175</v>
+        <v>0.01016859251456971</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03328870755241764</v>
+        <v>0.03338385679575732</v>
       </c>
     </row>
     <row r="64">
@@ -5546,46 +5546,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2197861281348692</v>
+        <v>0.2247029268396697</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3158654390730717</v>
+        <v>0.3239428980426945</v>
       </c>
       <c r="M64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.76527181006721</v>
       </c>
       <c r="N64" t="n">
-        <v>4.14643545732783</v>
+        <v>4.245801467891633</v>
       </c>
       <c r="O64" t="n">
-        <v>0.008489977190151739</v>
+        <v>0.008580109295817337</v>
       </c>
       <c r="P64" t="n">
-        <v>0.006036301305821117</v>
+        <v>0.0062297669490643</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.01096872790690472</v>
+        <v>0.01100638180666269</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01738187987455088</v>
+        <v>0.01775468262348194</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0526664466238676</v>
+        <v>0.05009160432275608</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01618323976875807</v>
+        <v>0.01623433134298639</v>
       </c>
       <c r="U64" t="n">
-        <v>0.008356980544929801</v>
+        <v>0.008529822570495555</v>
       </c>
       <c r="V64" t="n">
-        <v>0.03092470969539794</v>
+        <v>0.03113392025282145</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0251598466066336</v>
+        <v>0.02629174441983547</v>
       </c>
       <c r="X64" t="n">
-        <v>0.8645269603318493</v>
+        <v>0.7307409168651849</v>
       </c>
     </row>
     <row r="65">
@@ -5626,46 +5626,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2967152163516893</v>
+        <v>0.2977175138061146</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3673360861204166</v>
+        <v>0.3718661859461747</v>
       </c>
       <c r="M65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.910917589484847</v>
       </c>
       <c r="N65" t="n">
-        <v>4.221191524879276</v>
+        <v>4.268391502298174</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008120135907852941</v>
+        <v>0.008168707976664398</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007720727404675687</v>
+        <v>0.007792065518520204</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.01596062916262731</v>
+        <v>0.01591009005495642</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01038178697908472</v>
+        <v>0.01045815511809733</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03121390849564011</v>
+        <v>0.03117798260057641</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01382003150578177</v>
+        <v>0.01389820199854916</v>
       </c>
       <c r="U65" t="n">
-        <v>0.009976793770087174</v>
+        <v>0.01031477565224479</v>
       </c>
       <c r="V65" t="n">
-        <v>0.04645016979420426</v>
+        <v>0.04678863461115898</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01189011587419497</v>
+        <v>0.0129686084092222</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1229114970514657</v>
+        <v>0.1215408669487532</v>
       </c>
     </row>
     <row r="66">
@@ -5706,46 +5706,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2596205515275795</v>
+        <v>0.2630911090154406</v>
       </c>
       <c r="L66" t="n">
-        <v>0.31012420988207</v>
+        <v>0.3180915457236916</v>
       </c>
       <c r="M66" t="n">
-        <v>4.099154174190237</v>
+        <v>3.953139984689836</v>
       </c>
       <c r="N66" t="n">
-        <v>4.154098830233742</v>
+        <v>4.246211445618417</v>
       </c>
       <c r="O66" t="n">
-        <v>0.008714604142708872</v>
+        <v>0.008753578451990296</v>
       </c>
       <c r="P66" t="n">
-        <v>0.006694138740447101</v>
+        <v>0.006860829000433353</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0103570715044614</v>
+        <v>0.01043068174194119</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01540396124709768</v>
+        <v>0.01566223518513827</v>
       </c>
       <c r="S66" t="n">
-        <v>0.02945940335550907</v>
+        <v>0.02915070308948675</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01651149102075336</v>
+        <v>0.01644427099767844</v>
       </c>
       <c r="U66" t="n">
-        <v>0.00934919437118643</v>
+        <v>0.009107008422150361</v>
       </c>
       <c r="V66" t="n">
-        <v>0.02858332525053082</v>
+        <v>0.0289134040907657</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02009934167743573</v>
+        <v>0.02101157703432345</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1548152223507637</v>
+        <v>0.1492793972564135</v>
       </c>
     </row>
     <row r="67">
@@ -5786,46 +5786,46 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.418401611669922</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3753513190174045</v>
+        <v>0.3819472915502818</v>
       </c>
       <c r="M67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.381125636492835</v>
       </c>
       <c r="N67" t="n">
-        <v>4.258585196288732</v>
+        <v>4.3437415206267</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005852354178100658</v>
+        <v>0.005981321945530078</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0140512338670169</v>
+        <v>0.01443185780472609</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01313882320403884</v>
+        <v>0.01311134644951924</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009075457922740681</v>
+        <v>0.009002841936241821</v>
       </c>
       <c r="S67" t="n">
-        <v>0.04739127234099097</v>
+        <v>0.04955294692193526</v>
       </c>
       <c r="T67" t="n">
-        <v>0.008710835532838071</v>
+        <v>0.009110887363966863</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01300202346130564</v>
+        <v>0.01313118042554026</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0473848989243745</v>
+        <v>0.04752995067573015</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01241603719128795</v>
+        <v>0.01285489229042732</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0732556917317856</v>
+        <v>0.07785118174200721</v>
       </c>
     </row>
     <row r="68">
@@ -5866,46 +5866,46 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4063693156807596</v>
+        <v>0.4256809874704213</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3562816579232267</v>
+        <v>0.37024086989327</v>
       </c>
       <c r="M68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.452681279498789</v>
       </c>
       <c r="N68" t="n">
-        <v>4.191214319442804</v>
+        <v>4.341149041498635</v>
       </c>
       <c r="O68" t="n">
-        <v>0.006659301428044041</v>
+        <v>0.006850699174922427</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01644264664450179</v>
+        <v>0.01736370747453858</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.01346072781702055</v>
+        <v>0.01389884232357233</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01355071272240249</v>
+        <v>0.01344593217992822</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01304578632043396</v>
+        <v>0.01471683289192487</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01227040008864802</v>
+        <v>0.01276432462792603</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01574087209592317</v>
+        <v>0.01608805234569639</v>
       </c>
       <c r="V68" t="n">
-        <v>0.04050855815128544</v>
+        <v>0.04205631454760868</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0191999983277571</v>
+        <v>0.01918405262622363</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02237867609998142</v>
+        <v>0.02478310122419881</v>
       </c>
     </row>
     <row r="69">
@@ -5946,46 +5946,46 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1547738540766385</v>
+        <v>0.1578375667668122</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2114859339764434</v>
+        <v>0.2144567936729055</v>
       </c>
       <c r="M69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.342039872316217</v>
       </c>
       <c r="N69" t="n">
-        <v>4.256085517541196</v>
+        <v>4.303184532172819</v>
       </c>
       <c r="O69" t="n">
-        <v>0.00825316256355399</v>
+        <v>0.008246315744868482</v>
       </c>
       <c r="P69" t="n">
-        <v>0.005285802116097168</v>
+        <v>0.005349793618174257</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.006080160378219503</v>
+        <v>0.006110958250283045</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004293369366149172</v>
+        <v>0.004326322131112634</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004186026706090101</v>
+        <v>0.004195856823191065</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01791582725706597</v>
+        <v>0.01779893935194048</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009291219152592605</v>
+        <v>0.009261002924040385</v>
       </c>
       <c r="V69" t="n">
-        <v>0.01373322446171789</v>
+        <v>0.0138292357831867</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005898134762384522</v>
+        <v>0.006098152479391987</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006185562803649021</v>
+        <v>0.006144672343345428</v>
       </c>
     </row>
     <row r="70">
@@ -6026,46 +6026,46 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.153202753067615</v>
+        <v>0.1548404427189273</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2811910896704282</v>
+        <v>0.2803484396335723</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.394470536415335</v>
       </c>
       <c r="N70" t="n">
-        <v>4.369210223140158</v>
+        <v>4.362026188385227</v>
       </c>
       <c r="O70" t="n">
-        <v>0.006843781998321336</v>
+        <v>0.00683737974045138</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009684555966829168</v>
+        <v>0.009679926537964173</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.01030085951022081</v>
+        <v>0.01029419268685945</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004615040144523076</v>
+        <v>0.004619420786771253</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006479780598643192</v>
+        <v>0.006474843743780381</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01339220143155393</v>
+        <v>0.01330245434463462</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01375165541705452</v>
+        <v>0.01366541402875141</v>
       </c>
       <c r="V70" t="n">
-        <v>0.02671613065318683</v>
+        <v>0.02670982624033935</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006470626711414841</v>
+        <v>0.006677903647715045</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009767737622637133</v>
+        <v>0.009672788733917848</v>
       </c>
     </row>
     <row r="71">
@@ -6106,46 +6106,46 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3261006684563419</v>
+        <v>0.3259506110927289</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3496510616921307</v>
+        <v>0.3487351942206435</v>
       </c>
       <c r="M71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.436154054572222</v>
       </c>
       <c r="N71" t="n">
-        <v>4.456991752659532</v>
+        <v>4.440319465156644</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008560339494277865</v>
+        <v>0.008528487484165495</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009275639199627164</v>
+        <v>0.009241273042414807</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.01204200410084731</v>
+        <v>0.01207713702270264</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005176692427550532</v>
+        <v>0.005169486642996195</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005580550099553874</v>
+        <v>0.005569849868640615</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01427152759028517</v>
+        <v>0.01410704170665147</v>
       </c>
       <c r="U71" t="n">
-        <v>0.00996878029910352</v>
+        <v>0.009886467507369101</v>
       </c>
       <c r="V71" t="n">
-        <v>0.03225673607816794</v>
+        <v>0.03237053463994669</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006502340334094161</v>
+        <v>0.006798130412147313</v>
       </c>
       <c r="X71" t="n">
-        <v>0.007133626532204145</v>
+        <v>0.007000485893441635</v>
       </c>
     </row>
     <row r="72">
@@ -6186,46 +6186,46 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3263018165925168</v>
+        <v>0.3237573962818418</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4219964305399904</v>
+        <v>0.4164125635912082</v>
       </c>
       <c r="M72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.514536388254673</v>
       </c>
       <c r="N72" t="n">
-        <v>4.561833038126851</v>
+        <v>4.505611901814954</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006102641189221581</v>
+        <v>0.006054380605746239</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007117551424207363</v>
+        <v>0.007017628670037607</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.01941388300985733</v>
+        <v>0.01932574713487418</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004479683054489051</v>
+        <v>0.004440088622198801</v>
       </c>
       <c r="S72" t="n">
-        <v>0.006187321876780639</v>
+        <v>0.00611787710604061</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008973691659298301</v>
+        <v>0.008824815817617734</v>
       </c>
       <c r="U72" t="n">
-        <v>0.007954209981736208</v>
+        <v>0.007879640720981459</v>
       </c>
       <c r="V72" t="n">
-        <v>0.05679042575992647</v>
+        <v>0.0562945012273876</v>
       </c>
       <c r="W72" t="n">
-        <v>0.005944760005969081</v>
+        <v>0.006203244904443203</v>
       </c>
       <c r="X72" t="n">
-        <v>0.008047270533266258</v>
+        <v>0.007784376618793378</v>
       </c>
     </row>
     <row r="73">
@@ -6266,46 +6266,46 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.07823057899988078</v>
+        <v>0.08006297265283152</v>
       </c>
       <c r="L73" t="n">
-        <v>0.07924434046343981</v>
+        <v>0.08137670514789817</v>
       </c>
       <c r="M73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.341883758983041</v>
       </c>
       <c r="N73" t="n">
-        <v>4.219390275737816</v>
+        <v>4.328688871169668</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01315099197061887</v>
+        <v>0.01318043929528642</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01240326681684084</v>
+        <v>0.0125466430551157</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002167944110850656</v>
+        <v>0.002167715958196518</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002533549718873055</v>
+        <v>0.002549688039978831</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003708408580922839</v>
+        <v>0.0003793148708945231</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03799693390038639</v>
+        <v>0.03799856800368664</v>
       </c>
       <c r="U73" t="n">
-        <v>0.02535109665074397</v>
+        <v>0.02527688761485034</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004535740978730117</v>
+        <v>0.004536652955853525</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004107257599001495</v>
+        <v>0.004164534776591435</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003234161065743833</v>
+        <v>0.003228791926099474</v>
       </c>
     </row>
     <row r="74">
@@ -6346,46 +6346,46 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08513405677699858</v>
+        <v>0.0844764733101903</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1690961730137017</v>
+        <v>0.1660310188475765</v>
       </c>
       <c r="M74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.399088907307153</v>
       </c>
       <c r="N74" t="n">
-        <v>4.45756592349835</v>
+        <v>4.387721756493224</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006096538743777485</v>
+        <v>0.006072932102369062</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008491488973925579</v>
+        <v>0.008410328275183171</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.004650610120565482</v>
+        <v>0.004647142523476647</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002126688373280693</v>
+        <v>0.002118002127884821</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003748679951092767</v>
+        <v>0.003735940468329064</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01599811676669597</v>
+        <v>0.01595028617400128</v>
       </c>
       <c r="U74" t="n">
-        <v>0.01427024459881444</v>
+        <v>0.01426152891022485</v>
       </c>
       <c r="V74" t="n">
-        <v>0.009549561260527197</v>
+        <v>0.009536999307135391</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003632888646811138</v>
+        <v>0.003689238551000808</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005671425486361245</v>
+        <v>0.005621872710337207</v>
       </c>
     </row>
     <row r="75">
@@ -6426,46 +6426,46 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.210319821056764</v>
+        <v>0.207879713293752</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2647685225884287</v>
+        <v>0.2637502655822012</v>
       </c>
       <c r="M75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.205773976883957</v>
       </c>
       <c r="N75" t="n">
-        <v>4.299342775271379</v>
+        <v>4.285330064989372</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006167515725407984</v>
+        <v>0.006159956762773762</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009617496154975386</v>
+        <v>0.009588744945665553</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.007603770261480315</v>
+        <v>0.007587238447960803</v>
       </c>
       <c r="R75" t="n">
-        <v>0.004795557520724152</v>
+        <v>0.00478312747709922</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007193610613647226</v>
+        <v>0.007195917205156532</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01220292406057727</v>
+        <v>0.01213916372238912</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01271405661121299</v>
+        <v>0.01262105451104735</v>
       </c>
       <c r="V75" t="n">
-        <v>0.01818760233890528</v>
+        <v>0.0181684843263972</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006335314561406897</v>
+        <v>0.006550918900585312</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01098080906188252</v>
+        <v>0.01090162797408519</v>
       </c>
     </row>
     <row r="76">
@@ -6506,46 +6506,46 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.01998426772365844</v>
+        <v>0.02053128897390902</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02445810628066777</v>
+        <v>0.02508609066334347</v>
       </c>
       <c r="M76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.358945383991737</v>
       </c>
       <c r="N76" t="n">
-        <v>4.216707791069229</v>
+        <v>4.318049240424751</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04217631007679928</v>
+        <v>0.04219383973292156</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02721264255193905</v>
+        <v>0.02731077279643043</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002158852956775184</v>
+        <v>0.002159166201156925</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002212992805467323</v>
+        <v>0.00221778016466729</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007928616643627364</v>
+        <v>0.0007945433829504842</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1426843063898659</v>
+        <v>0.1426419537058833</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08411930222540388</v>
+        <v>0.08403595881690398</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003928235340434109</v>
+        <v>0.003928934316714309</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003723249631327251</v>
+        <v>0.003737555112816588</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002701032353154275</v>
+        <v>0.002698768418534519</v>
       </c>
     </row>
     <row r="77">
@@ -6586,46 +6586,46 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03972700182767472</v>
+        <v>0.03789390692492493</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09012410250784524</v>
+        <v>0.08292963581181916</v>
       </c>
       <c r="M77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.275909837651753</v>
       </c>
       <c r="N77" t="n">
-        <v>4.553736519599209</v>
+        <v>4.243110822914587</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01340436664360099</v>
+        <v>0.01335557096114733</v>
       </c>
       <c r="P77" t="n">
-        <v>0.003963150617794325</v>
+        <v>0.003709349423202523</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002387634581959334</v>
+        <v>0.002379726884508766</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003854162829427958</v>
+        <v>0.0003763306604480696</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001787782719177492</v>
+        <v>0.001771409539367823</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03335525549723769</v>
+        <v>0.03341861986133945</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01289585084541008</v>
+        <v>0.01283848610580937</v>
       </c>
       <c r="V77" t="n">
-        <v>0.004086689117455717</v>
+        <v>0.004071085524943788</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002006462079174294</v>
+        <v>0.002024296405620972</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002791484304500889</v>
+        <v>0.002769094973651774</v>
       </c>
     </row>
     <row r="78">
@@ -6666,46 +6666,46 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02841134719532212</v>
+        <v>0.02722131315634268</v>
       </c>
       <c r="L78" t="n">
-        <v>0.08212549273641169</v>
+        <v>0.07757285863185416</v>
       </c>
       <c r="M78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.411801604657093</v>
       </c>
       <c r="N78" t="n">
-        <v>4.642088518010579</v>
+        <v>4.377579260969767</v>
       </c>
       <c r="O78" t="n">
-        <v>0.006295000007249404</v>
+        <v>0.006191725781492362</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000048821e-05</v>
+        <v>1.000000000015629e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.002033300105763298</v>
+        <v>0.002055080234097392</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001555632221530713</v>
+        <v>0.0001676613644070592</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000029e-05</v>
+        <v>1.000000000000053e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0214656863995536</v>
+        <v>0.02127841748029065</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01876078187177839</v>
+        <v>0.01842605984610099</v>
       </c>
       <c r="V78" t="n">
-        <v>0.003619204868368156</v>
+        <v>0.003649740698448271</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001685492001063148</v>
+        <v>0.001708170741376304</v>
       </c>
       <c r="X78" t="n">
-        <v>0.00293513061426383</v>
+        <v>0.002929186528738509</v>
       </c>
     </row>
     <row r="79">
@@ -6746,46 +6746,46 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2899193890845111</v>
+        <v>0.291298707758667</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3202890234129229</v>
+        <v>0.3305190424627622</v>
       </c>
       <c r="M79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.395075630781815</v>
       </c>
       <c r="N79" t="n">
-        <v>4.431667214349138</v>
+        <v>4.439000976856815</v>
       </c>
       <c r="O79" t="n">
-        <v>0.00309970457079741</v>
+        <v>0.0030493650607155</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001839926556122231</v>
+        <v>0.001822142396168952</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.003364188108134238</v>
+        <v>0.003531992673649635</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001633543006676789</v>
+        <v>0.001661419250930073</v>
       </c>
       <c r="S79" t="n">
-        <v>0.4103458773541439</v>
+        <v>1.000000009297441e-05</v>
       </c>
       <c r="T79" t="n">
-        <v>0.006176071064160573</v>
+        <v>0.005999946057535997</v>
       </c>
       <c r="U79" t="n">
-        <v>0.00285523240620966</v>
+        <v>0.002118343938152528</v>
       </c>
       <c r="V79" t="n">
-        <v>0.009979722629907177</v>
+        <v>0.01106190708826921</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002473036311397118</v>
+        <v>0.002607464827299831</v>
       </c>
       <c r="X79" t="n">
-        <v>263.9322021172584</v>
+        <v>0.09212410143803679</v>
       </c>
     </row>
     <row r="80">
@@ -6826,46 +6826,46 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1594873656769697</v>
+        <v>0.1623021847871931</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2383360223124687</v>
+        <v>0.2461521505440487</v>
       </c>
       <c r="M80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.51750010072576</v>
       </c>
       <c r="N80" t="n">
-        <v>4.462370599644314</v>
+        <v>4.473602328272493</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004301208055208511</v>
+        <v>0.004240554041854937</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002644627465217513</v>
+        <v>0.002617430235380637</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.002949808959264549</v>
+        <v>0.003020996001069391</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001709740098828165</v>
+        <v>0.001734728906689512</v>
       </c>
       <c r="S80" t="n">
-        <v>0.1561656185085979</v>
+        <v>1.000000000000011e-05</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01110376385738375</v>
+        <v>0.01064745352376012</v>
       </c>
       <c r="U80" t="n">
-        <v>0.004434574465741509</v>
+        <v>0.003119576531330426</v>
       </c>
       <c r="V80" t="n">
-        <v>0.008772534569871513</v>
+        <v>0.008809571716300571</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002556108478007598</v>
+        <v>0.002866173669782213</v>
       </c>
       <c r="X80" t="n">
-        <v>445.1688512840099</v>
+        <v>0.1227993893269681</v>
       </c>
     </row>
     <row r="81">
@@ -6906,46 +6906,46 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2816063271155299</v>
+        <v>0.2797133348512962</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2525649310894141</v>
+        <v>0.2613693841799036</v>
       </c>
       <c r="M81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.547852263736372</v>
       </c>
       <c r="N81" t="n">
-        <v>4.557184999926726</v>
+        <v>4.585465525856633</v>
       </c>
       <c r="O81" t="n">
-        <v>0.00384406717748161</v>
+        <v>0.003804179579311715</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002256912195000025</v>
+        <v>0.002242178796737677</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.002053524575637056</v>
+        <v>0.002110477016987303</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001600769776404502</v>
+        <v>0.00162516530894053</v>
       </c>
       <c r="S81" t="n">
-        <v>0.4257567601010788</v>
+        <v>1.000000000000107e-05</v>
       </c>
       <c r="T81" t="n">
-        <v>0.008057655969365137</v>
+        <v>0.007874350316814688</v>
       </c>
       <c r="U81" t="n">
-        <v>0.00342428401096394</v>
+        <v>0.003200205194617548</v>
       </c>
       <c r="V81" t="n">
-        <v>0.005396265427017053</v>
+        <v>0.005901886150266844</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002170747568959797</v>
+        <v>0.002511681053593598</v>
       </c>
       <c r="X81" t="n">
-        <v>399.20291813603</v>
+        <v>0.1086244744926429</v>
       </c>
     </row>
     <row r="82">
@@ -6986,46 +6986,46 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1904621880632897</v>
+        <v>0.191395009818949</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1461522544551769</v>
+        <v>0.1472659688796732</v>
       </c>
       <c r="M82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.463985251926877</v>
       </c>
       <c r="N82" t="n">
-        <v>4.542169655898186</v>
+        <v>4.585567843391069</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006841051714969873</v>
+        <v>0.006875098066507971</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003088514430722867</v>
+        <v>0.003110473071782004</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001348252471614293</v>
+        <v>0.001345032898845416</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001765701231122805</v>
+        <v>0.001761914143982365</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0834373251131249</v>
+        <v>0.4999999999642853</v>
       </c>
       <c r="T82" t="n">
-        <v>0.03188253487168729</v>
+        <v>0.02417866104757076</v>
       </c>
       <c r="U82" t="n">
-        <v>0.01019881134143779</v>
+        <v>0.005817071056176423</v>
       </c>
       <c r="V82" t="n">
-        <v>0.003684970527283691</v>
+        <v>0.003963107370643349</v>
       </c>
       <c r="W82" t="n">
-        <v>0.002551422655963407</v>
+        <v>0.00332318454856039</v>
       </c>
       <c r="X82" t="n">
-        <v>937.2354235999352</v>
+        <v>30576.12093159843</v>
       </c>
     </row>
     <row r="83">
@@ -7064,46 +7064,46 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1872142165502269</v>
+        <v>0.189934792401037</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1743607991128898</v>
+        <v>0.1825649533455875</v>
       </c>
       <c r="M83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.578578953049799</v>
       </c>
       <c r="N83" t="n">
-        <v>4.496931118128425</v>
+        <v>4.572070906719971</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004233629169810319</v>
+        <v>0.004176303540321362</v>
       </c>
       <c r="P83" t="n">
-        <v>0.001704101599996542</v>
+        <v>0.00171416512532195</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.00141517286552671</v>
+        <v>0.001440721495200495</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001399145539084296</v>
+        <v>0.001422804646204883</v>
       </c>
       <c r="S83" t="n">
-        <v>0.3727359685394709</v>
+        <v>1.000000238964637e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.0101545265719777</v>
+        <v>0.01015904721240343</v>
       </c>
       <c r="U83" t="n">
-        <v>0.005203991012789394</v>
+        <v>0.004949107285929085</v>
       </c>
       <c r="V83" t="n">
-        <v>0.003429412089772532</v>
+        <v>0.003728365474135352</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002065145476873326</v>
+        <v>0.002372796481256224</v>
       </c>
       <c r="X83" t="n">
-        <v>389.9646767600557</v>
+        <v>0.1285327874998751</v>
       </c>
     </row>
     <row r="84">
@@ -7142,46 +7142,46 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1659043674747134</v>
+        <v>0.171344845273151</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2944529056840027</v>
+        <v>0.3150855700217797</v>
       </c>
       <c r="M84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.585710978228106</v>
       </c>
       <c r="N84" t="n">
-        <v>4.341541885135942</v>
+        <v>4.514447225996494</v>
       </c>
       <c r="O84" t="n">
-        <v>0.003483790642080804</v>
+        <v>0.00339100588623381</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0005411674282412329</v>
+        <v>0.0006915266427309581</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.004225007297875671</v>
+        <v>0.004446731886819412</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002164392580722491</v>
+        <v>0.002270999306836499</v>
       </c>
       <c r="S84" t="n">
         <v>1e-05</v>
       </c>
       <c r="T84" t="n">
-        <v>0.00829894855723879</v>
+        <v>0.007793437798429175</v>
       </c>
       <c r="U84" t="n">
-        <v>0.005050771744137397</v>
+        <v>0.004561462884380771</v>
       </c>
       <c r="V84" t="n">
-        <v>0.01364371042719127</v>
+        <v>0.01460357726672547</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003266281999827523</v>
+        <v>0.003725108105572998</v>
       </c>
       <c r="X84" t="n">
-        <v>0.08916770478323766</v>
+        <v>0.08015211397900641</v>
       </c>
     </row>
     <row r="85">
@@ -7220,46 +7220,46 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2307899480131057</v>
+        <v>0.2347111018878213</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2859293135894418</v>
+        <v>0.295207682566716</v>
       </c>
       <c r="M85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.499856930037251</v>
       </c>
       <c r="N85" t="n">
-        <v>4.43944731561167</v>
+        <v>4.494031048189669</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003205255059678889</v>
+        <v>0.003123853781395702</v>
       </c>
       <c r="P85" t="n">
-        <v>1.000000000000719e-05</v>
+        <v>1.000000000701515e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.003034437756600378</v>
+        <v>0.003071987961639764</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001704851840430194</v>
+        <v>0.001784312597282091</v>
       </c>
       <c r="S85" t="n">
-        <v>0.4999999999999917</v>
+        <v>1.000000000000973e-05</v>
       </c>
       <c r="T85" t="n">
-        <v>0.00725996502791166</v>
+        <v>0.006948181082872566</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008200876125719035</v>
+        <v>0.008318811544661376</v>
       </c>
       <c r="V85" t="n">
-        <v>0.009662292698878003</v>
+        <v>0.01012274793318518</v>
       </c>
       <c r="W85" t="n">
-        <v>0.002503095942119394</v>
+        <v>0.002901263572513301</v>
       </c>
       <c r="X85" t="n">
-        <v>560.2395891188245</v>
+        <v>0.1105351683117262</v>
       </c>
     </row>
     <row r="86">
@@ -7298,46 +7298,46 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1218510305567165</v>
+        <v>0.1247724149338163</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1552078986599854</v>
+        <v>0.1593628540125017</v>
       </c>
       <c r="M86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.570462719990509</v>
       </c>
       <c r="N86" t="n">
-        <v>4.395544097861261</v>
+        <v>4.515451460297303</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005655435583798523</v>
+        <v>0.005658362437520068</v>
       </c>
       <c r="P86" t="n">
-        <v>1.000000000000042e-05</v>
+        <v>1.000000000000045e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001972401789308168</v>
+        <v>0.001965539086526244</v>
       </c>
       <c r="R86" t="n">
-        <v>0.00176931382177261</v>
+        <v>0.001796124563344605</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000000002172458e-05</v>
+        <v>1.000000002528958e-05</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01788558509766338</v>
+        <v>0.01748892469336824</v>
       </c>
       <c r="U86" t="n">
-        <v>0.00966868143820117</v>
+        <v>0.01076500190864138</v>
       </c>
       <c r="V86" t="n">
-        <v>0.004966876626304382</v>
+        <v>0.004959107179541152</v>
       </c>
       <c r="W86" t="n">
-        <v>0.002741369478383236</v>
+        <v>0.003011727484439199</v>
       </c>
       <c r="X86" t="n">
-        <v>0.168505984882377</v>
+        <v>0.1599482502462652</v>
       </c>
     </row>
     <row r="87">
@@ -7376,46 +7376,46 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1823831187847791</v>
+        <v>0.1836932533354582</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3085129704106955</v>
+        <v>0.3217826304399089</v>
       </c>
       <c r="M87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.671002060938001</v>
       </c>
       <c r="N87" t="n">
-        <v>4.467221486905247</v>
+        <v>4.624548267061019</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004119575080093583</v>
+        <v>0.004065531845368829</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0004118781336248522</v>
+        <v>0.0005287448694617137</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.004681506291723889</v>
+        <v>0.004712946527177218</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002233132913344076</v>
+        <v>0.002298805776887696</v>
       </c>
       <c r="S87" t="n">
         <v>1e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>0.009646751735695741</v>
+        <v>0.009286656785054833</v>
       </c>
       <c r="U87" t="n">
-        <v>0.007508124261896846</v>
+        <v>0.006448920658482471</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01352822840280683</v>
+        <v>0.01355628129329457</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003224639927107268</v>
+        <v>0.003593754427822578</v>
       </c>
       <c r="X87" t="n">
-        <v>0.09736504413579224</v>
+        <v>0.08726436389754769</v>
       </c>
     </row>
     <row r="88">
@@ -7454,46 +7454,46 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2319557577696864</v>
+        <v>0.2269187226468679</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1633583026201504</v>
+        <v>0.1608076984320481</v>
       </c>
       <c r="M88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.508038364188548</v>
       </c>
       <c r="N88" t="n">
-        <v>4.564209722950051</v>
+        <v>4.616256397861295</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005281260374474418</v>
+        <v>0.005452937624335883</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0003674232705622044</v>
+        <v>0.0002918095167953743</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001209222273375171</v>
+        <v>0.001197308463295356</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001427948417358695</v>
+        <v>0.00139710216235785</v>
       </c>
       <c r="S88" t="n">
-        <v>7.332759815367288e-05</v>
+        <v>0.4999999996119651</v>
       </c>
       <c r="T88" t="n">
-        <v>0.01291269932341434</v>
+        <v>0.01570988562740987</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01093521425954527</v>
+        <v>0.01869809029283888</v>
       </c>
       <c r="V88" t="n">
-        <v>0.002997364573295608</v>
+        <v>0.003097420985304032</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002115146659416858</v>
+        <v>0.002148696395860506</v>
       </c>
       <c r="X88" t="n">
-        <v>0.1936981343840804</v>
+        <v>21137.86043238085</v>
       </c>
     </row>
     <row r="89">
@@ -7532,46 +7532,46 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3362423670805384</v>
+        <v>0.3352916146113781</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3293317404665053</v>
+        <v>0.3410051630823244</v>
       </c>
       <c r="M89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.501914574676857</v>
       </c>
       <c r="N89" t="n">
-        <v>4.620878519940363</v>
+        <v>4.602133439799404</v>
       </c>
       <c r="O89" t="n">
-        <v>0.004228377122259293</v>
+        <v>0.004105550385983831</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001580411887581831</v>
+        <v>0.001577168375250506</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00344042694278725</v>
+        <v>0.003669755913252894</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001853866026172971</v>
+        <v>0.00192518783043757</v>
       </c>
       <c r="S89" t="n">
-        <v>0.05436070154487376</v>
+        <v>1e-05</v>
       </c>
       <c r="T89" t="n">
-        <v>0.008801286647116345</v>
+        <v>0.008284268132251664</v>
       </c>
       <c r="U89" t="n">
-        <v>0.00589712004894071</v>
+        <v>0.004312184686117029</v>
       </c>
       <c r="V89" t="n">
-        <v>0.01180709859897049</v>
+        <v>0.01108419958385802</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002885428415815318</v>
+        <v>0.002831795004613285</v>
       </c>
       <c r="X89" t="n">
-        <v>114.2469501978194</v>
+        <v>0.06763402706008698</v>
       </c>
     </row>
     <row r="90">
@@ -7610,46 +7610,46 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2010801060973464</v>
+        <v>0.2309014164628462</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3867136108336567</v>
+        <v>0.483386414036669</v>
       </c>
       <c r="M90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.475080783493183</v>
       </c>
       <c r="N90" t="n">
-        <v>3.539499807742724</v>
+        <v>4.283333172759931</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003732571463229506</v>
+        <v>0.003752986198842751</v>
       </c>
       <c r="P90" t="n">
-        <v>0.002848309014405433</v>
+        <v>0.003629405959523495</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.198366039895676</v>
+        <v>0.2109041479825474</v>
       </c>
       <c r="R90" t="n">
-        <v>0.008099197626493427</v>
+        <v>0.009860024489724827</v>
       </c>
       <c r="S90" t="n">
-        <v>1.42749531282801e-05</v>
+        <v>0.003202106152940633</v>
       </c>
       <c r="T90" t="n">
-        <v>0.005785202219898183</v>
+        <v>0.007182533005404356</v>
       </c>
       <c r="U90" t="n">
-        <v>0.008029451264471325</v>
+        <v>0.00595018370944406</v>
       </c>
       <c r="V90" t="n">
-        <v>1.128555892500296</v>
+        <v>1.265635007840707</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02153309810798211</v>
+        <v>0.02551555414458263</v>
       </c>
       <c r="X90" t="n">
-        <v>0.01840030348178824</v>
+        <v>0.1305262995385734</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Flexible CUE/Local_estpar_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_True_vo_True_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001838908966245269</v>
+        <v>0.1674339198426332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004801288814977661</v>
+        <v>0.2034809323080299</v>
       </c>
       <c r="M2" t="n">
-        <v>4.428549100137174</v>
+        <v>4.387464748584332</v>
       </c>
       <c r="N2" t="n">
-        <v>4.430319695540526</v>
+        <v>4.429242959050717</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00181243363692048</v>
+        <v>0.003878333931121406</v>
       </c>
       <c r="P2" t="n">
-        <v>1.000000000020666e-05</v>
+        <v>0.002523778735336233</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001265151641667229</v>
+        <v>0.0009392952750567257</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006572126239619282</v>
+        <v>0.0009388997648356823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003013662695292899</v>
+        <v>0.0005945460288047852</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007220662104250231</v>
+        <v>0.01477369027068497</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01335677176717739</v>
+        <v>0.007002834473481353</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004609781837847328</v>
+        <v>0.002627162548146375</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004339154019135831</v>
+        <v>0.001924777402748358</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00544199787126697</v>
+        <v>0.001480582958079283</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001488722301635293</v>
+        <v>0.001198806640067375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003526771802274085</v>
+        <v>0.002700793605153488</v>
       </c>
       <c r="M3" t="n">
-        <v>4.340363192882071</v>
+        <v>4.350145945842956</v>
       </c>
       <c r="N3" t="n">
-        <v>4.312630789934726</v>
+        <v>4.310267429225191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002072717941895862</v>
+        <v>0.003260121222035619</v>
       </c>
       <c r="P3" t="n">
-        <v>1.000000000000539e-05</v>
+        <v>1.000000000000398e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009345535120094947</v>
+        <v>0.0007975254507360537</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003666806132081498</v>
+        <v>0.0003671404067708912</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001870037091887262</v>
+        <v>0.0001867143887654652</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009515705338381256</v>
+        <v>0.01848293117675865</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02160099393560846</v>
+        <v>0.0265549909433367</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003002790181098498</v>
+        <v>0.002240914979630686</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004586380540618682</v>
+        <v>0.003762645278500519</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003639364459247231</v>
+        <v>0.003019275484623095</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4182132258886959</v>
+        <v>0.3797397164270677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2202130590196362</v>
+        <v>0.3051924608157882</v>
       </c>
       <c r="M4" t="n">
-        <v>4.293493812215727</v>
+        <v>4.273400973870871</v>
       </c>
       <c r="N4" t="n">
-        <v>4.558566168431991</v>
+        <v>4.555784802437213</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002791111708370265</v>
+        <v>0.003468657640314652</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002317129919691388</v>
+        <v>0.002247642687662492</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005257623692854295</v>
+        <v>0.0004274476756200695</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001144606864305468</v>
+        <v>0.001155860957527253</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002604835020386588</v>
+        <v>0.0003478309892020422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008282507116400826</v>
+        <v>0.01165901972459547</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006153530817096397</v>
+        <v>0.00646915192054897</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002620901503959097</v>
+        <v>0.001853885890651095</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002079355207349396</v>
+        <v>0.002194943162434708</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001591051297729244</v>
+        <v>0.001773873556765214</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1838378561531941</v>
+        <v>0.1248483760324708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239793250601291</v>
+        <v>0.2041952440805852</v>
       </c>
       <c r="M5" t="n">
-        <v>4.308694607789535</v>
+        <v>4.305059003950912</v>
       </c>
       <c r="N5" t="n">
-        <v>4.348658188890339</v>
+        <v>4.341130994029877</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002359367928976639</v>
+        <v>0.003461325513130874</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00216167928923792</v>
+        <v>0.002044020233945446</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001407036633308179</v>
+        <v>0.001094771211158125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008342967139811359</v>
+        <v>0.0007846710908762858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001161370413790567</v>
+        <v>0.001091662531467206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007528554891609053</v>
+        <v>0.01320412193934987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004340090029285593</v>
+        <v>0.00500034416571196</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004898429666654569</v>
+        <v>0.003172565257775292</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001660147201223164</v>
+        <v>0.001617994006799005</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002486558493163133</v>
+        <v>0.00234608552290264</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1683825408883233</v>
+        <v>0.1063085574200649</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2128810735540558</v>
+        <v>0.1721744325011729</v>
       </c>
       <c r="M6" t="n">
-        <v>4.376451817448588</v>
+        <v>4.37329678087751</v>
       </c>
       <c r="N6" t="n">
-        <v>4.382914066084051</v>
+        <v>4.375534703115614</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001759699108784047</v>
+        <v>0.002561826981465904</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001371696633390666</v>
+        <v>0.00119476534340234</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008848921533980229</v>
+        <v>0.0006872852397940683</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003979444488495593</v>
+        <v>0.0003567298939471356</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003554642255074089</v>
+        <v>0.000302402756345319</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005320201585769097</v>
+        <v>0.00915186302206393</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002524265543290404</v>
+        <v>0.00264934579567079</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002824905179679858</v>
+        <v>0.001923950881882941</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009754383319290675</v>
+        <v>0.0009332156300785472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001054559052407779</v>
+        <v>0.0009783050717277286</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001787398233962809</v>
+        <v>0.001768829377981086</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004065270357696367</v>
+        <v>0.004051189450171949</v>
       </c>
       <c r="M7" t="n">
-        <v>4.252970041033242</v>
+        <v>4.241814344093751</v>
       </c>
       <c r="N7" t="n">
-        <v>4.358146218724919</v>
+        <v>4.361327791511593</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00258899009536736</v>
+        <v>0.003728115913715535</v>
       </c>
       <c r="P7" t="n">
-        <v>1.000000000004398e-05</v>
+        <v>1.42372297180809e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007417309071018624</v>
+        <v>0.0006441326692213889</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006067861512552388</v>
+        <v>0.0006052114684077744</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002746896904264295</v>
+        <v>0.0002744083945041364</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01161070953494402</v>
+        <v>0.02100467931023561</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02701805903610212</v>
+        <v>0.03066495229990765</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003105164155020395</v>
+        <v>0.001999377552563878</v>
       </c>
       <c r="W7" t="n">
-        <v>0.007929144812544822</v>
+        <v>0.00627332541890168</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008160861657476121</v>
+        <v>0.006517405617841828</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1601303832383536</v>
+        <v>0.1151345305983847</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1522977922019766</v>
+        <v>0.1546278703876657</v>
       </c>
       <c r="M8" t="n">
-        <v>4.44514495646937</v>
+        <v>4.414448855077785</v>
       </c>
       <c r="N8" t="n">
-        <v>4.408810185001522</v>
+        <v>4.413647383357921</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005078307386426126</v>
+        <v>0.008756108051336919</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002790201184433834</v>
+        <v>0.00324352597463824</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00142924531364939</v>
+        <v>0.001164155909670387</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001446189069921446</v>
+        <v>0.001393348592878838</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006845102427713426</v>
+        <v>0.0006530226456601318</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02107203520869344</v>
+        <v>0.04538314360613707</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009185300390162975</v>
+        <v>0.01563955055351057</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004877947084765272</v>
+        <v>0.003294968555615367</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003091512397015516</v>
+        <v>0.003096312280711682</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00144215010920352</v>
+        <v>0.001384967642858481</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00132724233869487</v>
+        <v>0.001015091906080705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00415186641684472</v>
+        <v>0.003233194103829165</v>
       </c>
       <c r="M9" t="n">
-        <v>4.224225056384286</v>
+        <v>4.215658680689763</v>
       </c>
       <c r="N9" t="n">
-        <v>4.344234670659814</v>
+        <v>4.345171829740377</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003611015906108416</v>
+        <v>0.005316256115243404</v>
       </c>
       <c r="P9" t="n">
-        <v>1.000000000072385e-05</v>
+        <v>1.000000000000434e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001061413336212196</v>
+        <v>0.0009025739432139733</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006557840610649507</v>
+        <v>0.0006563754005701785</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0006296329335881741</v>
+        <v>0.0006293040739808364</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01536833022798306</v>
+        <v>0.02793311220302789</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01926139535871686</v>
+        <v>0.02573927626612952</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003756038970481013</v>
+        <v>0.002660096748510807</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004897516613533341</v>
+        <v>0.004458294579294052</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003717905149215594</v>
+        <v>0.003435266331771564</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2184121480973804</v>
+        <v>0.1598414344543621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1173373640138827</v>
+        <v>0.1273419582007879</v>
       </c>
       <c r="M10" t="n">
-        <v>4.114152557453664</v>
+        <v>4.094150895426115</v>
       </c>
       <c r="N10" t="n">
-        <v>4.236237869017937</v>
+        <v>4.23751054248184</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004504611049889398</v>
+        <v>0.007494036156422006</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003053536285341186</v>
+        <v>0.003763851890991853</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007341552063229759</v>
+        <v>0.0006361039092850566</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001016859689721932</v>
+        <v>0.0009627585741528132</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005845228032727086</v>
+        <v>0.000573390315246578</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01819965483089298</v>
+        <v>0.03809019803540496</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01017847888491195</v>
+        <v>0.01808415756224956</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002178538063623833</v>
+        <v>0.001682322132170734</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001923673799178807</v>
+        <v>0.001910977245520666</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001307551328464436</v>
+        <v>0.001317824809646337</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1757473902023626</v>
+        <v>0.1415564032536594</v>
       </c>
       <c r="L11" t="n">
-        <v>0.346737297774575</v>
+        <v>0.3412782901833647</v>
       </c>
       <c r="M11" t="n">
-        <v>4.070128680268422</v>
+        <v>4.047587447108629</v>
       </c>
       <c r="N11" t="n">
-        <v>4.260751537960866</v>
+        <v>4.256091899529455</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002910557884972551</v>
+        <v>0.003972973338226013</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001710580451432206</v>
+        <v>0.001757055961087092</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004600689920554843</v>
+        <v>0.002126293685552779</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001827338124300223</v>
+        <v>0.001688434458609325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001644515380493603</v>
+        <v>0.001560468740381187</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009917333818493876</v>
+        <v>0.01724139638829264</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003546882173476502</v>
+        <v>0.003484378936563722</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02365734662705007</v>
+        <v>0.008427635701691158</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00433165744879935</v>
+        <v>0.004177676303016972</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003683025112671779</v>
+        <v>0.003506139789765974</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1058258334398891</v>
+        <v>0.08868436874967696</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1650178171755515</v>
+        <v>0.1710982125695913</v>
       </c>
       <c r="M12" t="n">
-        <v>4.069166306475234</v>
+        <v>4.093013469766094</v>
       </c>
       <c r="N12" t="n">
-        <v>4.116738332305455</v>
+        <v>4.126604074582002</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001236844122141616</v>
+        <v>0.001800213726897335</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001893568259837541</v>
+        <v>0.0008823826760775869</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0006708561132844725</v>
+        <v>0.000700945093478875</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001577945078393295</v>
+        <v>0.001946967496435867</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005159289436911813</v>
+        <v>0.000532442307444652</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005180714883698488</v>
+        <v>0.008867500841910507</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005500303970544891</v>
+        <v>0.005381907268634436</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002102540176373066</v>
+        <v>0.002080648051321857</v>
       </c>
       <c r="W12" t="n">
-        <v>0.007123502943990877</v>
+        <v>0.01110148731827411</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001098906384636875</v>
+        <v>0.001245983019224229</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.148515007205576</v>
+        <v>0.1318957320315873</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2205669081358906</v>
+        <v>0.1984051893243407</v>
       </c>
       <c r="M13" t="n">
-        <v>4.284045086843435</v>
+        <v>4.278667842899751</v>
       </c>
       <c r="N13" t="n">
-        <v>4.51367414491185</v>
+        <v>4.516623865074608</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002134332250830006</v>
+        <v>0.002634681722167011</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001761806068326073</v>
+        <v>0.001778379054933948</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001834052754278803</v>
+        <v>0.00141807565870679</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00867864905336191</v>
+        <v>0.008530235426514604</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01479978519774553</v>
+        <v>0.01465555618804882</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01662959998050208</v>
+        <v>0.01970287504993379</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04277330469049109</v>
+        <v>0.04054228414918898</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01475224373249821</v>
+        <v>0.01073997090811244</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02333877682440299</v>
+        <v>0.02059015376665118</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03966562280682006</v>
+        <v>0.03776481177971338</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1727584722120463</v>
+        <v>0.1444543606302343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2990582685016128</v>
+        <v>0.2451095585423392</v>
       </c>
       <c r="M14" t="n">
-        <v>4.415219190537966</v>
+        <v>4.410185119042559</v>
       </c>
       <c r="N14" t="n">
-        <v>4.362336425507728</v>
+        <v>4.353749615886303</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01125534832037346</v>
+        <v>0.01539263045771916</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003607630656927784</v>
+        <v>0.00207988579762189</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01788996516652828</v>
+        <v>0.01191055014334585</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007182597802538842</v>
+        <v>0.006264426285316007</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01121561652147218</v>
+        <v>0.009349428119143155</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02923068112280584</v>
+        <v>0.04642341692197619</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02182599392278025</v>
+        <v>0.0219677894259853</v>
       </c>
       <c r="V14" t="n">
-        <v>0.06322226242153146</v>
+        <v>0.03510718106128886</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01494646419532208</v>
+        <v>0.01414703625545588</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03039923048985699</v>
+        <v>0.02843173217900292</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1895470751595914</v>
+        <v>0.1316028009711741</v>
       </c>
       <c r="L15" t="n">
-        <v>0.29369105404012</v>
+        <v>0.2400705769377274</v>
       </c>
       <c r="M15" t="n">
-        <v>4.12729937470144</v>
+        <v>4.10389600519784</v>
       </c>
       <c r="N15" t="n">
-        <v>4.251286225585371</v>
+        <v>4.22981464645173</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01153787057806632</v>
+        <v>0.01524317318391451</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00491396510312218</v>
+        <v>0.004201389691584724</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01714618352170721</v>
+        <v>0.01199188534607597</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005813051837501348</v>
+        <v>0.004871167445716138</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02602301365812578</v>
+        <v>0.02342819584117343</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03008980968168116</v>
+        <v>0.04633043987740341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01420621379998798</v>
+        <v>0.01580429886900008</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06147698604334072</v>
+        <v>0.03618794928201523</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01289384432520191</v>
+        <v>0.01178828241598582</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0922494979583097</v>
+        <v>0.08084481313307681</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5109637156163565</v>
+        <v>0.5058025943758175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5248228053291905</v>
+        <v>0.511110244244519</v>
       </c>
       <c r="M16" t="n">
-        <v>4.305324632016705</v>
+        <v>4.349769392665977</v>
       </c>
       <c r="N16" t="n">
-        <v>4.499578138446319</v>
+        <v>4.49472646883386</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02795977037058923</v>
+        <v>0.02810439883375163</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01973319386874771</v>
+        <v>0.01938628811915379</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2494908810873907</v>
+        <v>0.05188156448837034</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01289464404103659</v>
+        <v>0.01227263702583894</v>
       </c>
       <c r="S16" t="n">
-        <v>0.03895640810840645</v>
+        <v>0.01882851590407672</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08300044579389146</v>
+        <v>0.1330096261850886</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03064668158106581</v>
+        <v>0.07189983533492456</v>
       </c>
       <c r="V16" t="n">
-        <v>14.77209280393934</v>
+        <v>1.114022073397786</v>
       </c>
       <c r="W16" t="n">
-        <v>0.05918381767874265</v>
+        <v>0.01941348160139615</v>
       </c>
       <c r="X16" t="n">
-        <v>62.19966838387636</v>
+        <v>23.14791809572846</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1374919669067439</v>
+        <v>0.1560962956401372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2308473659312212</v>
+        <v>0.2176141117888516</v>
       </c>
       <c r="M17" t="n">
-        <v>3.873370159099386</v>
+        <v>3.850449758009987</v>
       </c>
       <c r="N17" t="n">
-        <v>4.005862584706665</v>
+        <v>4.003355433840693</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01274779713484942</v>
+        <v>0.01666553333665856</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001087304268477051</v>
+        <v>0.002197486440482451</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0135142453541742</v>
+        <v>0.01002107382384962</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003854742165844369</v>
+        <v>0.003776831460417556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01038510830637266</v>
+        <v>0.01035570677527403</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03437143974099936</v>
+        <v>0.04892807629792244</v>
       </c>
       <c r="U17" t="n">
-        <v>0.04661198334546052</v>
+        <v>0.01617964664858214</v>
       </c>
       <c r="V17" t="n">
-        <v>0.04457607386191233</v>
+        <v>0.02853311470594959</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02445355547810242</v>
+        <v>0.009876345471894084</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02261828801005894</v>
+        <v>0.02039276390262555</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.24258952682581</v>
+        <v>0.181582972876025</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2660266826871621</v>
+        <v>0.2291146013485572</v>
       </c>
       <c r="M18" t="n">
-        <v>4.300562681691318</v>
+        <v>4.287479093745305</v>
       </c>
       <c r="N18" t="n">
-        <v>4.300495078191944</v>
+        <v>4.290261353909024</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0132376709096335</v>
+        <v>0.01753672101882884</v>
       </c>
       <c r="P18" t="n">
-        <v>0.00681129232931395</v>
+        <v>0.006870036782572463</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01171949635204929</v>
+        <v>0.008715530420308126</v>
       </c>
       <c r="R18" t="n">
-        <v>0.00849322490141575</v>
+        <v>0.007720678040889745</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008848764120452022</v>
+        <v>0.008261082358081404</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03396721605044127</v>
+        <v>0.05164777757734745</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01541847042973249</v>
+        <v>0.0180420084871737</v>
       </c>
       <c r="V18" t="n">
-        <v>0.03681490085125969</v>
+        <v>0.02397901788142032</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01494770064066304</v>
+        <v>0.01425800340100273</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01553792814555296</v>
+        <v>0.01484889274857591</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1618647634163979</v>
+        <v>0.1080512787950732</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2267943694544231</v>
+        <v>0.1791781034397167</v>
       </c>
       <c r="M19" t="n">
-        <v>4.01013022703957</v>
+        <v>4.009989320724906</v>
       </c>
       <c r="N19" t="n">
-        <v>4.381077920595329</v>
+        <v>4.370018245738256</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004872206345465319</v>
+        <v>0.006290359912523457</v>
       </c>
       <c r="P19" t="n">
-        <v>0.009584503966047387</v>
+        <v>0.009253317473517224</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.00567637946513994</v>
+        <v>0.004622994132354418</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001511907495789723</v>
+        <v>0.001363803486557137</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03178593550258741</v>
+        <v>0.02918612017959531</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01913960821570984</v>
+        <v>0.02689310905183208</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02404432928852039</v>
+        <v>0.02579526438579246</v>
       </c>
       <c r="V19" t="n">
-        <v>0.01841223697550069</v>
+        <v>0.01428351500742926</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006863433741323773</v>
+        <v>0.00662328925985413</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1605060758022008</v>
+        <v>0.1388125283573169</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.270337140109575</v>
+        <v>0.2057008732256997</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3065526125294156</v>
+        <v>0.252707072651963</v>
       </c>
       <c r="M20" t="n">
-        <v>4.622332151259288</v>
+        <v>4.630704694731168</v>
       </c>
       <c r="N20" t="n">
-        <v>4.58922304767674</v>
+        <v>4.594475229012931</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00785931586429609</v>
+        <v>0.009872294106548635</v>
       </c>
       <c r="P20" t="n">
-        <v>0.001025000800824494</v>
+        <v>1.000000000000019e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.009860404575518641</v>
+        <v>0.007137382040759152</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005480568839047294</v>
+        <v>0.005058806643561632</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01578174284774004</v>
+        <v>0.01312097949495857</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02039597948269816</v>
+        <v>0.0282826994433424</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01580429778794902</v>
+        <v>0.01683493049796974</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03100472001297187</v>
+        <v>0.0203756399269727</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01141743107428418</v>
+        <v>0.01095269707200741</v>
       </c>
       <c r="X20" t="n">
-        <v>0.03092722591672567</v>
+        <v>0.02782289100854413</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1205682193591666</v>
+        <v>0.07288078000139452</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1423733601157885</v>
+        <v>0.136876123227639</v>
       </c>
       <c r="M21" t="n">
-        <v>4.116445283604787</v>
+        <v>4.177714502255803</v>
       </c>
       <c r="N21" t="n">
-        <v>4.12095334053991</v>
+        <v>4.130153181638189</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01478801104066373</v>
+        <v>0.01780058433932053</v>
       </c>
       <c r="P21" t="n">
-        <v>0.04991584459655532</v>
+        <v>0.06021739648152067</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.006895745083284601</v>
+        <v>0.00829291290901191</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000000209e-05</v>
+        <v>1.000000000000064e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.00000000000495e-05</v>
+        <v>1.000000021545476e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05290185517907468</v>
+        <v>0.07839590074529819</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1596640232419171</v>
+        <v>0.2445336871846416</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02511739227185156</v>
+        <v>0.0319129703818624</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0112216396004246</v>
+        <v>0.01285682772051475</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03925832733083881</v>
+        <v>0.05801580626211517</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2807614585076638</v>
+        <v>0.2533994605117408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3240124900058231</v>
+        <v>0.2796877818453221</v>
       </c>
       <c r="M22" t="n">
-        <v>4.13956210274015</v>
+        <v>4.12741070069084</v>
       </c>
       <c r="N22" t="n">
-        <v>4.310404336206148</v>
+        <v>4.298014114122767</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00571654877721342</v>
+        <v>0.006817344245350855</v>
       </c>
       <c r="P22" t="n">
-        <v>1.00000228731639e-05</v>
+        <v>1.000000000000001e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.006856071904564442</v>
+        <v>0.004992983105345955</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003427287695314076</v>
+        <v>0.003196624357946525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0126438157668045</v>
+        <v>0.01205767744382579</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01594674238280221</v>
+        <v>0.02012359538097784</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01521096615998836</v>
+        <v>0.01278669684914623</v>
       </c>
       <c r="V22" t="n">
-        <v>0.02671265268570759</v>
+        <v>0.01845404951752473</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009394481557100728</v>
+        <v>0.008751757135339943</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02780094666908808</v>
+        <v>0.02617809791309104</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2125758680225998</v>
+        <v>0.1677259721457121</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2730812615444278</v>
+        <v>0.235138132867317</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85839694517567</v>
+        <v>3.852888542897317</v>
       </c>
       <c r="N23" t="n">
-        <v>4.109303918133452</v>
+        <v>4.08852238024105</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01072659083934483</v>
+        <v>0.01378907207399461</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004300359945717686</v>
+        <v>0.003850503513362134</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.008953973906172932</v>
+        <v>0.006335179494781582</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006185063060610859</v>
+        <v>0.00502815306776162</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02443520304292202</v>
+        <v>0.02280483930196217</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02759364091948696</v>
+        <v>0.0400842843432053</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01924557130798039</v>
+        <v>0.01951120878469059</v>
       </c>
       <c r="V23" t="n">
-        <v>0.02987848763398218</v>
+        <v>0.01946645806195994</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01567491900785745</v>
+        <v>0.01479487736778822</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07694288199533526</v>
+        <v>0.07018540746802567</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3899491530645845</v>
+        <v>0.3438194492405634</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4738363484336767</v>
+        <v>0.437378249201195</v>
       </c>
       <c r="M24" t="n">
-        <v>4.330915049849626</v>
+        <v>4.306058852366302</v>
       </c>
       <c r="N24" t="n">
-        <v>4.386143874223134</v>
+        <v>4.362088745449129</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01270831934923817</v>
+        <v>0.01423551908088942</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009365876712975773</v>
+        <v>0.009555158334524815</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.09201728505651084</v>
+        <v>0.03731791514541583</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01374423130417479</v>
+        <v>0.0123537954402443</v>
       </c>
       <c r="S24" t="n">
-        <v>1.000000000093162e-05</v>
+        <v>1.000000000000118e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03005267218255816</v>
+        <v>0.04996179553438058</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0174588122687918</v>
+        <v>0.02531212413221801</v>
       </c>
       <c r="V24" t="n">
-        <v>0.957382973086685</v>
+        <v>0.3016128715086063</v>
       </c>
       <c r="W24" t="n">
-        <v>0.022327840589088</v>
+        <v>0.02272787044231356</v>
       </c>
       <c r="X24" t="n">
-        <v>1.070619086120369</v>
+        <v>1.672168558357028</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2158934749426978</v>
+        <v>0.1556531723472595</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288212176259103</v>
+        <v>0.1799981948277626</v>
       </c>
       <c r="M25" t="n">
-        <v>4.311008836928643</v>
+        <v>4.318162033299422</v>
       </c>
       <c r="N25" t="n">
-        <v>4.340698822330908</v>
+        <v>4.341389638091139</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002227050793343374</v>
+        <v>0.002989582916939963</v>
       </c>
       <c r="P25" t="n">
-        <v>1.000000000000249e-05</v>
+        <v>1.000000000013433e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0009272596949026803</v>
+        <v>0.0008429935862196409</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003337747272566673</v>
+        <v>0.0003187777235327907</v>
       </c>
       <c r="S25" t="n">
-        <v>9.830293358068274e-05</v>
+        <v>7.337609308982667e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005445970633114964</v>
+        <v>0.008007604718600316</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002891211546329953</v>
+        <v>0.003273380797079072</v>
       </c>
       <c r="V25" t="n">
-        <v>0.003144059723205296</v>
+        <v>0.002629735058687421</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001343883601891845</v>
+        <v>0.001316430220211471</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001314232368928139</v>
+        <v>0.001298921092651921</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.319605401855295</v>
+        <v>0.2654673820478013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3067566003139182</v>
+        <v>0.2647920494983484</v>
       </c>
       <c r="M26" t="n">
-        <v>4.221808346553291</v>
+        <v>4.203760876198466</v>
       </c>
       <c r="N26" t="n">
-        <v>4.299252264058017</v>
+        <v>4.287929336576728</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002895729894423425</v>
+        <v>0.003553513156912719</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001540869741159283</v>
+        <v>0.001334508429188928</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001530688559659498</v>
+        <v>0.001077203479874421</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005610067201126984</v>
+        <v>0.0004960517045919929</v>
       </c>
       <c r="S26" t="n">
-        <v>0.000320505036665777</v>
+        <v>0.0002768043466932458</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005815480477789379</v>
+        <v>0.007738924825548683</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002436834387079412</v>
+        <v>0.002345317387659328</v>
       </c>
       <c r="V26" t="n">
-        <v>0.005128512473180752</v>
+        <v>0.003423105226798544</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001509443271880516</v>
+        <v>0.001457587125908658</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001258773084795716</v>
+        <v>0.001236541296998774</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2452896402637705</v>
+        <v>0.1860906494832026</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3103151281310915</v>
+        <v>0.2609263764648936</v>
       </c>
       <c r="M27" t="n">
-        <v>4.171003209011483</v>
+        <v>4.150022463863345</v>
       </c>
       <c r="N27" t="n">
-        <v>4.14908671879705</v>
+        <v>4.128377186623956</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001437276480514978</v>
+        <v>0.001717769227681431</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005765645320171647</v>
+        <v>0.0003089896690472835</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.002832226853502619</v>
+        <v>0.002123112731797632</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006441285626390565</v>
+        <v>0.0005393147709790656</v>
       </c>
       <c r="S27" t="n">
-        <v>0.000723606562769694</v>
+        <v>0.0006857694344910315</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003444973016160398</v>
+        <v>0.004504618205352874</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002439560836847509</v>
+        <v>0.002448038014065887</v>
       </c>
       <c r="V27" t="n">
-        <v>0.009038235150673847</v>
+        <v>0.006131222436242601</v>
       </c>
       <c r="W27" t="n">
-        <v>0.00172238019203396</v>
+        <v>0.001627411464295071</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001795122101848619</v>
+        <v>0.001768716077328466</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3983434145777525</v>
+        <v>0.3628997599405132</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4053307112609433</v>
+        <v>0.3889961231312799</v>
       </c>
       <c r="M28" t="n">
-        <v>4.109024811393252</v>
+        <v>4.105048742406989</v>
       </c>
       <c r="N28" t="n">
-        <v>4.291467493787325</v>
+        <v>4.286841258219166</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002072957554302384</v>
+        <v>0.002327585182824392</v>
       </c>
       <c r="P28" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.005863184085985075</v>
+        <v>0.003750470988081168</v>
       </c>
       <c r="R28" t="n">
-        <v>0.004994582163527573</v>
+        <v>0.004891282785943639</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0103342467062638</v>
+        <v>0.01004340971661274</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004751802764048289</v>
+        <v>0.005731329136174606</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01082368026150989</v>
+        <v>0.01051632903110562</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01889566661618548</v>
+        <v>0.01066528431710511</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009508319048192264</v>
+        <v>0.01008378282648866</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02337550559569725</v>
+        <v>0.02286036847442736</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5340055862294603</v>
+        <v>0.5406426407248554</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3537511708827761</v>
+        <v>0.5160117356780172</v>
       </c>
       <c r="M29" t="n">
-        <v>4.257333241600258</v>
+        <v>4.311389929681745</v>
       </c>
       <c r="N29" t="n">
-        <v>4.213034118342315</v>
+        <v>4.268701719023421</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004706119344066876</v>
+        <v>0.004208460938638278</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01781406183477655</v>
+        <v>0.01898441589271225</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.001112501966933918</v>
+        <v>0.001118501547823159</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01718721293510463</v>
+        <v>0.02092074429580722</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009435734175553634</v>
+        <v>0.01041158193496168</v>
       </c>
       <c r="T29" t="n">
-        <v>0.008991775749481973</v>
+        <v>0.007153637877931236</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06048863068591687</v>
+        <v>0.0741560046989375</v>
       </c>
       <c r="V29" t="n">
-        <v>0.009328677827489671</v>
+        <v>0.004328849056691108</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03271838197794723</v>
+        <v>0.04647781886524555</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01595010890889274</v>
+        <v>0.01790096064573862</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4943630247919256</v>
+        <v>0.4607304856375613</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4068925873055509</v>
+        <v>0.4543013235556531</v>
       </c>
       <c r="M30" t="n">
-        <v>4.508966688135797</v>
+        <v>4.513720172905545</v>
       </c>
       <c r="N30" t="n">
-        <v>4.315230370276968</v>
+        <v>4.32303836590311</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002582538463188679</v>
+        <v>0.002701764263880254</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005210999333369798</v>
+        <v>0.005069376756646178</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00178291325763776</v>
+        <v>0.0009641508591327167</v>
       </c>
       <c r="R30" t="n">
-        <v>0.009395269430449356</v>
+        <v>0.0096988047111842</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00423607094647921</v>
+        <v>0.004500642032621628</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004948356639668149</v>
+        <v>0.005321573953414356</v>
       </c>
       <c r="U30" t="n">
-        <v>0.009468897455161546</v>
+        <v>0.00908723102903955</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01415929849040101</v>
+        <v>0.007022148398314661</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01535040043333628</v>
+        <v>0.01624545057413348</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005622001961398414</v>
+        <v>0.006068707230812009</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4901448304506785</v>
+        <v>0.4758642080817636</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307997022511386</v>
+        <v>0.4406806010885068</v>
       </c>
       <c r="M31" t="n">
-        <v>4.249026147841872</v>
+        <v>4.25445111063005</v>
       </c>
       <c r="N31" t="n">
-        <v>4.408930889587362</v>
+        <v>4.40692901143991</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002771812191914096</v>
+        <v>0.002896833466915962</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007349276814842575</v>
+        <v>0.006979953479778965</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.001566470648079969</v>
+        <v>0.0008208872974695813</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001811076871221427</v>
+        <v>0.001813080468693583</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005777036260591665</v>
+        <v>0.0005815794138276866</v>
       </c>
       <c r="T31" t="n">
-        <v>0.005009747952420827</v>
+        <v>0.005378205838510211</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01717453529252223</v>
+        <v>0.01520734795926888</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01294604338786009</v>
+        <v>0.006290688468045455</v>
       </c>
       <c r="W31" t="n">
-        <v>0.002981214292240811</v>
+        <v>0.003101129852167588</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002777060325854031</v>
+        <v>0.002830260208189001</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003028185540506</v>
+        <v>0.4784031200138491</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4274257323699956</v>
+        <v>0.4392796549618741</v>
       </c>
       <c r="M32" t="n">
-        <v>4.530139452862152</v>
+        <v>4.543747350314697</v>
       </c>
       <c r="N32" t="n">
-        <v>4.426366733301174</v>
+        <v>4.423271470040162</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008333218414156414</v>
+        <v>0.0009142669654756379</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005242317589998033</v>
+        <v>0.005177174879196569</v>
       </c>
       <c r="Q32" t="n">
         <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00440900614646704</v>
+        <v>0.004553087041111755</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00139890869216171</v>
+        <v>0.001421900330206515</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002812879990652049</v>
+        <v>0.003079277993690341</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01135121579130941</v>
+        <v>0.01090292616308419</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0112527633064123</v>
+        <v>0.00690587100610414</v>
       </c>
       <c r="W32" t="n">
-        <v>0.008038982106448744</v>
+        <v>0.008675892082943424</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003574017750836421</v>
+        <v>0.003638539412270129</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2845720576653915</v>
+        <v>0.2253351707878397</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3094853665471586</v>
+        <v>0.2837466557410158</v>
       </c>
       <c r="M33" t="n">
-        <v>4.300519149462805</v>
+        <v>4.284692602034447</v>
       </c>
       <c r="N33" t="n">
-        <v>4.268789356988536</v>
+        <v>4.261031171421288</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006459786430733619</v>
+        <v>0.008115100619960626</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00399209826014126</v>
+        <v>0.002125819784889603</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.008740491515353622</v>
+        <v>0.006162918274277718</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00740634246084285</v>
+        <v>0.006758154152190116</v>
       </c>
       <c r="S33" t="n">
-        <v>0.004069966116854634</v>
+        <v>0.003724652038501375</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01754609504531611</v>
+        <v>0.02613761107579867</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02441502329541632</v>
+        <v>0.01992965701022312</v>
       </c>
       <c r="V33" t="n">
-        <v>0.03359882083314529</v>
+        <v>0.01973016690136992</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01425906458768727</v>
+        <v>0.01427286197100559</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007911558518548282</v>
+        <v>0.007611593408086906</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5337173211659239</v>
+        <v>0.5349204065807047</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4594789794307157</v>
+        <v>0.5197406872727356</v>
       </c>
       <c r="M34" t="n">
-        <v>4.254011730907492</v>
+        <v>4.266981556961285</v>
       </c>
       <c r="N34" t="n">
-        <v>4.290063054664384</v>
+        <v>4.309138203257641</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005293537958390806</v>
+        <v>0.00628782296019729</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01449325049678961</v>
+        <v>0.01467439651491651</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.02173365729682402</v>
+        <v>0.004578528656272019</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01405915792835894</v>
+        <v>0.0169074716336018</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008223738851225243</v>
+        <v>0.01007384153344677</v>
       </c>
       <c r="T34" t="n">
-        <v>0.007883139557382282</v>
+        <v>0.009936572049361467</v>
       </c>
       <c r="U34" t="n">
-        <v>0.05427348058791771</v>
+        <v>0.05720527863386792</v>
       </c>
       <c r="V34" t="n">
-        <v>0.08259749265859682</v>
+        <v>0.007451586020058591</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01769669622720369</v>
+        <v>0.02172882129978074</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00716031978545314</v>
+        <v>0.008510070342187705</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3017567405934108</v>
+        <v>0.2503626538263644</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2446039175795452</v>
+        <v>0.2453795286280497</v>
       </c>
       <c r="M35" t="n">
-        <v>4.047146068348874</v>
+        <v>4.042303821541178</v>
       </c>
       <c r="N35" t="n">
-        <v>4.156055410298507</v>
+        <v>4.151387123043699</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002591332400424746</v>
+        <v>0.003414373605622675</v>
       </c>
       <c r="P35" t="n">
-        <v>0.05839057765869057</v>
+        <v>0.07099712768706633</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.001164952168749607</v>
+        <v>0.0008715678302221226</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004759437049525006</v>
+        <v>0.004589076205805081</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009506602365975521</v>
+        <v>0.0009287545709174635</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01243090473175927</v>
+        <v>0.01611089855860847</v>
       </c>
       <c r="U35" t="n">
-        <v>26.22187932220613</v>
+        <v>37.08922309558062</v>
       </c>
       <c r="V35" t="n">
-        <v>0.006920718809434856</v>
+        <v>0.00412076659259366</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0224981326684356</v>
+        <v>0.01603199649632354</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002626807572345213</v>
+        <v>0.002516073717486858</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4303510992459229</v>
+        <v>0.3952543891983995</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3939800805864314</v>
+        <v>0.3747781148056714</v>
       </c>
       <c r="M36" t="n">
-        <v>4.305403694774172</v>
+        <v>4.294431636644179</v>
       </c>
       <c r="N36" t="n">
-        <v>4.32080620179621</v>
+        <v>4.314044964815882</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001354609422965776</v>
+        <v>0.001492384113974396</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002766124108187839</v>
+        <v>0.002641666187450695</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.001606529954626481</v>
+        <v>0.001017956687124919</v>
       </c>
       <c r="R36" t="n">
-        <v>0.00193283348767519</v>
+        <v>0.001818642362291593</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001309712328047509</v>
+        <v>0.001238512457880979</v>
       </c>
       <c r="T36" t="n">
-        <v>0.00357449806879154</v>
+        <v>0.00410114037856216</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006171265407889702</v>
+        <v>0.005823012244503736</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01083814594914742</v>
+        <v>0.006833825909894108</v>
       </c>
       <c r="W36" t="n">
-        <v>0.00360372821623126</v>
+        <v>0.003536142813104424</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004516753479447161</v>
+        <v>0.004460046111833033</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1033156315000568</v>
+        <v>0.05739037544262496</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1059828642371518</v>
+        <v>0.07231248674386465</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2322895226395</v>
+        <v>4.220030963149969</v>
       </c>
       <c r="N37" t="n">
-        <v>4.263470541648745</v>
+        <v>4.254880235658854</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007601944601201592</v>
+        <v>0.01409299383830764</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003361003954592212</v>
+        <v>0.003954565711144898</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001413775568260181</v>
+        <v>0.001232243063209071</v>
       </c>
       <c r="R37" t="n">
-        <v>0.000843397419013481</v>
+        <v>0.0007393673710214549</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002269007126178266</v>
+        <v>0.00195348610883983</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02835794664986396</v>
+        <v>0.06179369845426744</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009377544212304727</v>
+        <v>0.01511853165498354</v>
       </c>
       <c r="V37" t="n">
-        <v>0.004401015687790313</v>
+        <v>0.003600815012614599</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002560594535593874</v>
+        <v>0.002463416353803291</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005732714442660184</v>
+        <v>0.005022231249432033</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1414949912042679</v>
+        <v>0.08860067203198282</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1087290221050649</v>
+        <v>0.07286588812336381</v>
       </c>
       <c r="M38" t="n">
-        <v>4.109497407226164</v>
+        <v>4.08380765192147</v>
       </c>
       <c r="N38" t="n">
-        <v>4.195576882556786</v>
+        <v>4.186742415431928</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009466158791810689</v>
+        <v>0.01816598417491</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002600888321473296</v>
+        <v>0.004227706630053943</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0008554167754102429</v>
+        <v>0.0007082095574105887</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004639389345015955</v>
+        <v>0.0003633383539267042</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003912853955704609</v>
+        <v>1.164662717910109e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.03180668575211528</v>
+        <v>0.06979823262080743</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009225924844419304</v>
+        <v>0.01794262277099509</v>
       </c>
       <c r="V38" t="n">
-        <v>0.003383070468159375</v>
+        <v>0.002774645470050516</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002123099521003483</v>
+        <v>0.00204844995178657</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003150037007840459</v>
+        <v>0.002560507964710769</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514588065490762</v>
+        <v>0.09603082938732513</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1342305756371794</v>
+        <v>0.09754471230093976</v>
       </c>
       <c r="M39" t="n">
-        <v>4.258033543989585</v>
+        <v>4.238213191185915</v>
       </c>
       <c r="N39" t="n">
-        <v>4.266426390932311</v>
+        <v>4.25765369969348</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006470581946873035</v>
+        <v>0.01071137263928643</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002042234687859863</v>
+        <v>0.001961444739868802</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001427725333833631</v>
+        <v>0.001207864357196952</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002326252982001576</v>
+        <v>0.002111422013714206</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001422625470839602</v>
+        <v>0.001326087434818644</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01696030028570612</v>
+        <v>0.03147823833097897</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009743853811556683</v>
+        <v>0.01336011302082606</v>
       </c>
       <c r="V39" t="n">
-        <v>0.004199213581852069</v>
+        <v>0.003477579320632029</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004036201977016299</v>
+        <v>0.00389078326458341</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003023760583938646</v>
+        <v>0.002971047251071547</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2387698264019981</v>
+        <v>0.218083522895272</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3956825352388806</v>
+        <v>0.3846724701350712</v>
       </c>
       <c r="M40" t="n">
-        <v>4.328495843657492</v>
+        <v>4.338385918030463</v>
       </c>
       <c r="N40" t="n">
-        <v>4.521598307569784</v>
+        <v>4.514872051921762</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004141366185699709</v>
+        <v>0.004734518986587938</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002630245184229858</v>
+        <v>0.002302196428921594</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.008507641359775022</v>
+        <v>0.005122107454131429</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002450527941873048</v>
+        <v>0.002367993380255572</v>
       </c>
       <c r="S40" t="n">
-        <v>0.05435511079335989</v>
+        <v>0.04895581188028639</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008166940448019633</v>
+        <v>0.01005684707481663</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004233563662852916</v>
+        <v>0.003795106322111856</v>
       </c>
       <c r="V40" t="n">
-        <v>0.0277448184869841</v>
+        <v>0.01434562330737222</v>
       </c>
       <c r="W40" t="n">
-        <v>0.003730238184086705</v>
+        <v>0.003731335972206004</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2590994290714659</v>
+        <v>0.2315607548645489</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2578829215911677</v>
+        <v>0.195968443087551</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2872888548942679</v>
+        <v>0.2459191158747739</v>
       </c>
       <c r="M41" t="n">
-        <v>4.435301806859223</v>
+        <v>4.44269170170953</v>
       </c>
       <c r="N41" t="n">
-        <v>4.505865362691527</v>
+        <v>4.503036302764246</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001885877375446798</v>
+        <v>0.002317709688281154</v>
       </c>
       <c r="P41" t="n">
-        <v>0.003090226968247373</v>
+        <v>0.002599174120601318</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.002032213311689036</v>
+        <v>0.001514245590003984</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009525834802123272</v>
+        <v>0.0008795098894913764</v>
       </c>
       <c r="S41" t="n">
-        <v>0.00394716397471301</v>
+        <v>0.003634776313891874</v>
       </c>
       <c r="T41" t="n">
-        <v>0.004721541871466996</v>
+        <v>0.006353219210752181</v>
       </c>
       <c r="U41" t="n">
-        <v>0.00524317454898725</v>
+        <v>0.004715218570472433</v>
       </c>
       <c r="V41" t="n">
-        <v>0.00595275449814794</v>
+        <v>0.004150081423463792</v>
       </c>
       <c r="W41" t="n">
-        <v>0.00214361476577934</v>
+        <v>0.002073064051156007</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006966234404942577</v>
+        <v>0.006552049059421441</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.277385678721059</v>
+        <v>0.1441683716926044</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4383678837373725</v>
+        <v>0.3899771823117972</v>
       </c>
       <c r="M42" t="n">
-        <v>4.541320208590085</v>
+        <v>2.686505160363577</v>
       </c>
       <c r="N42" t="n">
-        <v>4.559186423294103</v>
+        <v>4.454623603050445</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004705710918496453</v>
+        <v>0.005364330611886858</v>
       </c>
       <c r="P42" t="n">
-        <v>0.003876279332582651</v>
+        <v>0.003030304522746277</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01857064230759505</v>
+        <v>0.01060956910122831</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003052553016029436</v>
+        <v>0.002858888520482701</v>
       </c>
       <c r="S42" t="n">
-        <v>1e-05</v>
+        <v>0.3384617058731676</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01259720908775944</v>
+        <v>0.01623224108036893</v>
       </c>
       <c r="U42" t="n">
-        <v>0.009059050116525634</v>
+        <v>0.01076633795144252</v>
       </c>
       <c r="V42" t="n">
-        <v>0.08843077978423618</v>
+        <v>0.04863460963850247</v>
       </c>
       <c r="W42" t="n">
-        <v>0.006262541837585448</v>
+        <v>0.006709909277476691</v>
       </c>
       <c r="X42" t="n">
-        <v>0.5431002981913414</v>
+        <v>4274.098996495557</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1503222139950792</v>
+        <v>0.1272625710749767</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3686132989106535</v>
+        <v>0.2928974500929452</v>
       </c>
       <c r="M43" t="n">
-        <v>4.014610252289849</v>
+        <v>3.9221433094044</v>
       </c>
       <c r="N43" t="n">
-        <v>4.251204890422223</v>
+        <v>4.22516973289385</v>
       </c>
       <c r="O43" t="n">
-        <v>0.02407732618856541</v>
+        <v>0.04759847288116823</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01359415067763194</v>
+        <v>0.01439222034535242</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.05916084326513653</v>
+        <v>0.02371542099818499</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02190333776307291</v>
+        <v>0.01582124408532712</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06097075169211408</v>
+        <v>0.05589968844383721</v>
       </c>
       <c r="T43" t="n">
-        <v>0.05850073955802389</v>
+        <v>0.1547121186223338</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02077956282061677</v>
+        <v>0.0241070585282844</v>
       </c>
       <c r="V43" t="n">
-        <v>0.2311450064487306</v>
+        <v>0.06890128083277684</v>
       </c>
       <c r="W43" t="n">
-        <v>0.03758231622513954</v>
+        <v>0.03770391068065179</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1655365740693592</v>
+        <v>0.1522902869529593</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1750004298657557</v>
+        <v>0.1168265495049782</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3277841145113169</v>
+        <v>0.2997327023322942</v>
       </c>
       <c r="M44" t="n">
-        <v>4.26677501303533</v>
+        <v>4.250053691127665</v>
       </c>
       <c r="N44" t="n">
-        <v>4.388906099140782</v>
+        <v>4.369655603421465</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05523841796833086</v>
+        <v>0.08685026361533522</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02242912332517252</v>
+        <v>0.02682898621294981</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04130001213799385</v>
+        <v>0.02705206182328824</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01124542818330652</v>
+        <v>0.01017648877893654</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02245171420635166</v>
+        <v>0.01900367150708703</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1662677252229182</v>
+        <v>0.3107426153187798</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04069814013028705</v>
+        <v>0.06515612897456106</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1496235450402074</v>
+        <v>0.07949079146785069</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02142311010372736</v>
+        <v>0.02043865642472508</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04611776250969853</v>
+        <v>0.039270011428226</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3970700662958236</v>
+        <v>0.3530798955686953</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3269920361240056</v>
+        <v>0.4388472945079925</v>
       </c>
       <c r="M45" t="n">
-        <v>4.224020019874794</v>
+        <v>4.170472779500921</v>
       </c>
       <c r="N45" t="n">
-        <v>4.376588707455891</v>
+        <v>4.433088135609349</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1183172323013069</v>
+        <v>0.1807364622369918</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1290516876741385</v>
+        <v>0.1528338742228456</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.151567191082598</v>
+        <v>0.07482038086892241</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09413662262835801</v>
+        <v>0.08777549654071587</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1138836702494154</v>
+        <v>0.1085122831761504</v>
       </c>
       <c r="T45" t="n">
-        <v>0.5422051448390474</v>
+        <v>1.153023632505882</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4101037140660773</v>
+        <v>0.6138067585891148</v>
       </c>
       <c r="V45" t="n">
-        <v>1.106649450776112</v>
+        <v>0.3250142105320909</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2716016590243724</v>
+        <v>0.2461268743862165</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4490887177443214</v>
+        <v>0.4015819041937621</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4191548341898909</v>
+        <v>0.4067201208266214</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4168528808457668</v>
+        <v>0.465094401034203</v>
       </c>
       <c r="M46" t="n">
-        <v>3.769550246054656</v>
+        <v>3.808282305100428</v>
       </c>
       <c r="N46" t="n">
-        <v>4.479216138634888</v>
+        <v>4.469208613927203</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06815244606365466</v>
+        <v>0.08059038517937758</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04363101644153401</v>
+        <v>0.04943361346132352</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1115269200480784</v>
+        <v>0.04460463973866373</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03506941055577647</v>
+        <v>0.03545861834688241</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1766596998023533</v>
+        <v>0.1655978876784426</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1839301078095844</v>
+        <v>0.2358430308776615</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08708392857054373</v>
+        <v>0.10470355008253</v>
       </c>
       <c r="V46" t="n">
-        <v>0.4252814507212731</v>
+        <v>0.1164883164149852</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05383642207826184</v>
+        <v>0.05657768721927307</v>
       </c>
       <c r="X46" t="n">
-        <v>1.852554806219026</v>
+        <v>1.589133733935244</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2534470292225203</v>
+        <v>0.1898361565792907</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3811388062430823</v>
+        <v>0.3170324206859707</v>
       </c>
       <c r="M47" t="n">
-        <v>4.285238971656212</v>
+        <v>4.207363086855939</v>
       </c>
       <c r="N47" t="n">
-        <v>4.355084664189493</v>
+        <v>4.332319379528892</v>
       </c>
       <c r="O47" t="n">
-        <v>0.03719789115727632</v>
+        <v>0.06418753791702034</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0192020824216369</v>
+        <v>0.02508102916053349</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.06126978512097164</v>
+        <v>0.02591344311583163</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01798217060741234</v>
+        <v>0.01427090144933693</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02701672834624705</v>
+        <v>0.02075426605287888</v>
       </c>
       <c r="T47" t="n">
-        <v>0.0922260101293388</v>
+        <v>0.1957143218236412</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03184278833795193</v>
+        <v>0.05752413428380904</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2514649973089039</v>
+        <v>0.07869034439131588</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03095129787733047</v>
+        <v>0.026470205203441</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04978584852880755</v>
+        <v>0.03976262882243074</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1132798991704734</v>
+        <v>0.07057579079882771</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3961852980358451</v>
+        <v>0.4745752762180548</v>
       </c>
       <c r="M48" t="n">
-        <v>3.703826593445649</v>
+        <v>3.801459647451884</v>
       </c>
       <c r="N48" t="n">
-        <v>4.328103045292792</v>
+        <v>4.347047091259896</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03608141213484152</v>
+        <v>0.03929900350856486</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05217034402924473</v>
+        <v>0.05417157240514107</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1190733979486861</v>
+        <v>0.1241591739825809</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03932959554243818</v>
+        <v>0.04530971811799489</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2373343859913021</v>
+        <v>0.2256831012710456</v>
       </c>
       <c r="T48" t="n">
-        <v>0.105073370176132</v>
+        <v>0.1231249764716775</v>
       </c>
       <c r="U48" t="n">
-        <v>0.115918779459669</v>
+        <v>0.1222769913184401</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5973731506809006</v>
+        <v>0.5210320119382282</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08880654171337501</v>
+        <v>0.08483266795404527</v>
       </c>
       <c r="X48" t="n">
-        <v>5.873755705300761</v>
+        <v>4.519125382949449</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3104389713261221</v>
+        <v>0.3223441909441093</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4661903841014798</v>
+        <v>0.4530260037366964</v>
       </c>
       <c r="M49" t="n">
-        <v>4.067105644874856</v>
+        <v>4.043607044971687</v>
       </c>
       <c r="N49" t="n">
-        <v>4.397535410259387</v>
+        <v>4.383995846359112</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0195800640648723</v>
+        <v>0.02183775125969165</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01184954805723922</v>
+        <v>0.01220224553277607</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1116541917950874</v>
+        <v>0.04905244273263658</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0181838818403872</v>
+        <v>0.01733682755285186</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09474574817526989</v>
+        <v>0.08667373452157981</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03797539827685248</v>
+        <v>0.04638903603515153</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01669329196316697</v>
+        <v>0.01621107564724511</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4475239439399956</v>
+        <v>0.1646129563276379</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02679993955553984</v>
+        <v>0.02761662630678731</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3310683530183063</v>
+        <v>0.291923069261095</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5041804397675377</v>
+        <v>0.4969413621409701</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5283724817625948</v>
+        <v>0.5558011348926327</v>
       </c>
       <c r="M50" t="n">
-        <v>4.245466267633814</v>
+        <v>4.269727495470134</v>
       </c>
       <c r="N50" t="n">
-        <v>4.524558493791908</v>
+        <v>4.552559913109352</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0870643850815126</v>
+        <v>0.07522103933914269</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06649343178727672</v>
+        <v>0.0637517630761114</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4950957030827258</v>
+        <v>0.2161791793253504</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03299544411367916</v>
+        <v>0.03211954590151369</v>
       </c>
       <c r="S50" t="n">
-        <v>0.004429056687361941</v>
+        <v>0.00349161940464249</v>
       </c>
       <c r="T50" t="n">
-        <v>0.0002369187574658769</v>
+        <v>0.2223535233103695</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1340819236589611</v>
+        <v>0.1196406222358911</v>
       </c>
       <c r="V50" t="n">
-        <v>2.297132503872639</v>
+        <v>0.8772386404210584</v>
       </c>
       <c r="W50" t="n">
-        <v>0.06795212325910853</v>
+        <v>0.05071067091516898</v>
       </c>
       <c r="X50" t="n">
-        <v>0.2650505668175427</v>
+        <v>0.6121742521796609</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.403137792451537</v>
+        <v>0.4799319100595422</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4653196877428078</v>
+        <v>0.5535747883704961</v>
       </c>
       <c r="M51" t="n">
-        <v>3.865900326542421</v>
+        <v>3.888757795315895</v>
       </c>
       <c r="N51" t="n">
-        <v>4.48384234197186</v>
+        <v>4.442650024333787</v>
       </c>
       <c r="O51" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.07935799048627404</v>
       </c>
       <c r="P51" t="n">
-        <v>0.08714068819845351</v>
+        <v>0.04976419921806362</v>
       </c>
       <c r="Q51" t="n">
         <v>0.4999999999999999</v>
       </c>
       <c r="R51" t="n">
-        <v>0.11180265482878</v>
+        <v>0.07574123568963934</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.2295652459480341</v>
       </c>
       <c r="T51" t="n">
-        <v>35.70558667471899</v>
+        <v>0.2280422724283145</v>
       </c>
       <c r="U51" t="n">
-        <v>0.3389177667722044</v>
+        <v>0.1018793922183666</v>
       </c>
       <c r="V51" t="n">
-        <v>6.343129710584399</v>
+        <v>2.075309702285547</v>
       </c>
       <c r="W51" t="n">
-        <v>0.6244297718457708</v>
+        <v>0.1435815110654676</v>
       </c>
       <c r="X51" t="n">
-        <v>28.98723405653553</v>
+        <v>2.706024554128635</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1606943136811414</v>
+        <v>0.1030582047638746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3258488121138525</v>
+        <v>0.245699661210445</v>
       </c>
       <c r="M52" t="n">
-        <v>4.367592709598685</v>
+        <v>4.3471512475704</v>
       </c>
       <c r="N52" t="n">
-        <v>4.304345849735195</v>
+        <v>4.27932093195647</v>
       </c>
       <c r="O52" t="n">
-        <v>0.01559011913636744</v>
+        <v>0.0229852753930611</v>
       </c>
       <c r="P52" t="n">
-        <v>0.008592507796055511</v>
+        <v>0.009271876120134291</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.02659308178128166</v>
+        <v>0.01502695579423551</v>
       </c>
       <c r="R52" t="n">
-        <v>0.005967432658001913</v>
+        <v>0.004501576941872644</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01993959391141046</v>
+        <v>0.01479814432843962</v>
       </c>
       <c r="T52" t="n">
-        <v>0.03672823729495082</v>
+        <v>0.06729399446284115</v>
       </c>
       <c r="U52" t="n">
-        <v>0.0166197342823487</v>
+        <v>0.02228388908260022</v>
       </c>
       <c r="V52" t="n">
-        <v>0.0858232788430276</v>
+        <v>0.04123251203429341</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01435306706455114</v>
+        <v>0.01298268692998369</v>
       </c>
       <c r="X52" t="n">
-        <v>0.04672440451977132</v>
+        <v>0.04302576643890685</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3301843999480364</v>
+        <v>0.2718345787311342</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2240901512487175</v>
+        <v>0.2630965545361177</v>
       </c>
       <c r="M53" t="n">
-        <v>4.38210137775019</v>
+        <v>4.337572452346413</v>
       </c>
       <c r="N53" t="n">
-        <v>4.426651157655445</v>
+        <v>4.431692220656839</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03852063928316336</v>
+        <v>0.05656158564803275</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02203292985472621</v>
+        <v>0.02557519882363565</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01662066593722407</v>
+        <v>0.01213188865711044</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02157825212368393</v>
+        <v>0.02115337376842716</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06492062944712745</v>
+        <v>0.05978724444164666</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08361079889747045</v>
+        <v>0.1460636694518522</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03750899195664795</v>
+        <v>0.05095372448969718</v>
       </c>
       <c r="V53" t="n">
-        <v>0.04232456896730836</v>
+        <v>0.02595519905024486</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03674217385693565</v>
+        <v>0.03783415389952461</v>
       </c>
       <c r="X53" t="n">
-        <v>0.0833636015477511</v>
+        <v>0.07653218184976915</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1364187938617844</v>
+        <v>0.1304722568169745</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4114960935501225</v>
+        <v>0.3942531241048626</v>
       </c>
       <c r="M54" t="n">
-        <v>4.231856710657762</v>
+        <v>4.211287370114428</v>
       </c>
       <c r="N54" t="n">
-        <v>4.304873160013968</v>
+        <v>4.290170541386825</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02910654022717292</v>
+        <v>0.03621852398722265</v>
       </c>
       <c r="P54" t="n">
-        <v>0.009243086630634095</v>
+        <v>0.009646948612388845</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.07255981861292519</v>
+        <v>0.04408360131137274</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009067833061688037</v>
+        <v>0.008477236847220923</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02310987300211455</v>
+        <v>0.02180233863666013</v>
       </c>
       <c r="T54" t="n">
-        <v>0.07128378914059678</v>
+        <v>0.1020262134181514</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01705502859555651</v>
+        <v>0.01760260459424834</v>
       </c>
       <c r="V54" t="n">
-        <v>0.2943742743972195</v>
+        <v>0.1524678483153258</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01638544768323177</v>
+        <v>0.0171181266676</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04201567078519512</v>
+        <v>0.040619412340708</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0949000769531866</v>
+        <v>0.06740234337865914</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4231232279039885</v>
+        <v>0.4432166279653624</v>
       </c>
       <c r="M55" t="n">
-        <v>4.425812673917372</v>
+        <v>4.447550900380854</v>
       </c>
       <c r="N55" t="n">
-        <v>4.387990122460482</v>
+        <v>4.384192390887899</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02018013346376439</v>
+        <v>0.02156334665445141</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009946550188878916</v>
+        <v>0.0103212568109287</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.08210655172856671</v>
+        <v>0.07515129322328908</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01297656494219324</v>
+        <v>0.01365002697296463</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01212401297244044</v>
+        <v>0.01343146585206332</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04517608153037267</v>
+        <v>0.05172919979320922</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01531409660371437</v>
+        <v>0.01593233673197135</v>
       </c>
       <c r="V55" t="n">
-        <v>0.3407612491355209</v>
+        <v>0.2976349655186854</v>
       </c>
       <c r="W55" t="n">
-        <v>0.01846199273579462</v>
+        <v>0.01972513562497009</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02293597909263046</v>
+        <v>0.02423092766794174</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2084054602031741</v>
+        <v>0.1490350938530598</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3600930313309837</v>
+        <v>0.3130003395004233</v>
       </c>
       <c r="M56" t="n">
-        <v>4.062930613106723</v>
+        <v>4.00125006971951</v>
       </c>
       <c r="N56" t="n">
-        <v>4.325495710244655</v>
+        <v>4.300990731249425</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02210648824806744</v>
+        <v>0.03136166837880883</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01176598458901091</v>
+        <v>0.01355636486177632</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.04075638105339113</v>
+        <v>0.02257138592356472</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01410140152206501</v>
+        <v>0.0124107588552113</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04455726009686568</v>
+        <v>0.04142768918841687</v>
       </c>
       <c r="T56" t="n">
-        <v>0.05061686586084162</v>
+        <v>0.08888577867181016</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02061985347214569</v>
+        <v>0.02906462288831178</v>
       </c>
       <c r="V56" t="n">
-        <v>0.1520098973950142</v>
+        <v>0.06936069911019119</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02442111072520134</v>
+        <v>0.02280688940987835</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1119627520468515</v>
+        <v>0.105269825361745</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3825163888057561</v>
+        <v>0.3369187868683771</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4558533320374499</v>
+        <v>0.4319675110610038</v>
       </c>
       <c r="M57" t="n">
-        <v>4.276433697976676</v>
+        <v>4.255979924055767</v>
       </c>
       <c r="N57" t="n">
-        <v>4.373380090074489</v>
+        <v>4.360443573573453</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02538363146635662</v>
+        <v>0.02937663718189853</v>
       </c>
       <c r="P57" t="n">
-        <v>0.00997545735538052</v>
+        <v>0.01073015857585876</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.08595078289326201</v>
+        <v>0.03711489628129596</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01385699480007947</v>
+        <v>0.01290305073225852</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02163546040652497</v>
+        <v>0.01943423316834082</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05255138351840975</v>
+        <v>0.06500580921654261</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01630445804602742</v>
+        <v>0.01887041573001512</v>
       </c>
       <c r="V57" t="n">
-        <v>0.3264916220278885</v>
+        <v>0.1153641534422299</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02010057229666719</v>
+        <v>0.01963561255385254</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03345048501093955</v>
+        <v>0.03083073092316636</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.07740090498216672</v>
+        <v>0.07176931293700975</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4686578136586437</v>
+        <v>0.4700019069046773</v>
       </c>
       <c r="M58" t="n">
-        <v>4.225917546295505</v>
+        <v>4.208071932580222</v>
       </c>
       <c r="N58" t="n">
-        <v>4.399910791868061</v>
+        <v>4.392028852053976</v>
       </c>
       <c r="O58" t="n">
-        <v>0.05115586872456744</v>
+        <v>0.06001533920863211</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01056689686493179</v>
+        <v>0.01060277540358777</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.1695130321053566</v>
+        <v>0.1079954602932957</v>
       </c>
       <c r="R58" t="n">
-        <v>0.007709478013053325</v>
+        <v>0.007488949426304055</v>
       </c>
       <c r="S58" t="n">
-        <v>0.04347199380854039</v>
+        <v>0.04174377540960261</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1456320596511286</v>
+        <v>0.1903187406505568</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02010374954440855</v>
+        <v>0.0204949994476919</v>
       </c>
       <c r="V58" t="n">
-        <v>1.091195420794422</v>
+        <v>0.5737975238732927</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01796724233466184</v>
+        <v>0.01835105472137644</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09615967060313067</v>
+        <v>0.09349028426158587</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4677808511850242</v>
+        <v>0.4429337950329169</v>
       </c>
       <c r="L59" t="n">
-        <v>0.515649168052881</v>
+        <v>0.5117118598911705</v>
       </c>
       <c r="M59" t="n">
-        <v>4.211580767596805</v>
+        <v>4.170892786605078</v>
       </c>
       <c r="N59" t="n">
-        <v>4.385713492739145</v>
+        <v>4.382706479156165</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01105778307330017</v>
+        <v>0.012938841595171</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004345440540321473</v>
+        <v>0.004588499984797221</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1144390838443708</v>
+        <v>0.02889084174910219</v>
       </c>
       <c r="R59" t="n">
-        <v>0.006022792112750541</v>
+        <v>0.005694087223939987</v>
       </c>
       <c r="S59" t="n">
-        <v>0.007022642699285349</v>
+        <v>0.006522554144210779</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01886039609919973</v>
+        <v>0.02353707247088712</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005461442732465875</v>
+        <v>0.006009502286765845</v>
       </c>
       <c r="V59" t="n">
-        <v>0.4198095712585483</v>
+        <v>0.07877091497965838</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005860135464004924</v>
+        <v>0.005677728764287528</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006622152778646</v>
+        <v>0.006298999300228241</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3189569329734549</v>
+        <v>0.2695921991018025</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2352244177000707</v>
+        <v>0.2149184850172595</v>
       </c>
       <c r="M60" t="n">
-        <v>4.034948938354199</v>
+        <v>4.021231498279722</v>
       </c>
       <c r="N60" t="n">
-        <v>4.20670577107314</v>
+        <v>4.205633539409629</v>
       </c>
       <c r="O60" t="n">
-        <v>0.005140916073778912</v>
+        <v>0.008241467527600905</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003592402431774052</v>
+        <v>0.003734552356181131</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001837122072453943</v>
+        <v>0.001217605464887179</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001655957385243227</v>
+        <v>0.00147210294664117</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004692208695951013</v>
+        <v>0.004355688575257831</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008957972913942772</v>
+        <v>0.01649763825184458</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005505035720714246</v>
+        <v>0.006404388779868022</v>
       </c>
       <c r="V60" t="n">
-        <v>0.004777767969539658</v>
+        <v>0.002945604444029672</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002288017436048617</v>
+        <v>0.00219284455410715</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005390282671363266</v>
+        <v>0.005077915923142286</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3156444100186744</v>
+        <v>0.226423205536829</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2998222032130222</v>
+        <v>0.3357050961463092</v>
       </c>
       <c r="M61" t="n">
-        <v>3.852023036776635</v>
+        <v>3.899472266641207</v>
       </c>
       <c r="N61" t="n">
-        <v>4.246883897328603</v>
+        <v>4.261694529851082</v>
       </c>
       <c r="O61" t="n">
-        <v>0.008000835002615484</v>
+        <v>0.01136154583916313</v>
       </c>
       <c r="P61" t="n">
-        <v>0.006969793551223095</v>
+        <v>0.006276122781012861</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.006581062093736738</v>
+        <v>0.00354668590353659</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01015760648561536</v>
+        <v>0.009367580453382414</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03655672033482341</v>
+        <v>0.03166711348320733</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01355272840557953</v>
+        <v>0.02467577736985847</v>
       </c>
       <c r="U61" t="n">
-        <v>0.0088587644751767</v>
+        <v>0.008552364868070974</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01752125348787074</v>
+        <v>0.007924685062434812</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01002039379629985</v>
+        <v>0.01150065663745447</v>
       </c>
       <c r="X61" t="n">
-        <v>0.2063285917700857</v>
+        <v>0.153650244924232</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1479508876328733</v>
+        <v>0.1165417096757402</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2335736377982629</v>
+        <v>0.2712072500748563</v>
       </c>
       <c r="M62" t="n">
-        <v>4.143875794202612</v>
+        <v>4.119557613484383</v>
       </c>
       <c r="N62" t="n">
-        <v>4.196078696735074</v>
+        <v>4.208328690022832</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01013572231471528</v>
+        <v>0.01296652145494129</v>
       </c>
       <c r="P62" t="n">
-        <v>0.004716179654627466</v>
+        <v>0.004495900785977764</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.006015638688699266</v>
+        <v>0.004000553669106541</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01328294584221445</v>
+        <v>0.01262221713017217</v>
       </c>
       <c r="S62" t="n">
-        <v>0.009508792157189323</v>
+        <v>0.009239873630306676</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02101183914386468</v>
+        <v>0.0312240031042392</v>
       </c>
       <c r="U62" t="n">
-        <v>0.00916925041257584</v>
+        <v>0.007987659038281013</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01643212575949786</v>
+        <v>0.009305677166930192</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02201037740592593</v>
+        <v>0.02122118705259016</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01995416574495661</v>
+        <v>0.01948986187293265</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2740450099273068</v>
+        <v>0.2127859095014644</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2963371421677554</v>
+        <v>0.3362263613309709</v>
       </c>
       <c r="M63" t="n">
-        <v>3.971058122228126</v>
+        <v>3.979056729897652</v>
       </c>
       <c r="N63" t="n">
-        <v>4.237971206123075</v>
+        <v>4.239739917792786</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007370477188540842</v>
+        <v>0.008954605143622681</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006053861537779436</v>
+        <v>0.00542727977383668</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.005778785575188449</v>
+        <v>0.003588418274839358</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007746446798016527</v>
+        <v>0.007310927140204697</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01655511826470095</v>
+        <v>0.01503926274583652</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01291409643532909</v>
+        <v>0.0181737854385139</v>
       </c>
       <c r="U63" t="n">
-        <v>0.007907969858541563</v>
+        <v>0.007231193371523351</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01566925641199429</v>
+        <v>0.008102217359828065</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01016859251456971</v>
+        <v>0.01108031867779643</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03338385679575732</v>
+        <v>0.03001330354471574</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2247029268396697</v>
+        <v>0.1803589411167573</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3239428980426945</v>
+        <v>0.3448409942947389</v>
       </c>
       <c r="M64" t="n">
-        <v>3.76527181006721</v>
+        <v>3.834210013489763</v>
       </c>
       <c r="N64" t="n">
-        <v>4.245801467891633</v>
+        <v>4.257362661840995</v>
       </c>
       <c r="O64" t="n">
-        <v>0.008580109295817337</v>
+        <v>0.01184330685121756</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0062297669490643</v>
+        <v>0.005668392656526538</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.01100638180666269</v>
+        <v>0.00578737135311157</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01775468262348194</v>
+        <v>0.01652855335044876</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05009160432275608</v>
+        <v>0.04293546266849024</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01623433134298639</v>
+        <v>0.02700190301948806</v>
       </c>
       <c r="U64" t="n">
-        <v>0.008529822570495555</v>
+        <v>0.007850982763722675</v>
       </c>
       <c r="V64" t="n">
-        <v>0.03113392025282145</v>
+        <v>0.01333213982836715</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02629174441983547</v>
+        <v>0.02595318305165482</v>
       </c>
       <c r="X64" t="n">
-        <v>0.7307409168651849</v>
+        <v>0.5005474384759415</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2977175138061146</v>
+        <v>0.2347993178879202</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3718661859461747</v>
+        <v>0.3915461804907263</v>
       </c>
       <c r="M65" t="n">
-        <v>3.910917589484847</v>
+        <v>3.926683483740697</v>
       </c>
       <c r="N65" t="n">
-        <v>4.268391502298174</v>
+        <v>4.269855683336993</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008168707976664398</v>
+        <v>0.0102065438027897</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007792065518520204</v>
+        <v>0.007053330157425273</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.01591009005495642</v>
+        <v>0.007981488944183591</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01045815511809733</v>
+        <v>0.00962276771205864</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03117798260057641</v>
+        <v>0.02779937194762008</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01389820199854916</v>
+        <v>0.02111514832540688</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01031477565224479</v>
+        <v>0.009469602257461674</v>
       </c>
       <c r="V65" t="n">
-        <v>0.04678863461115898</v>
+        <v>0.01935971113828022</v>
       </c>
       <c r="W65" t="n">
-        <v>0.0129686084092222</v>
+        <v>0.01421577118567614</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1215408669487532</v>
+        <v>0.100570670493679</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2630911090154406</v>
+        <v>0.2134227876690053</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3180915457236916</v>
+        <v>0.3572350208117648</v>
       </c>
       <c r="M66" t="n">
-        <v>3.953139984689836</v>
+        <v>3.96341282918015</v>
       </c>
       <c r="N66" t="n">
-        <v>4.246211445618417</v>
+        <v>4.259408444545748</v>
       </c>
       <c r="O66" t="n">
-        <v>0.008753578451990296</v>
+        <v>0.01109069641592818</v>
       </c>
       <c r="P66" t="n">
-        <v>0.006860829000433353</v>
+        <v>0.006196174161418632</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.01043068174194119</v>
+        <v>0.0061094961163932</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01566223518513827</v>
+        <v>0.01494931055772131</v>
       </c>
       <c r="S66" t="n">
-        <v>0.02915070308948675</v>
+        <v>0.02715999573529515</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01644427099767844</v>
+        <v>0.02439180547733236</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009107008422150361</v>
+        <v>0.008208770886152116</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0289134040907657</v>
+        <v>0.01395436790191231</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02101157703432345</v>
+        <v>0.02140363745281743</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1492793972564135</v>
+        <v>0.1292467962964357</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.418401611669922</v>
+        <v>0.378033758727203</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3819472915502818</v>
+        <v>0.3947213665194616</v>
       </c>
       <c r="M67" t="n">
-        <v>4.381125636492835</v>
+        <v>4.37112257107835</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3437415206267</v>
+        <v>4.339059934310458</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005981321945530078</v>
+        <v>0.00771334183516295</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01443185780472609</v>
+        <v>0.01400829248932625</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01311134644951924</v>
+        <v>0.008832826891741431</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009002841936241821</v>
+        <v>0.009646353555781839</v>
       </c>
       <c r="S67" t="n">
-        <v>0.04955294692193526</v>
+        <v>0.05276454314517653</v>
       </c>
       <c r="T67" t="n">
-        <v>0.009110887363966863</v>
+        <v>0.01218441112744616</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01313118042554026</v>
+        <v>0.0125362747752769</v>
       </c>
       <c r="V67" t="n">
-        <v>0.04752995067573015</v>
+        <v>0.02638129603029016</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01285489229042732</v>
+        <v>0.01423506735731534</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07785118174200721</v>
+        <v>0.07690151086321746</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4256809874704213</v>
+        <v>0.3818260119870678</v>
       </c>
       <c r="L68" t="n">
-        <v>0.37024086989327</v>
+        <v>0.3804433632154383</v>
       </c>
       <c r="M68" t="n">
-        <v>4.452681279498789</v>
+        <v>4.412285529802531</v>
       </c>
       <c r="N68" t="n">
-        <v>4.341149041498635</v>
+        <v>4.339395362258712</v>
       </c>
       <c r="O68" t="n">
-        <v>0.006850699174922427</v>
+        <v>0.009231917212703304</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01736370747453858</v>
+        <v>0.01628437574162377</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.01389884232357233</v>
+        <v>0.007762453702357012</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01344593217992822</v>
+        <v>0.01336135272836154</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01471683289192487</v>
+        <v>0.01403469665102593</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01276432462792603</v>
+        <v>0.01849211783055578</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01608805234569639</v>
+        <v>0.01469460090193423</v>
       </c>
       <c r="V68" t="n">
-        <v>0.04205631454760868</v>
+        <v>0.01927769983464867</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01918405262622363</v>
+        <v>0.02006569512838435</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02478310122419881</v>
+        <v>0.0227738455583372</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1578375667668122</v>
+        <v>0.1011765085600368</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2144567936729055</v>
+        <v>0.1773044766578075</v>
       </c>
       <c r="M69" t="n">
-        <v>4.342039872316217</v>
+        <v>4.336669816495358</v>
       </c>
       <c r="N69" t="n">
-        <v>4.303184532172819</v>
+        <v>4.293565429207068</v>
       </c>
       <c r="O69" t="n">
-        <v>0.008246315744868482</v>
+        <v>0.01192085036804403</v>
       </c>
       <c r="P69" t="n">
-        <v>0.005349793618174257</v>
+        <v>0.005140067404071069</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.006110958250283045</v>
+        <v>0.004779986688728197</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004326322131112634</v>
+        <v>0.003953450859161891</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004195856823191065</v>
+        <v>0.003975182461431559</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01779893935194048</v>
+        <v>0.03072204792244168</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009261002924040385</v>
+        <v>0.01103774978648109</v>
       </c>
       <c r="V69" t="n">
-        <v>0.0138292357831867</v>
+        <v>0.009510092508828843</v>
       </c>
       <c r="W69" t="n">
-        <v>0.006098152479391987</v>
+        <v>0.005806384873026062</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006144672343345428</v>
+        <v>0.005929783566498684</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548404427189273</v>
+        <v>0.09853776886812335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2803484396335723</v>
+        <v>0.2513895127329258</v>
       </c>
       <c r="M70" t="n">
-        <v>4.394470536415335</v>
+        <v>4.406147207166384</v>
       </c>
       <c r="N70" t="n">
-        <v>4.362026188385227</v>
+        <v>4.351024519902161</v>
       </c>
       <c r="O70" t="n">
-        <v>0.00683737974045138</v>
+        <v>0.008765521100579968</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009679926537964173</v>
+        <v>0.01068221954004405</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.01029419268685945</v>
+        <v>0.007922641009322219</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004619420786771253</v>
+        <v>0.004296356545144776</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006474843743780381</v>
+        <v>0.006107706783452278</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01330245434463462</v>
+        <v>0.02023648112270535</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01366541402875141</v>
+        <v>0.01786036947290127</v>
       </c>
       <c r="V70" t="n">
-        <v>0.02670982624033935</v>
+        <v>0.0175526467522126</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006677903647715045</v>
+        <v>0.006430910297688076</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009672788733917848</v>
+        <v>0.009235210727375705</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259506110927289</v>
+        <v>0.2686805224204179</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3487351942206435</v>
+        <v>0.3298379176249303</v>
       </c>
       <c r="M71" t="n">
-        <v>4.436154054572222</v>
+        <v>4.434548768386005</v>
       </c>
       <c r="N71" t="n">
-        <v>4.440319465156644</v>
+        <v>4.434143043383641</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008528487484165495</v>
+        <v>0.01013475919470083</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009241273042414807</v>
+        <v>0.008543614698053002</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.01207713702270264</v>
+        <v>0.007918245385571619</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005169486642996195</v>
+        <v>0.004815296352703093</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005569849868640615</v>
+        <v>0.005204764643569146</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01410704170665147</v>
+        <v>0.01877846019129199</v>
       </c>
       <c r="U71" t="n">
-        <v>0.009886467507369101</v>
+        <v>0.009636368397903189</v>
       </c>
       <c r="V71" t="n">
-        <v>0.03237053463994669</v>
+        <v>0.01731433038885014</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006798130412147313</v>
+        <v>0.006605738005774752</v>
       </c>
       <c r="X71" t="n">
-        <v>0.007000485893441635</v>
+        <v>0.00667178450941795</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3237573962818418</v>
+        <v>0.2657819781201773</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4164125635912082</v>
+        <v>0.3863103603617924</v>
       </c>
       <c r="M72" t="n">
-        <v>4.514536388254673</v>
+        <v>4.534002379268917</v>
       </c>
       <c r="N72" t="n">
-        <v>4.505611901814954</v>
+        <v>4.499145574022029</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006054380605746239</v>
+        <v>0.006633208398129004</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007017628670037607</v>
+        <v>0.006724645729910657</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.01932574713487418</v>
+        <v>0.01144681954947674</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004440088622198801</v>
+        <v>0.004107308929607375</v>
       </c>
       <c r="S72" t="n">
-        <v>0.00611787710604061</v>
+        <v>0.005690126789497516</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008824815817617734</v>
+        <v>0.01045793283686352</v>
       </c>
       <c r="U72" t="n">
-        <v>0.007879640720981459</v>
+        <v>0.007896627128392394</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0562945012273876</v>
+        <v>0.02671937725093047</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006203244904443203</v>
+        <v>0.005899612183437609</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007784376618793378</v>
+        <v>0.007431302082436496</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08006297265283152</v>
+        <v>0.04025470310716591</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08137670514789817</v>
+        <v>0.05547139631089849</v>
       </c>
       <c r="M73" t="n">
-        <v>4.341883758983041</v>
+        <v>4.333373537311013</v>
       </c>
       <c r="N73" t="n">
-        <v>4.328688871169668</v>
+        <v>4.324632151484231</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01318043929528642</v>
+        <v>0.02656051278654263</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0125466430551157</v>
+        <v>0.01761088477961548</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002167715958196518</v>
+        <v>0.001940807240261154</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002549688039978831</v>
+        <v>0.002341227483811922</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003793148708945231</v>
+        <v>0.0002712346699651212</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03799856800368664</v>
+        <v>0.09005882264789054</v>
       </c>
       <c r="U73" t="n">
-        <v>0.02527688761485034</v>
+        <v>0.04982984561406703</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004536652955853525</v>
+        <v>0.00385627289056864</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004164534776591435</v>
+        <v>0.004034216497276533</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003228791926099474</v>
+        <v>0.003166052232820611</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0844764733101903</v>
+        <v>0.0432396473856516</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1660310188475765</v>
+        <v>0.1275131185111846</v>
       </c>
       <c r="M74" t="n">
-        <v>4.399088907307153</v>
+        <v>4.405756282529817</v>
       </c>
       <c r="N74" t="n">
-        <v>4.387721756493224</v>
+        <v>4.379623734047607</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006072932102369062</v>
+        <v>0.009036396602258273</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008410328275183171</v>
+        <v>0.00951219288903165</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.004647142523476647</v>
+        <v>0.003989001420836452</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002118002127884821</v>
+        <v>0.001965770896891096</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003735940468329064</v>
+        <v>0.003557275117506128</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01595028617400128</v>
+        <v>0.02832279090894285</v>
       </c>
       <c r="U74" t="n">
-        <v>0.01426152891022485</v>
+        <v>0.02113693945261803</v>
       </c>
       <c r="V74" t="n">
-        <v>0.009536999307135391</v>
+        <v>0.007509255721148217</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003689238551000808</v>
+        <v>0.003572465014471213</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005621872710337207</v>
+        <v>0.005458596495202792</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.207879713293752</v>
+        <v>0.1486427815751791</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2637502655822012</v>
+        <v>0.2372415857304349</v>
       </c>
       <c r="M75" t="n">
-        <v>4.205773976883957</v>
+        <v>4.1963263632822</v>
       </c>
       <c r="N75" t="n">
-        <v>4.285330064989372</v>
+        <v>4.273131781469809</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006159956762773762</v>
+        <v>0.008049330484596119</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009588744945665553</v>
+        <v>0.01017478689827593</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.007587238447960803</v>
+        <v>0.005740851996500027</v>
       </c>
       <c r="R75" t="n">
-        <v>0.00478312747709922</v>
+        <v>0.004479090666957137</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007195917205156532</v>
+        <v>0.006956014864066315</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01213916372238912</v>
+        <v>0.01830197226282498</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01262105451104735</v>
+        <v>0.01531091751475299</v>
       </c>
       <c r="V75" t="n">
-        <v>0.0181684843263972</v>
+        <v>0.0119442418441968</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006550918900585312</v>
+        <v>0.006385456671668417</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01090162797408519</v>
+        <v>0.0106358047943159</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053128897390902</v>
+        <v>0.006369178043669377</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02508609066334347</v>
+        <v>0.01261258660883754</v>
       </c>
       <c r="M76" t="n">
-        <v>4.358945383991737</v>
+        <v>4.366980950655456</v>
       </c>
       <c r="N76" t="n">
-        <v>4.318049240424751</v>
+        <v>4.315739753543173</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04219383973292156</v>
+        <v>0.1220354474114868</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02731077279643043</v>
+        <v>0.06977388087551961</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002159166201156925</v>
+        <v>0.002112399601787165</v>
       </c>
       <c r="R76" t="n">
-        <v>0.00221778016466729</v>
+        <v>0.002116109762018163</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007945433829504842</v>
+        <v>0.0007606266839337863</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1426419537058833</v>
+        <v>0.5012827575709123</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08403595881690398</v>
+        <v>0.2848303657151451</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003928934316714309</v>
+        <v>0.003653492051418415</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003737555112816588</v>
+        <v>0.003680396910777065</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002698768418534519</v>
+        <v>0.002684782228033904</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03789390692492493</v>
+        <v>0.01471419240858703</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08292963581181916</v>
+        <v>0.04879795355628472</v>
       </c>
       <c r="M77" t="n">
-        <v>4.275909837651753</v>
+        <v>4.278059968673261</v>
       </c>
       <c r="N77" t="n">
-        <v>4.243110822914587</v>
+        <v>4.238087355601671</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01335557096114733</v>
+        <v>0.02725600802704585</v>
       </c>
       <c r="P77" t="n">
-        <v>0.003709349423202523</v>
+        <v>0.003604208836173149</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002379726884508766</v>
+        <v>0.002119454954673124</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003763306604480696</v>
+        <v>0.0003389795294416913</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001771409539367823</v>
+        <v>0.001687012383260638</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03341861986133945</v>
+        <v>0.08448269531811869</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01283848610580937</v>
+        <v>0.02077965702906235</v>
       </c>
       <c r="V77" t="n">
-        <v>0.004071085524943788</v>
+        <v>0.003436142524285324</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002024296405620972</v>
+        <v>0.001995876991854825</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002769094973651774</v>
+        <v>0.002714291076052019</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02722131315634268</v>
+        <v>0.009270839155371313</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07757285863185416</v>
+        <v>0.04545609631557472</v>
       </c>
       <c r="M78" t="n">
-        <v>4.411801604657093</v>
+        <v>4.408817932135783</v>
       </c>
       <c r="N78" t="n">
-        <v>4.377579260969767</v>
+        <v>4.362545037288026</v>
       </c>
       <c r="O78" t="n">
-        <v>0.006191725781492362</v>
+        <v>0.01110894999695566</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000015629e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.002055080234097392</v>
+        <v>0.00197147610529522</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001676613644070592</v>
+        <v>0.0001285615819903837</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000053e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.02127841748029065</v>
+        <v>0.04589527158411448</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01842605984610099</v>
+        <v>0.0223009582419472</v>
       </c>
       <c r="V78" t="n">
-        <v>0.003649740698448271</v>
+        <v>0.003343603908246705</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001708170741376304</v>
+        <v>0.00167453506465394</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002929186528738509</v>
+        <v>0.003013550785088979</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.291298707758667</v>
+        <v>0.2303690117158935</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3305190424627622</v>
+        <v>0.2922880082219665</v>
       </c>
       <c r="M79" t="n">
-        <v>4.395075630781815</v>
+        <v>4.373390288550217</v>
       </c>
       <c r="N79" t="n">
-        <v>4.439000976856815</v>
+        <v>4.374687753223522</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0030493650607155</v>
+        <v>0.003874377896894359</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001822142396168952</v>
+        <v>0.0016599042526357</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.003531992673649635</v>
+        <v>0.002263333549891524</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001661419250930073</v>
+        <v>0.001486610813278864</v>
       </c>
       <c r="S79" t="n">
-        <v>1.000000009297441e-05</v>
+        <v>0.4999999999999485</v>
       </c>
       <c r="T79" t="n">
-        <v>0.005999946057535997</v>
+        <v>0.009242686592394859</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002118343938152528</v>
+        <v>0.002317044747122417</v>
       </c>
       <c r="V79" t="n">
-        <v>0.01106190708826921</v>
+        <v>0.005528595548609682</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002607464827299831</v>
+        <v>0.002331140057399013</v>
       </c>
       <c r="X79" t="n">
-        <v>0.09212410143803679</v>
+        <v>11323.29021045563</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1623021847871931</v>
+        <v>0.1039261725912166</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2461521505440487</v>
+        <v>0.2177205905103834</v>
       </c>
       <c r="M80" t="n">
-        <v>4.51750010072576</v>
+        <v>4.528963221921295</v>
       </c>
       <c r="N80" t="n">
-        <v>4.473602328272493</v>
+        <v>4.423770408154914</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004240554041854937</v>
+        <v>0.005951138760815349</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002617430235380637</v>
+        <v>0.002696588537901111</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.003020996001069391</v>
+        <v>0.002332579388829773</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001734728906689512</v>
+        <v>0.001592891305252286</v>
       </c>
       <c r="S80" t="n">
-        <v>1.000000000000011e-05</v>
+        <v>0.4999999999996049</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01064745352376012</v>
+        <v>0.01822606393509635</v>
       </c>
       <c r="U80" t="n">
-        <v>0.003119576531330426</v>
+        <v>0.004384310329737579</v>
       </c>
       <c r="V80" t="n">
-        <v>0.008809571716300571</v>
+        <v>0.005608328160742104</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002866173669782213</v>
+        <v>0.002570635045126057</v>
       </c>
       <c r="X80" t="n">
-        <v>0.1227993893269681</v>
+        <v>13524.07704700123</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2797133348512962</v>
+        <v>0.2166350389501655</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2613693841799036</v>
+        <v>0.2371417458613794</v>
       </c>
       <c r="M81" t="n">
-        <v>4.547852263736372</v>
+        <v>4.522784247933544</v>
       </c>
       <c r="N81" t="n">
-        <v>4.585465525856633</v>
+        <v>4.544896669458152</v>
       </c>
       <c r="O81" t="n">
-        <v>0.003804179579311715</v>
+        <v>0.005296059022033181</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002242178796737677</v>
+        <v>0.00203526027187488</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.002110477016987303</v>
+        <v>0.001499616329197247</v>
       </c>
       <c r="R81" t="n">
-        <v>0.00162516530894053</v>
+        <v>0.001541782119411789</v>
       </c>
       <c r="S81" t="n">
-        <v>1.000000000000107e-05</v>
+        <v>0.4999999999728434</v>
       </c>
       <c r="T81" t="n">
-        <v>0.007874350316814688</v>
+        <v>0.01319379447680768</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003200205194617548</v>
+        <v>0.003512461142381435</v>
       </c>
       <c r="V81" t="n">
-        <v>0.005901886150266844</v>
+        <v>0.003324158690234575</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002511681053593598</v>
+        <v>0.002256930545991414</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1086244744926429</v>
+        <v>17920.27500102449</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.191395009818949</v>
+        <v>0.1242093141540693</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1472659688796732</v>
+        <v>0.1490321853629991</v>
       </c>
       <c r="M82" t="n">
-        <v>4.463985251926877</v>
+        <v>4.419262235589021</v>
       </c>
       <c r="N82" t="n">
-        <v>4.585567843391069</v>
+        <v>4.605624092861748</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006875098066507971</v>
+        <v>0.01120430684438876</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003110473071782004</v>
+        <v>0.003014696196797962</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001345032898845416</v>
+        <v>0.001120934802493275</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001761914143982365</v>
+        <v>0.001740307876196882</v>
       </c>
       <c r="S82" t="n">
-        <v>0.4999999999642853</v>
+        <v>0.0009068663020461606</v>
       </c>
       <c r="T82" t="n">
-        <v>0.02417866104757076</v>
+        <v>0.03395955230409108</v>
       </c>
       <c r="U82" t="n">
-        <v>0.005817071056176423</v>
+        <v>0.009518257289088086</v>
       </c>
       <c r="V82" t="n">
-        <v>0.003963107370643349</v>
+        <v>0.002265557876177989</v>
       </c>
       <c r="W82" t="n">
-        <v>0.00332318454856039</v>
+        <v>0.002804928622121021</v>
       </c>
       <c r="X82" t="n">
-        <v>30576.12093159843</v>
+        <v>0.4529554584650052</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.189934792401037</v>
+        <v>0.1273374851235748</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1825649533455875</v>
+        <v>0.157400500745707</v>
       </c>
       <c r="M83" t="n">
-        <v>4.578578953049799</v>
+        <v>4.56844405665582</v>
       </c>
       <c r="N83" t="n">
-        <v>4.572070906719971</v>
+        <v>4.569187436921868</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004176303540321362</v>
+        <v>0.006228560111931896</v>
       </c>
       <c r="P83" t="n">
-        <v>0.00171416512532195</v>
+        <v>0.001748406588302307</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001440721495200495</v>
+        <v>0.001197211537960298</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001422804646204883</v>
+        <v>0.001338320582679912</v>
       </c>
       <c r="S83" t="n">
-        <v>1.000000238964637e-05</v>
+        <v>1.000000000612286e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.01015904721240343</v>
+        <v>0.01803997071749969</v>
       </c>
       <c r="U83" t="n">
-        <v>0.004949107285929085</v>
+        <v>0.006721020505277444</v>
       </c>
       <c r="V83" t="n">
-        <v>0.003728365474135352</v>
+        <v>0.002615807150191567</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002372796481256224</v>
+        <v>0.00209822374099612</v>
       </c>
       <c r="X83" t="n">
-        <v>0.1285327874998751</v>
+        <v>0.1666386537309144</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.171344845273151</v>
+        <v>0.08008330526260318</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3150855700217797</v>
+        <v>0.2347346333735086</v>
       </c>
       <c r="M84" t="n">
-        <v>4.585710978228106</v>
+        <v>3.382055805903954</v>
       </c>
       <c r="N84" t="n">
-        <v>4.514447225996494</v>
+        <v>4.453971427677734</v>
       </c>
       <c r="O84" t="n">
-        <v>0.00339100588623381</v>
+        <v>0.005104231222167039</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0006915266427309581</v>
+        <v>1.000000000000145e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.004446731886819412</v>
+        <v>0.002752311988366877</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002270999306836499</v>
+        <v>0.001942772582694066</v>
       </c>
       <c r="S84" t="n">
-        <v>1e-05</v>
+        <v>0.4999999999999321</v>
       </c>
       <c r="T84" t="n">
-        <v>0.007793437798429175</v>
+        <v>0.01596272339679174</v>
       </c>
       <c r="U84" t="n">
-        <v>0.004561462884380771</v>
+        <v>0.005118553751037366</v>
       </c>
       <c r="V84" t="n">
-        <v>0.01460357726672547</v>
+        <v>0.007404730175260726</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003725108105572998</v>
+        <v>0.003195418765320875</v>
       </c>
       <c r="X84" t="n">
-        <v>0.08015211397900641</v>
+        <v>13432.9369331339</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2347111018878213</v>
+        <v>0.232649974815383</v>
       </c>
       <c r="L85" t="n">
-        <v>0.295207682566716</v>
+        <v>0.2503677912979759</v>
       </c>
       <c r="M85" t="n">
-        <v>4.499856930037251</v>
+        <v>4.312526024436617</v>
       </c>
       <c r="N85" t="n">
-        <v>4.494031048189669</v>
+        <v>4.385938184561081</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003123853781395702</v>
+        <v>0.004768096678336523</v>
       </c>
       <c r="P85" t="n">
-        <v>1.000000000701515e-05</v>
+        <v>0.001685538803218939</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.003071987961639764</v>
+        <v>0.001580410836808789</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001784312597282091</v>
+        <v>0.001422356102245414</v>
       </c>
       <c r="S85" t="n">
-        <v>1.000000000000973e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T85" t="n">
-        <v>0.006948181082872566</v>
+        <v>0.01235886264802923</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008318811544661376</v>
+        <v>0.003428135596984249</v>
       </c>
       <c r="V85" t="n">
-        <v>0.01012274793318518</v>
+        <v>0.003633335137743125</v>
       </c>
       <c r="W85" t="n">
-        <v>0.002901263572513301</v>
+        <v>0.002169788631533367</v>
       </c>
       <c r="X85" t="n">
-        <v>0.1105351683117262</v>
+        <v>18360.72015810333</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1247724149338163</v>
+        <v>0.1063207427095769</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1593628540125017</v>
+        <v>0.1881933317005607</v>
       </c>
       <c r="M86" t="n">
-        <v>4.570462719990509</v>
+        <v>4.515115790775487</v>
       </c>
       <c r="N86" t="n">
-        <v>4.515451460297303</v>
+        <v>4.436565061005309</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005658362437520068</v>
+        <v>0.006787665072071847</v>
       </c>
       <c r="P86" t="n">
-        <v>1.000000000000045e-05</v>
+        <v>0.00272660493227992</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001965539086526244</v>
+        <v>0.00192774752448879</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001796124563344605</v>
+        <v>0.001602177685287185</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000000002528958e-05</v>
+        <v>0.4999999999999994</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01748892469336824</v>
+        <v>0.02145019925618195</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01076500190864138</v>
+        <v>0.006269128759394136</v>
       </c>
       <c r="V86" t="n">
-        <v>0.004959107179541152</v>
+        <v>0.004318345807380173</v>
       </c>
       <c r="W86" t="n">
-        <v>0.003011727484439199</v>
+        <v>0.00262564607667321</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1599482502462652</v>
+        <v>21566.41144480819</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836932533354582</v>
+        <v>0.1406552764699671</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3217826304399089</v>
+        <v>0.1438421564541501</v>
       </c>
       <c r="M87" t="n">
-        <v>4.671002060938001</v>
+        <v>4.405005859431377</v>
       </c>
       <c r="N87" t="n">
-        <v>4.624548267061019</v>
+        <v>4.603972792640124</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004065531845368829</v>
+        <v>0.0138823693215494</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0005287448694617137</v>
+        <v>0.004150565073769642</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.004712946527177218</v>
+        <v>0.001239442104862697</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002298805776887696</v>
+        <v>0.001942600353559264</v>
       </c>
       <c r="S87" t="n">
-        <v>1e-05</v>
+        <v>0.0009989770622487915</v>
       </c>
       <c r="T87" t="n">
-        <v>0.009286656785054833</v>
+        <v>0.04530490897862714</v>
       </c>
       <c r="U87" t="n">
-        <v>0.006448920658482471</v>
+        <v>0.01184237864446213</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01355628129329457</v>
+        <v>0.002403115244039473</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003593754427822578</v>
+        <v>0.003152044139994795</v>
       </c>
       <c r="X87" t="n">
-        <v>0.08726436389754769</v>
+        <v>0.4619308308663748</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2269187226468679</v>
+        <v>0.1958473687662303</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1608076984320481</v>
+        <v>0.2436811967209199</v>
       </c>
       <c r="M88" t="n">
-        <v>4.508038364188548</v>
+        <v>4.5240596280908</v>
       </c>
       <c r="N88" t="n">
-        <v>4.616256397861295</v>
+        <v>4.546396592013187</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005452937624335883</v>
+        <v>0.005584145213556851</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0002918095167953743</v>
+        <v>0.00233753810251095</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001197308463295356</v>
+        <v>0.001621145235619104</v>
       </c>
       <c r="R88" t="n">
-        <v>0.00139710216235785</v>
+        <v>0.001692415332561156</v>
       </c>
       <c r="S88" t="n">
-        <v>0.4999999996119651</v>
+        <v>0.1640676430750137</v>
       </c>
       <c r="T88" t="n">
-        <v>0.01570988562740987</v>
+        <v>0.01507266153172322</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01869809029283888</v>
+        <v>0.005678351255743345</v>
       </c>
       <c r="V88" t="n">
-        <v>0.003097420985304032</v>
+        <v>0.003605009897913573</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002148696395860506</v>
+        <v>0.003051824593876234</v>
       </c>
       <c r="X88" t="n">
-        <v>21137.86043238085</v>
+        <v>1798.724450672134</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3352916146113781</v>
+        <v>0.2882739572399665</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3410051630823244</v>
+        <v>0.2783509614000913</v>
       </c>
       <c r="M89" t="n">
-        <v>4.501914574676857</v>
+        <v>4.43262461682365</v>
       </c>
       <c r="N89" t="n">
-        <v>4.602133439799404</v>
+        <v>4.569726954502554</v>
       </c>
       <c r="O89" t="n">
-        <v>0.004105550385983831</v>
+        <v>0.005809606757248858</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001577168375250506</v>
+        <v>0.0003769539363309212</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.003669755913252894</v>
+        <v>0.002011902168114216</v>
       </c>
       <c r="R89" t="n">
-        <v>0.00192518783043757</v>
+        <v>0.001770729880067014</v>
       </c>
       <c r="S89" t="n">
-        <v>1e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T89" t="n">
-        <v>0.008284268132251664</v>
+        <v>0.01526176932998909</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004312184686117029</v>
+        <v>0.003395122595854767</v>
       </c>
       <c r="V89" t="n">
-        <v>0.01108419958385802</v>
+        <v>0.004688176525263031</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002831795004613285</v>
+        <v>0.00258670567740796</v>
       </c>
       <c r="X89" t="n">
-        <v>0.06763402706008698</v>
+        <v>13183.72371730601</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2309014164628462</v>
+        <v>0.4614348426234622</v>
       </c>
       <c r="L90" t="n">
-        <v>0.483386414036669</v>
+        <v>0.5242327772282152</v>
       </c>
       <c r="M90" t="n">
-        <v>4.475080783493183</v>
+        <v>4.51157711099569</v>
       </c>
       <c r="N90" t="n">
-        <v>4.283333172759931</v>
+        <v>4.295638066052733</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003752986198842751</v>
+        <v>0.00387866042803835</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003629405959523495</v>
+        <v>0.004514511541183412</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.2109041479825474</v>
+        <v>0.01288942993200503</v>
       </c>
       <c r="R90" t="n">
-        <v>0.009860024489724827</v>
+        <v>0.01102594884407855</v>
       </c>
       <c r="S90" t="n">
-        <v>0.003202106152940633</v>
+        <v>0.003409844168584894</v>
       </c>
       <c r="T90" t="n">
-        <v>0.007182533005404356</v>
+        <v>0.006785296208056096</v>
       </c>
       <c r="U90" t="n">
-        <v>0.00595018370944406</v>
+        <v>0.006150913484596976</v>
       </c>
       <c r="V90" t="n">
-        <v>1.265635007840707</v>
+        <v>0.02029156533843756</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02551555414458263</v>
+        <v>0.02443854517099459</v>
       </c>
       <c r="X90" t="n">
-        <v>0.1305262995385734</v>
+        <v>0.1198816875153625</v>
       </c>
     </row>
   </sheetData>
